--- a/public/templates/竞迹统一数据导入模板.xlsx
+++ b/public/templates/竞迹统一数据导入模板.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="264">
   <si>
     <t>竞迹训练监控系统｜统一数据导入模板</t>
   </si>
@@ -291,7 +291,7 @@
     <t>训练课次</t>
   </si>
   <si>
-    <t>每人每课一行，时长与距离至少填写一项；强度未测留空；SRPE未填时仅按已填时长×RPE计算。</t>
+    <t>每人每课一行，时长与距离至少填写一项；仅承载已填力量组次的课次可同时留空。强度未测留空；SRPE未填时仅按已填时长×RPE计算。</t>
   </si>
   <si>
     <t>日期</t>
@@ -345,7 +345,7 @@
     <t>力量训练组次</t>
   </si>
   <si>
-    <t>每人每动作每组一行；计划次数和强度百分比选填，实际次数和实际重量必填。计划重量由训练计划维护。</t>
+    <t>每人每动作每组一行；课次序号与训练课次表一致，旧文件缺省时仅唯一课次可自动关联。实际次数和实际重量必填；完成状态填0/1或未完成/已完成，其他字段按实填写。</t>
   </si>
   <si>
     <t>课次名称</t>
@@ -375,6 +375,24 @@
     <t>身体部位</t>
   </si>
   <si>
+    <t>动作代码</t>
+  </si>
+  <si>
+    <t>计划重量kg</t>
+  </si>
+  <si>
+    <t>完成状态</t>
+  </si>
+  <si>
+    <t>训练环境</t>
+  </si>
+  <si>
+    <t>组次时长分钟</t>
+  </si>
+  <si>
+    <t>组次距离千米</t>
+  </si>
+  <si>
     <t>每日恢复</t>
   </si>
   <si>
@@ -477,7 +495,7 @@
     <t>其他测试</t>
   </si>
   <si>
-    <t>高级选填：一项指标一行；代码和单位见数据字典；常用指标优先填写对应专用表。</t>
+    <t>高级选填：一项指标一行；代码和单位见数据字典；测试类型和目标值按原记录保留。常用指标优先填写对应专用表。</t>
   </si>
   <si>
     <t>测试类型</t>
@@ -499,6 +517,9 @@
   </si>
   <si>
     <t>测试时长分钟</t>
+  </si>
+  <si>
+    <t>目标值</t>
   </si>
   <si>
     <t>填写工作表</t>
@@ -1279,7 +1300,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1298,7 +1319,7 @@
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1323,40 +1344,40 @@
         <v>11</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="O3" s="6" t="s">
         <v>41</v>
@@ -1375,19 +1396,19 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="18" style="3" customWidth="1"/>
     <col min="4" max="9" width="16" customWidth="1"/>
     <col min="10" max="11" width="28" customWidth="1"/>
-    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="12" max="13" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1400,10 +1421,11 @@
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
-    </row>
-    <row r="2" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" s="4"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1416,8 +1438,9 @@
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
-    </row>
-    <row r="3" ht="32" customHeight="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M2" s="5"/>
+    </row>
+    <row r="3" ht="32" customHeight="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
@@ -1428,38 +1451,41 @@
         <v>72</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>41</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>158</v>
+        <v>164</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L3"/>
+  <autoFilter ref="A3:M3"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1477,767 +1503,767 @@
   <sheetData>
     <row r="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D2" t="s">
         <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D3" t="s">
         <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D4" t="s">
         <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D5" t="s">
         <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D6" t="s">
         <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" t="s">
         <v>176</v>
-      </c>
-      <c r="C7" t="s">
-        <v>169</v>
       </c>
       <c r="D7" t="s">
         <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B8" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C8" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D8" t="s">
         <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B9" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C9" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B10" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C10" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D10" t="s">
         <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C11" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D11" t="s">
         <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C12" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D12" t="s">
         <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B13" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C13" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D13" t="s">
         <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B14" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C14" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D14" t="s">
         <v>42</v>
       </c>
       <c r="E14" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>199</v>
+      </c>
+      <c r="B15" t="s">
+        <v>200</v>
+      </c>
+      <c r="C15" t="s">
         <v>192</v>
-      </c>
-      <c r="B15" t="s">
-        <v>193</v>
-      </c>
-      <c r="C15" t="s">
-        <v>185</v>
       </c>
       <c r="D15" t="s">
         <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s">
         <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="D16" t="s">
         <v>42</v>
       </c>
       <c r="E16" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C17" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D17" t="s">
         <v>42</v>
       </c>
       <c r="E17" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C18" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D18" t="s">
         <v>42</v>
       </c>
       <c r="E18" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B19" t="s">
         <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="D19" t="s">
         <v>42</v>
       </c>
       <c r="E19" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C20" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D20" t="s">
         <v>42</v>
       </c>
       <c r="E20" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C21" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D21" t="s">
         <v>42</v>
       </c>
       <c r="E21" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C22" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D22" t="s">
         <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C23" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D23" t="s">
         <v>42</v>
       </c>
       <c r="E23" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C24" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D24" t="s">
         <v>42</v>
       </c>
       <c r="E24" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C25" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D25" t="s">
         <v>42</v>
       </c>
       <c r="E25" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C26" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D26" t="s">
         <v>42</v>
       </c>
       <c r="E26" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B27" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C27" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D27" t="s">
         <v>70</v>
       </c>
       <c r="E27" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B28" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C28" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D28" t="s">
         <v>70</v>
       </c>
       <c r="E28" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B29" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C29" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D29" t="s">
         <v>70</v>
       </c>
       <c r="E29" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B30" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C30" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D30" t="s">
         <v>70</v>
       </c>
       <c r="E30" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B31" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C31" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="D31" t="s">
         <v>70</v>
       </c>
       <c r="E31" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B32" t="s">
         <v>81</v>
       </c>
       <c r="C32" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D32" t="s">
         <v>79</v>
       </c>
       <c r="E32" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B33" t="s">
         <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D33" t="s">
         <v>79</v>
       </c>
       <c r="E33" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B34" t="s">
         <v>83</v>
       </c>
       <c r="C34" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D34" t="s">
         <v>79</v>
       </c>
       <c r="E34" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B35" t="s">
         <v>84</v>
       </c>
       <c r="C35" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D35" t="s">
         <v>79</v>
       </c>
       <c r="E35" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B36" t="s">
         <v>85</v>
       </c>
       <c r="C36" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D36" t="s">
         <v>79</v>
       </c>
       <c r="E36" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="B37" t="s">
         <v>86</v>
       </c>
       <c r="C37" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D37" t="s">
         <v>79</v>
       </c>
       <c r="E37" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B38" t="s">
         <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D38" t="s">
         <v>79</v>
       </c>
       <c r="E38" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B39" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C39" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D39" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E39" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B40" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C40" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D40" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E40" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B41" t="s">
         <v>81</v>
       </c>
       <c r="C41" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D41" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E41" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B42" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="C42" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D42" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E42" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B43" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C43" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D43" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E43" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B44" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C44" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D44" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E44" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>262</v>
+      </c>
+      <c r="B45" t="s">
+        <v>263</v>
+      </c>
+      <c r="C45" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" t="s">
+        <v>156</v>
+      </c>
+      <c r="E45" t="s">
         <v>255</v>
-      </c>
-      <c r="B45" t="s">
-        <v>256</v>
-      </c>
-      <c r="C45" t="s">
-        <v>163</v>
-      </c>
-      <c r="D45" t="s">
-        <v>150</v>
-      </c>
-      <c r="E45" t="s">
-        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -2912,16 +2938,17 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="18" style="3" customWidth="1"/>
     <col min="4" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="28" customWidth="1"/>
+    <col min="15" max="22" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>106</v>
       </c>
@@ -2938,8 +2965,16 @@
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
-    </row>
-    <row r="2" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>107</v>
       </c>
@@ -2956,8 +2991,16 @@
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
-    </row>
-    <row r="3" ht="32" customHeight="1" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+    </row>
+    <row r="3" ht="32" customHeight="1" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
@@ -3000,12 +3043,36 @@
       <c r="N3" s="6" t="s">
         <v>41</v>
       </c>
+      <c r="O3" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>96</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N3"/>
+  <autoFilter ref="A3:V3"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:V2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3025,7 +3092,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3041,7 +3108,7 @@
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3066,28 +3133,28 @@
         <v>90</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>41</v>
@@ -3118,7 +3185,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3134,7 +3201,7 @@
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3156,31 +3223,31 @@
         <v>11</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F3" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="H3" s="6" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>41</v>

--- a/public/templates/竞迹统一数据导入模板.xlsx
+++ b/public/templates/竞迹统一数据导入模板.xlsx
@@ -42,7 +42,7 @@
     <t>5. 数值只填数字，单位见表头；空白表示未提供，真实0保留；非法值会标明单元格并阻止该行入库。</t>
   </si>
   <si>
-    <t>6. 同一事实只填一次；重复记录默认保留已有值，覆盖需确认；已有运动员不通过导入调队。</t>
+    <t>6. 同一事实只填一次；本次导入非空值自动更新已有记录，空白保留原值；同一文件内不同值需审查；已有运动员不通过导入调队。</t>
   </si>
   <si>
     <t>7. 冠军模型、雷达图、参考值和达标等级由系统分析，不在模板中采集。</t>

--- a/public/templates/竞迹统一数据导入模板.xlsx
+++ b/public/templates/竞迹统一数据导入模板.xlsx
@@ -34,9 +34,9 @@
       <text>
         <r>
           <t xml:space="preserve">系统运动员编号
-系统预填｜无单位
+系统预填
 例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。</t>
+已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
         </r>
       </text>
     </comment>
@@ -44,9 +44,9 @@
       <text>
         <r>
           <t xml:space="preserve">姓名
-条件必填｜无单位
+条件必填：没有系统编号，或新建人员时填写
 例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。</t>
+无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
         </r>
       </text>
     </comment>
@@ -54,9 +54,9 @@
       <text>
         <r>
           <t xml:space="preserve">评估日期
-条件必填｜YYYY-MM-DD
+条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
 例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。</t>
+本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
         </r>
       </text>
     </comment>
@@ -64,9 +64,9 @@
       <text>
         <r>
           <t xml:space="preserve">总分
-条件必填｜分
-例：按既有评价协议原值填写
-新增竞技状态记录需有依据的原始总分；单项一般耐力/核心力量评分可单独填写并注明评估协议，不能编造总分。</t>
+条件必填：填写专项耐力等竞技评价时提供真实总分｜分
+例：80（须按实际评分表打分）
+新增竞技状态记录需有依据的原始总分；单项一般耐力/核心力量评分可单独填写并注明评估协议，不能编造总分。 例：80（须按实际评分表打分）</t>
         </r>
       </text>
     </comment>
@@ -74,9 +74,9 @@
       <text>
         <r>
           <t xml:space="preserve">等级
-选填｜无单位
+选填
 例：建设
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：建设</t>
         </r>
       </text>
     </comment>
@@ -85,8 +85,8 @@
         <r>
           <t xml:space="preserve">一般耐力评分
 选填｜分
-例：按既有协议填写
-仅填写实际已采集数据，未提供留空。</t>
+例：80（须按实际评分表打分）
+仅填写实际已采集数据，未提供留空。 例：80（须按实际评分表打分）</t>
         </r>
       </text>
     </comment>
@@ -95,8 +95,8 @@
         <r>
           <t xml:space="preserve">核心力量评分
 选填｜分
-例：按既有协议填写
-仅填写实际已采集数据，未提供留空。</t>
+例：75（须按实际评分表打分）
+仅填写实际已采集数据，未提供留空。 例：75（须按实际评分表打分）</t>
         </r>
       </text>
     </comment>
@@ -104,9 +104,10 @@
       <text>
         <r>
           <t xml:space="preserve">评估协议
-条件必填｜无单位
-例：本队已采用的评分协议名称及版本
-一般耐力和核心力量评分必须填写协议；禁止虚构总分或维度得分。</t>
+评分标准：这些分数按哪张评分表打的
+条件必填：填一般耐力/核心力量评分时填写
+例：队内核心力量评分表（2026版）
+评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。</t>
         </r>
       </text>
     </comment>
@@ -116,7 +117,7 @@
           <t xml:space="preserve">专项耐力
 选填｜分
 例：按现有评分协议填写
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写</t>
         </r>
       </text>
     </comment>
@@ -126,7 +127,7 @@
           <t xml:space="preserve">力量爆发
 选填｜分
 例：按现有评分协议填写
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写</t>
         </r>
       </text>
     </comment>
@@ -136,7 +137,7 @@
           <t xml:space="preserve">技术效率
 选填｜分
 例：按现有评分协议填写
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写</t>
         </r>
       </text>
     </comment>
@@ -146,7 +147,7 @@
           <t xml:space="preserve">负荷适应
 选填｜分
 例：按现有评分协议填写
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写</t>
         </r>
       </text>
     </comment>
@@ -156,7 +157,7 @@
           <t xml:space="preserve">恢复能力
 选填｜分
 例：按现有评分协议填写
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写</t>
         </r>
       </text>
     </comment>
@@ -166,7 +167,7 @@
           <t xml:space="preserve">比赛能力
 选填｜分
 例：按现有评分协议填写
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写</t>
         </r>
       </text>
     </comment>
@@ -174,9 +175,9 @@
       <text>
         <r>
           <t xml:space="preserve">备注
-选填｜无单位
+选填
 例：本次实测
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：本次实测</t>
         </r>
       </text>
     </comment>
@@ -194,9 +195,9 @@
       <text>
         <r>
           <t xml:space="preserve">系统运动员编号
-系统预填｜无单位
+系统预填
 例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。</t>
+已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
         </r>
       </text>
     </comment>
@@ -204,9 +205,9 @@
       <text>
         <r>
           <t xml:space="preserve">姓名
-条件必填｜无单位
+条件必填：没有系统编号，或新建人员时填写
 例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。</t>
+无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
         </r>
       </text>
     </comment>
@@ -214,9 +215,9 @@
       <text>
         <r>
           <t xml:space="preserve">测试日期
-条件必填｜YYYY-MM-DD
+条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
 例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。</t>
+本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
         </r>
       </text>
     </comment>
@@ -224,9 +225,10 @@
       <text>
         <r>
           <t xml:space="preserve">指标代码
-必填｜无单位
+测试项目编号：告诉系统测的是哪一项
+必填
 例：vertical_jump_cm
-按项目指标字典填写；一项指标一行。</t>
+测试项目编号：告诉系统测的是哪一项。怎么填：从数据字典复制对应代码；例如纵跳用vertical_jump_cm，不用自己编编号。例：vertical_jump_cm。为什么：同一个数值可能是距离、重量或时间，需要明确对应的测试项目。不知道时：先找身体测量、体能测试等现成工作表；字典仍找不到时先确认项目，不随便套用别的代码。</t>
         </r>
       </text>
     </comment>
@@ -234,9 +236,9 @@
       <text>
         <r>
           <t xml:space="preserve">指标名称
-选填｜无单位
+选填
 例：纵跳
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：纵跳</t>
         </r>
       </text>
     </comment>
@@ -246,7 +248,7 @@
           <t xml:space="preserve">数值
 必填｜指标字典单位
 例：45
-按项目指标字典填写；一项指标一行。</t>
+按项目指标字典填写；一项指标一行。 例：45</t>
         </r>
       </text>
     </comment>
@@ -254,9 +256,9 @@
       <text>
         <r>
           <t xml:space="preserve">单位
-条件必填｜指标字典单位
+条件必填：系统不能从指标字典确定单位时填写｜指标字典单位
 例：cm
-可由已知指标字典确定；不能确定时必须补充，冲突不得静默换算。</t>
+可由已知指标字典确定；不能确定时必须补充，冲突不得静默换算。 例：cm</t>
         </r>
       </text>
     </comment>
@@ -264,9 +266,9 @@
       <text>
         <r>
           <t xml:space="preserve">测试类型
-选填｜无单位
+选填
 例：专项测试
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：专项测试</t>
         </r>
       </text>
     </comment>
@@ -274,9 +276,10 @@
       <text>
         <r>
           <t xml:space="preserve">协议
-选填｜无单位
-例：实际测试方法及版本
-仅填写实际已采集数据，未提供留空。</t>
+测试方法：记录这个数值的实际测法
+选填
+例：纵跳摸高，测3次取最好成绩
+测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。</t>
         </r>
       </text>
     </comment>
@@ -284,10 +287,9 @@
       <text>
         <r>
           <t xml:space="preserve">侧别
-条件必填｜无单位
+条件必填：测左侧、右侧或双侧时填写
 例：左
-侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。
-可选值：左、右、双侧、中央</t>
+侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央</t>
         </r>
       </text>
     </comment>
@@ -295,9 +297,9 @@
       <text>
         <r>
           <t xml:space="preserve">备注
-选填｜无单位
+选填
 例：本次实测
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：本次实测</t>
         </r>
       </text>
     </comment>
@@ -307,7 +309,7 @@
           <t xml:space="preserve">测试时长分钟
 选填｜min
 例：12.5
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -317,7 +319,7 @@
           <t xml:space="preserve">目标值
 选填｜与实测值同单位
 例：50
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：50</t>
         </r>
       </text>
     </comment>
@@ -335,9 +337,9 @@
       <text>
         <r>
           <t xml:space="preserve">系统运动员编号
-系统预填｜无单位
+系统预填
 例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。</t>
+已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
         </r>
       </text>
     </comment>
@@ -345,9 +347,9 @@
       <text>
         <r>
           <t xml:space="preserve">姓名
-条件必填｜无单位
+条件必填：没有系统编号，或新建人员时填写
 例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。</t>
+无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
         </r>
       </text>
     </comment>
@@ -355,9 +357,9 @@
       <text>
         <r>
           <t xml:space="preserve">运动项目
-条件必填｜无单位
+条件必填：未由当前项目、队伍预填时填写
 例：赛艇
-使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。</t>
+使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：赛艇</t>
         </r>
       </text>
     </comment>
@@ -365,9 +367,9 @@
       <text>
         <r>
           <t xml:space="preserve">所属队伍
-条件必填｜无单位
+条件必填：未由当前项目、队伍预填时填写
 例：一队
-使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。</t>
+使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队</t>
         </r>
       </text>
     </comment>
@@ -375,10 +377,9 @@
       <text>
         <r>
           <t xml:space="preserve">性别
-选填｜无单位
+选填
 例：男
-仅填写实际已采集数据，未提供留空。
-可选值：男、女</t>
+仅填写实际已采集数据，未提供留空。 例：男 可选：男、女</t>
         </r>
       </text>
     </comment>
@@ -388,7 +389,7 @@
           <t xml:space="preserve">出生日期
 选填｜YYYY-MM-DD
 例：2026-10-01
-档案选填；不套用注册必填规则，不根据年龄反推生日。</t>
+档案选填；不套用注册必填规则，不根据年龄反推生日。 例：2026-10-01</t>
         </r>
       </text>
     </comment>
@@ -396,10 +397,9 @@
       <text>
         <r>
           <t xml:space="preserve">技术等级
-选填｜无单位
+选填
 例：一级运动员
-仅填写实际已采集数据，未提供留空。
-可选值：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员</t>
+仅填写实际已采集数据，未提供留空。 例：一级运动员 可选：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员</t>
         </r>
       </text>
     </comment>
@@ -407,9 +407,9 @@
       <text>
         <r>
           <t xml:space="preserve">备注
-选填｜无单位
+选填
 例：本次实测
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：本次实测</t>
         </r>
       </text>
     </comment>
@@ -417,9 +417,9 @@
       <text>
         <r>
           <t xml:space="preserve">省份
-选填｜无单位
+选填
 例：浙江省
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：浙江省</t>
         </r>
       </text>
     </comment>
@@ -427,9 +427,9 @@
       <text>
         <r>
           <t xml:space="preserve">城市
-选填｜无单位
+选填
 例：杭州市
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：杭州市</t>
         </r>
       </text>
     </comment>
@@ -437,9 +437,9 @@
       <text>
         <r>
           <t xml:space="preserve">区县
-选填｜无单位
+选填
 例：西湖区
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：西湖区</t>
         </r>
       </text>
     </comment>
@@ -447,9 +447,9 @@
       <text>
         <r>
           <t xml:space="preserve">民族
-选填｜无单位
+选填
 例：汉族
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：汉族</t>
         </r>
       </text>
     </comment>
@@ -457,9 +457,9 @@
       <text>
         <r>
           <t xml:space="preserve">手机号
-选填｜无单位
+选填
 例：按实际号码填写
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：按实际号码填写</t>
         </r>
       </text>
     </comment>
@@ -467,10 +467,9 @@
       <text>
         <r>
           <t xml:space="preserve">血型
-选填｜无单位
+选填
 例：A
-仅填写实际已采集数据，未提供留空。
-可选值：A、B、AB、O</t>
+仅填写实际已采集数据，未提供留空。 例：A 可选：A、B、AB、O</t>
         </r>
       </text>
     </comment>
@@ -478,9 +477,9 @@
       <text>
         <r>
           <t xml:space="preserve">紧急联系人
-选填｜无单位
+选填
 例：李某
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：李某</t>
         </r>
       </text>
     </comment>
@@ -488,9 +487,9 @@
       <text>
         <r>
           <t xml:space="preserve">紧急电话
-选填｜无单位
+选填
 例：按实际号码填写
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：按实际号码填写</t>
         </r>
       </text>
     </comment>
@@ -498,9 +497,9 @@
       <text>
         <r>
           <t xml:space="preserve">学历
-选填｜无单位
+选填
 例：本科
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：本科</t>
         </r>
       </text>
     </comment>
@@ -508,9 +507,9 @@
       <text>
         <r>
           <t xml:space="preserve">位置号位
-选填｜无单位
+选填
 例：1号位
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：1号位</t>
         </r>
       </text>
     </comment>
@@ -518,9 +517,9 @@
       <text>
         <r>
           <t xml:space="preserve">身体状态
-选填｜无单位
+选填
 例：健康
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：健康</t>
         </r>
       </text>
     </comment>
@@ -528,9 +527,9 @@
       <text>
         <r>
           <t xml:space="preserve">最好成绩
-选填｜无单位
+选填
 例：原始成绩及单位
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：原始成绩及单位</t>
         </r>
       </text>
     </comment>
@@ -538,9 +537,9 @@
       <text>
         <r>
           <t xml:space="preserve">籍贯
-选填｜无单位
+选填
 例：浙江杭州
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：浙江杭州</t>
         </r>
       </text>
     </comment>
@@ -548,9 +547,9 @@
       <text>
         <r>
           <t xml:space="preserve">家庭住址
-选填｜无单位
+选填
 例：实际联系地址
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：实际联系地址</t>
         </r>
       </text>
     </comment>
@@ -558,9 +557,9 @@
       <text>
         <r>
           <t xml:space="preserve">训练状态
-选填｜无单位
+选填
 例：在训
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：在训</t>
         </r>
       </text>
     </comment>
@@ -570,7 +569,7 @@
           <t xml:space="preserve">开始运动日期
 选填｜YYYY-MM-DD
 例：2026-10-01
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：2026-10-01</t>
         </r>
       </text>
     </comment>
@@ -578,9 +577,9 @@
       <text>
         <r>
           <t xml:space="preserve">训练场地
-选填｜无单位
+选填
 例：训练中心
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：训练中心</t>
         </r>
       </text>
     </comment>
@@ -588,9 +587,9 @@
       <text>
         <r>
           <t xml:space="preserve">备战赛事
-选填｜无单位
+选填
 例：实际赛事名称
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：实际赛事名称</t>
         </r>
       </text>
     </comment>
@@ -598,9 +597,9 @@
       <text>
         <r>
           <t xml:space="preserve">备战阶段
-选填｜无单位
+选填
 例：基础期
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：基础期</t>
         </r>
       </text>
     </comment>
@@ -608,9 +607,9 @@
       <text>
         <r>
           <t xml:space="preserve">集训时间
-选填｜无单位
+选填
 例：2026-10-01至2026-10-15
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：2026-10-01至2026-10-15</t>
         </r>
       </text>
     </comment>
@@ -618,9 +617,9 @@
       <text>
         <r>
           <t xml:space="preserve">输送地
-选填｜无单位
+选填
 例：杭州
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：杭州</t>
         </r>
       </text>
     </comment>
@@ -628,9 +627,9 @@
       <text>
         <r>
           <t xml:space="preserve">输送单位
-选填｜无单位
+选填
 例：实际单位名称
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：实际单位名称</t>
         </r>
       </text>
     </comment>
@@ -638,9 +637,9 @@
       <text>
         <r>
           <t xml:space="preserve">输送教练
-选填｜无单位
+选填
 例：王某
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：王某</t>
         </r>
       </text>
     </comment>
@@ -648,9 +647,9 @@
       <text>
         <r>
           <t xml:space="preserve">优势项
-选填｜无单位
+选填
 例：专项耐力
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：专项耐力</t>
         </r>
       </text>
     </comment>
@@ -668,9 +667,9 @@
       <text>
         <r>
           <t xml:space="preserve">系统运动员编号
-系统预填｜无单位
+系统预填
 例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。</t>
+已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
         </r>
       </text>
     </comment>
@@ -678,9 +677,9 @@
       <text>
         <r>
           <t xml:space="preserve">姓名
-条件必填｜无单位
+条件必填：没有系统编号，或新建人员时填写
 例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。</t>
+无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
         </r>
       </text>
     </comment>
@@ -688,9 +687,9 @@
       <text>
         <r>
           <t xml:space="preserve">测量日期
-条件必填｜YYYY-MM-DD
+条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
 例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。</t>
+本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
         </r>
       </text>
     </comment>
@@ -700,7 +699,7 @@
           <t xml:space="preserve">体重kg
 选填｜kg
 例：75
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：75</t>
         </r>
       </text>
     </comment>
@@ -710,7 +709,7 @@
           <t xml:space="preserve">身高cm
 选填｜cm
 例：180
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：180</t>
         </r>
       </text>
     </comment>
@@ -720,7 +719,7 @@
           <t xml:space="preserve">臂展cm
 选填｜cm
 例：185
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：185</t>
         </r>
       </text>
     </comment>
@@ -730,7 +729,7 @@
           <t xml:space="preserve">体脂率%
 选填｜%
 例：15
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：15</t>
         </r>
       </text>
     </comment>
@@ -740,7 +739,7 @@
           <t xml:space="preserve">骨骼肌kg
 选填｜kg
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -750,7 +749,7 @@
           <t xml:space="preserve">肌肉量kg
 选填｜kg
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -760,7 +759,7 @@
           <t xml:space="preserve">上肢肌肉kg
 选填｜kg
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -770,7 +769,7 @@
           <t xml:space="preserve">下肢肌肉kg
 选填｜kg
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -780,7 +779,7 @@
           <t xml:space="preserve">躯干肌肉kg
 选填｜kg
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -790,7 +789,7 @@
           <t xml:space="preserve">皮下脂肪mm
 选填｜mm
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -800,7 +799,7 @@
           <t xml:space="preserve">肱三头肌皮褶mm
 选填｜mm
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -810,7 +809,7 @@
           <t xml:space="preserve">腹部皮褶mm
 选填｜mm
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -820,7 +819,7 @@
           <t xml:space="preserve">大腿皮褶mm
 选填｜mm
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -830,7 +829,7 @@
           <t xml:space="preserve">小腿皮褶mm
 选填｜mm
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -838,9 +837,9 @@
       <text>
         <r>
           <t xml:space="preserve">内脏脂肪等级
-选填｜无单位
+选填
 例：5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：5</t>
         </r>
       </text>
     </comment>
@@ -850,7 +849,7 @@
           <t xml:space="preserve">基础代谢kcal
 选填｜kcal
 例：1800
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：1800</t>
         </r>
       </text>
     </comment>
@@ -860,7 +859,7 @@
           <t xml:space="preserve">总水分kg
 选填｜kg
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -868,9 +867,9 @@
       <text>
         <r>
           <t xml:space="preserve">细胞外水比
-选填｜无单位
+选填
 例：0.38
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：0.38</t>
         </r>
       </text>
     </comment>
@@ -880,7 +879,7 @@
           <t xml:space="preserve">相位角°
 选填｜°
 例：6
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：6</t>
         </r>
       </text>
     </comment>
@@ -890,7 +889,7 @@
           <t xml:space="preserve">内脏脂肪面积cm²
 选填｜cm²
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -900,7 +899,7 @@
           <t xml:space="preserve">左上肢瘦体重kg
 选填｜kg
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -910,7 +909,7 @@
           <t xml:space="preserve">右上肢瘦体重kg
 选填｜kg
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -920,7 +919,7 @@
           <t xml:space="preserve">躯干瘦体重kg
 选填｜kg
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -930,7 +929,7 @@
           <t xml:space="preserve">左下肢瘦体重kg
 选填｜kg
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -940,7 +939,7 @@
           <t xml:space="preserve">右下肢瘦体重kg
 选填｜kg
 例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。</t>
+本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -948,9 +947,9 @@
       <text>
         <r>
           <t xml:space="preserve">备注
-选填｜无单位
+选填
 例：本次实测
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：本次实测</t>
         </r>
       </text>
     </comment>
@@ -968,9 +967,9 @@
       <text>
         <r>
           <t xml:space="preserve">系统运动员编号
-系统预填｜无单位
+系统预填
 例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。</t>
+已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
         </r>
       </text>
     </comment>
@@ -978,9 +977,9 @@
       <text>
         <r>
           <t xml:space="preserve">姓名
-条件必填｜无单位
+条件必填：没有系统编号，或新建人员时填写
 例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。</t>
+无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
         </r>
       </text>
     </comment>
@@ -988,9 +987,9 @@
       <text>
         <r>
           <t xml:space="preserve">测试日期
-条件必填｜YYYY-MM-DD
+条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
 例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。</t>
+本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
         </r>
       </text>
     </comment>
@@ -1000,7 +999,7 @@
           <t xml:space="preserve">VO2Max
 选填｜ml/kg/min
 例：55
-本表至少一项实测成绩；不得以0代表未测。</t>
+本表至少一项实测成绩；不得以0代表未测。 例：55</t>
         </r>
       </text>
     </comment>
@@ -1010,7 +1009,7 @@
           <t xml:space="preserve">CMJ峰值功率W
 选填｜W
 例：3000
-本表至少一项实测成绩；不得以0代表未测。</t>
+本表至少一项实测成绩；不得以0代表未测。 例：3000</t>
         </r>
       </text>
     </comment>
@@ -1020,7 +1019,7 @@
           <t xml:space="preserve">无氧功率W/kg
 选填｜W/kg
 例：12
-本表至少一项实测成绩；不得以0代表未测。</t>
+本表至少一项实测成绩；不得以0代表未测。 例：12</t>
         </r>
       </text>
     </comment>
@@ -1030,7 +1029,7 @@
           <t xml:space="preserve">IMTP峰值力量N
 选填｜N
 例：2000
-本表至少一项实测成绩；不得以0代表未测。</t>
+本表至少一项实测成绩；不得以0代表未测。 例：2000</t>
         </r>
       </text>
     </comment>
@@ -1040,7 +1039,7 @@
           <t xml:space="preserve">不对称指数%
 选填｜%
 例：8
-本表至少一项实测成绩；不得以0代表未测。</t>
+本表至少一项实测成绩；不得以0代表未测。 例：8</t>
         </r>
       </text>
     </comment>
@@ -1048,9 +1047,10 @@
       <text>
         <r>
           <t xml:space="preserve">测试协议
-条件必填｜无单位
-例：实际设备、方法与版本
-不对称指数必须注明设备、方法或协议；其他成绩建议注明方法以便比较。</t>
+测试方法：这个结果是怎样测出来的
+条件必填：填不对称指数时必须写明测法
+例：测力台单腿跳测试（按设备报告）
+测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。</t>
         </r>
       </text>
     </comment>
@@ -1058,9 +1058,9 @@
       <text>
         <r>
           <t xml:space="preserve">备注
-选填｜无单位
+选填
 例：本次实测
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：本次实测</t>
         </r>
       </text>
     </comment>
@@ -1078,9 +1078,9 @@
       <text>
         <r>
           <t xml:space="preserve">系统运动员编号
-系统预填｜无单位
+系统预填
 例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。</t>
+已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
         </r>
       </text>
     </comment>
@@ -1088,9 +1088,9 @@
       <text>
         <r>
           <t xml:space="preserve">姓名
-条件必填｜无单位
+条件必填：没有系统编号，或新建人员时填写
 例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。</t>
+无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
         </r>
       </text>
     </comment>
@@ -1098,9 +1098,9 @@
       <text>
         <r>
           <t xml:space="preserve">测试日期
-条件必填｜YYYY-MM-DD
+条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
 例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。</t>
+本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
         </r>
       </text>
     </comment>
@@ -1110,8 +1110,7 @@
           <t xml:space="preserve">深蹲
 选填｜分
 例：2
-整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。
-可选值：0、1、2、3</t>
+整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3</t>
         </r>
       </text>
     </comment>
@@ -1121,8 +1120,7 @@
           <t xml:space="preserve">跨栏步
 选填｜分
 例：2
-整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。
-可选值：0、1、2、3</t>
+整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3</t>
         </r>
       </text>
     </comment>
@@ -1132,8 +1130,7 @@
           <t xml:space="preserve">直线弓步蹲
 选填｜分
 例：2
-整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。
-可选值：0、1、2、3</t>
+整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3</t>
         </r>
       </text>
     </comment>
@@ -1143,8 +1140,7 @@
           <t xml:space="preserve">肩部灵活性
 选填｜分
 例：2
-整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。
-可选值：0、1、2、3</t>
+整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3</t>
         </r>
       </text>
     </comment>
@@ -1154,8 +1150,7 @@
           <t xml:space="preserve">主动直腿上抬
 选填｜分
 例：2
-整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。
-可选值：0、1、2、3</t>
+整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3</t>
         </r>
       </text>
     </comment>
@@ -1165,8 +1160,7 @@
           <t xml:space="preserve">躯干稳定俯卧撑
 选填｜分
 例：2
-整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。
-可选值：0、1、2、3</t>
+整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3</t>
         </r>
       </text>
     </comment>
@@ -1176,8 +1170,7 @@
           <t xml:space="preserve">旋转稳定性
 选填｜分
 例：2
-整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。
-可选值：0、1、2、3</t>
+整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3</t>
         </r>
       </text>
     </comment>
@@ -1185,9 +1178,9 @@
       <text>
         <r>
           <t xml:space="preserve">备注
-选填｜无单位
+选填
 例：本次实测
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：本次实测</t>
         </r>
       </text>
     </comment>
@@ -1205,9 +1198,9 @@
       <text>
         <r>
           <t xml:space="preserve">系统运动员编号
-系统预填｜无单位
+系统预填
 例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。</t>
+已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
         </r>
       </text>
     </comment>
@@ -1215,9 +1208,9 @@
       <text>
         <r>
           <t xml:space="preserve">姓名
-条件必填｜无单位
+条件必填：没有系统编号，或新建人员时填写
 例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。</t>
+无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
         </r>
       </text>
     </comment>
@@ -1225,9 +1218,9 @@
       <text>
         <r>
           <t xml:space="preserve">日期
-条件必填｜YYYY-MM-DD
+条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
 例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。</t>
+本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
         </r>
       </text>
     </comment>
@@ -1235,9 +1228,9 @@
       <text>
         <r>
           <t xml:space="preserve">课次序号
-条件必填｜无单位
+条件必填：同一人同一天有多次训练时填写
 例：1
-同人同日多课必须明确所属课次；仅一课可使用默认值。</t>
+同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1</t>
         </r>
       </text>
     </comment>
@@ -1245,9 +1238,9 @@
       <text>
         <r>
           <t xml:space="preserve">时长分钟
-条件必填｜min
+条件必填：时长、距离至少填一项｜min
 例：60
-时长或距离至少一项；仅承载有效力量组次的课次可同时留空。</t>
+时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：60</t>
         </r>
       </text>
     </comment>
@@ -1255,9 +1248,9 @@
       <text>
         <r>
           <t xml:space="preserve">距离千米
-条件必填｜km
+条件必填：时长、距离至少填一项｜km
 例：12.5
-时长或距离至少一项；仅承载有效力量组次的课次可同时留空。</t>
+时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -1267,7 +1260,7 @@
           <t xml:space="preserve">开始时间
 选填｜HH:mm
 例：08:30
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：08:30</t>
         </r>
       </text>
     </comment>
@@ -1275,9 +1268,9 @@
       <text>
         <r>
           <t xml:space="preserve">训练类型
-选填｜无单位
+选填
 例：基础力量
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：基础力量</t>
         </r>
       </text>
     </comment>
@@ -1285,9 +1278,9 @@
       <text>
         <r>
           <t xml:space="preserve">训练内容
-选填｜无单位
+选填
 例：水上耐力训练
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：水上耐力训练</t>
         </r>
       </text>
     </comment>
@@ -1295,9 +1288,10 @@
       <text>
         <r>
           <t xml:space="preserve">RPE
-选填｜无单位
+主观用力程度：运动员觉得这次训练有多累
+选填
 例：6
-0—10；未采集留空。时长与RPE齐全时系统计算SRPE；缺RPE仍可导入。</t>
+主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。</t>
         </r>
       </text>
     </comment>
@@ -1305,9 +1299,9 @@
       <text>
         <r>
           <t xml:space="preserve">训练阶段
-选填｜无单位
+选填
 例：基础期
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：基础期</t>
         </r>
       </text>
     </comment>
@@ -1315,10 +1309,10 @@
       <text>
         <r>
           <t xml:space="preserve">强度区间
-选填｜无单位
+原训练记录采用的强度分区
+选填
 例：U2
-仅填写实际已采集数据，未提供留空。
-可选值：U3、U2、U1、AT、TPT、AN、ATP</t>
+原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。</t>
         </r>
       </text>
     </comment>
@@ -1326,9 +1320,10 @@
       <text>
         <r>
           <t xml:space="preserve">SRPE
+本次训练负荷：系统用时长和RPE计算
 选填｜AU
 例：360
-专业外部来源选填；日常无需手算。系统计算规则见填写说明，外部原值按既有冲突规则处理。</t>
+本次训练负荷：系统用时长和RPE计算。怎么填：日常不用填。填写训练时长和RPE后由系统计算；只有已有外部原始负荷值时才补这列。例：360。为什么：用于记录训练负荷，公式为分钟数×RPE。不知道时：没有外部原始值就留空；缺RPE时也不用自己估算。</t>
         </r>
       </text>
     </comment>
@@ -1336,9 +1331,10 @@
       <text>
         <r>
           <t xml:space="preserve">SMVL
+力量训练量：系统汇总实际次数和重量
 选填｜kg·次
 例：360
-专业外部来源选填；日常无需手算。系统计算规则见填写说明，外部原值按既有冲突规则处理。</t>
+力量训练量：系统汇总实际次数和重量。怎么填：日常不用填，逐组填写实际次数和实际重量；只有外部记录已给出整课总量时才补本列。例：360。为什么：用于汇总力量训练完成量；计划重量不能当成实际重量。不知道时：不知道整课总量就留空，不必手算，也不要填0占位。</t>
         </r>
       </text>
     </comment>
@@ -1348,7 +1344,7 @@
           <t xml:space="preserve">平均心率
 选填｜bpm
 例：140
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：140</t>
         </r>
       </text>
     </comment>
@@ -1358,7 +1354,7 @@
           <t xml:space="preserve">最大心率
 选填｜bpm
 例：175
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：175</t>
         </r>
       </text>
     </comment>
@@ -1368,7 +1364,7 @@
           <t xml:space="preserve">平均功率W
 选填｜W
 例：12.5
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -1378,7 +1374,7 @@
           <t xml:space="preserve">桨频SPM
 选填｜SPM
 例：22
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：22</t>
         </r>
       </text>
     </comment>
@@ -1396,9 +1392,9 @@
       <text>
         <r>
           <t xml:space="preserve">系统运动员编号
-系统预填｜无单位
+系统预填
 例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。</t>
+已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
         </r>
       </text>
     </comment>
@@ -1406,9 +1402,9 @@
       <text>
         <r>
           <t xml:space="preserve">姓名
-条件必填｜无单位
+条件必填：没有系统编号，或新建人员时填写
 例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。</t>
+无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
         </r>
       </text>
     </comment>
@@ -1416,9 +1412,9 @@
       <text>
         <r>
           <t xml:space="preserve">日期
-条件必填｜YYYY-MM-DD
+条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
 例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。</t>
+本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
         </r>
       </text>
     </comment>
@@ -1426,9 +1422,9 @@
       <text>
         <r>
           <t xml:space="preserve">课次序号
-条件必填｜无单位
+条件必填：同一人同一天有多次训练时填写
 例：1
-同人同日多课必须明确所属课次；仅一课可使用默认值。</t>
+同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1</t>
         </r>
       </text>
     </comment>
@@ -1436,9 +1432,9 @@
       <text>
         <r>
           <t xml:space="preserve">课次名称
-选填｜无单位
+选填
 例：上午力量
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：上午力量</t>
         </r>
       </text>
     </comment>
@@ -1446,9 +1442,9 @@
       <text>
         <r>
           <t xml:space="preserve">动作
-必填｜无单位
+必填
 例：深蹲
-填写实际记录。</t>
+填写实际记录。 例：深蹲</t>
         </r>
       </text>
     </comment>
@@ -1456,9 +1452,9 @@
       <text>
         <r>
           <t xml:space="preserve">组序
-条件必填｜无单位
+条件必填：同一动作做了多组时填写
 例：1
-同动作多组必须区分组序；仅一组可默认1。</t>
+同动作多组必须区分组序；仅一组可默认1。 例：1</t>
         </r>
       </text>
     </comment>
@@ -1468,7 +1464,7 @@
           <t xml:space="preserve">实际次数
 必填｜次
 例：6
-填写实际记录。</t>
+填写实际记录。 例：6</t>
         </r>
       </text>
     </comment>
@@ -1478,7 +1474,7 @@
           <t xml:space="preserve">实际重量kg
 必填｜kg
 例：60
-真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。</t>
+真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60</t>
         </r>
       </text>
     </comment>
@@ -1486,9 +1482,10 @@
       <text>
         <r>
           <t xml:space="preserve">RPE
-选填｜无单位
+主观用力程度：运动员觉得这次训练有多累
+选填
 例：6
-0—10；未采集留空。时长与RPE齐全时系统计算SRPE；缺RPE仍可导入。</t>
+主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。</t>
         </r>
       </text>
     </comment>
@@ -1496,10 +1493,9 @@
       <text>
         <r>
           <t xml:space="preserve">完成状态
-选填｜无单位
+选填
 例：已完成
-仅填写实际已采集数据，未提供留空。
-可选值：已完成、未完成</t>
+仅填写实际已采集数据，未提供留空。 例：已完成 可选：已完成、未完成</t>
         </r>
       </text>
     </comment>
@@ -1507,9 +1503,9 @@
       <text>
         <r>
           <t xml:space="preserve">备注
-选填｜无单位
+选填
 例：本次实测
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：本次实测</t>
         </r>
       </text>
     </comment>
@@ -1519,7 +1515,7 @@
           <t xml:space="preserve">计划次数
 选填｜次
 例：6
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：6</t>
         </r>
       </text>
     </comment>
@@ -1527,9 +1523,10 @@
       <text>
         <r>
           <t xml:space="preserve">强度百分比
+按原训练记录给出的强度百分比
 选填｜%
 例：80
-仅填写实际已采集数据，未提供留空。</t>
+按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。</t>
         </r>
       </text>
     </comment>
@@ -1537,10 +1534,9 @@
       <text>
         <r>
           <t xml:space="preserve">类别
-选填｜无单位
+选填
 例：基础力量
-仅填写实际已采集数据，未提供留空。
-可选值：基础力量、功能性体能、核心力量、专项力量、代谢训练</t>
+仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练</t>
         </r>
       </text>
     </comment>
@@ -1548,10 +1544,9 @@
       <text>
         <r>
           <t xml:space="preserve">身体部位
-选填｜无单位
+选填
 例：下肢
-仅填写实际已采集数据，未提供留空。
-可选值：上肢、下肢、核心、全身</t>
+仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身</t>
         </r>
       </text>
     </comment>
@@ -1559,9 +1554,9 @@
       <text>
         <r>
           <t xml:space="preserve">动作代码
-选填｜无单位
+选填
 例：squat
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：squat</t>
         </r>
       </text>
     </comment>
@@ -1571,7 +1566,7 @@
           <t xml:space="preserve">计划重量kg
 选填｜kg
 例：60
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：60</t>
         </r>
       </text>
     </comment>
@@ -1579,10 +1574,9 @@
       <text>
         <r>
           <t xml:space="preserve">训练环境
-选填｜无单位
+选填
 例：陆上
-仅填写实际已采集数据，未提供留空。
-可选值：水上、陆上、测功仪、泳池、场馆、其他</t>
+仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他</t>
         </r>
       </text>
     </comment>
@@ -1592,7 +1586,7 @@
           <t xml:space="preserve">组次时长分钟
 选填｜min
 例：12.5
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -1602,7 +1596,7 @@
           <t xml:space="preserve">组次距离千米
 选填｜km
 例：12.5
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -1610,10 +1604,10 @@
       <text>
         <r>
           <t xml:space="preserve">强度区间
-选填｜无单位
+原训练记录采用的强度分区
+选填
 例：U2
-仅填写实际已采集数据，未提供留空。
-可选值：U3、U2、U1、AT、TPT、AN、ATP</t>
+原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。</t>
         </r>
       </text>
     </comment>
@@ -1631,9 +1625,9 @@
       <text>
         <r>
           <t xml:space="preserve">系统运动员编号
-系统预填｜无单位
+系统预填
 例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。</t>
+已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
         </r>
       </text>
     </comment>
@@ -1641,9 +1635,9 @@
       <text>
         <r>
           <t xml:space="preserve">姓名
-条件必填｜无单位
+条件必填：没有系统编号，或新建人员时填写
 例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。</t>
+无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
         </r>
       </text>
     </comment>
@@ -1651,9 +1645,9 @@
       <text>
         <r>
           <t xml:space="preserve">日期
-条件必填｜YYYY-MM-DD
+条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
 例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。</t>
+本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
         </r>
       </text>
     </comment>
@@ -1663,7 +1657,7 @@
           <t xml:space="preserve">睡眠小时
 选填｜h
 例：8
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：8</t>
         </r>
       </text>
     </comment>
@@ -1673,7 +1667,7 @@
           <t xml:space="preserve">睡眠质量
 选填｜分
 例：4
-0—10分，越高越好；仅填本人实际报告。</t>
+0—10分，越高越好；仅填本人实际报告。 例：4</t>
         </r>
       </text>
     </comment>
@@ -1683,7 +1677,7 @@
           <t xml:space="preserve">疲劳
 选填｜分
 例：2
-0—10分，越高越严重；仅填本人实际报告。</t>
+0—10分，越高越严重；仅填本人实际报告。 例：2</t>
         </r>
       </text>
     </comment>
@@ -1693,7 +1687,7 @@
           <t xml:space="preserve">肌肉酸痛
 选填｜分
 例：2
-0—10分，越高越严重；仅填本人实际报告。</t>
+0—10分，越高越严重；仅填本人实际报告。 例：2</t>
         </r>
       </text>
     </comment>
@@ -1703,7 +1697,7 @@
           <t xml:space="preserve">情绪
 选填｜分
 例：4
-0—10分，越高越好；仅填本人实际报告。</t>
+0—10分，越高越好；仅填本人实际报告。 例：4</t>
         </r>
       </text>
     </comment>
@@ -1713,7 +1707,7 @@
           <t xml:space="preserve">晨脉
 选填｜bpm
 例：55
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：55</t>
         </r>
       </text>
     </comment>
@@ -1723,7 +1717,7 @@
           <t xml:space="preserve">体重kg
 选填｜kg
 例：75
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：75</t>
         </r>
       </text>
     </comment>
@@ -1731,10 +1725,9 @@
       <text>
         <r>
           <t xml:space="preserve">状态
-选填｜无单位
+选填
 例：normal
-normal正常、rest休息、attention关注、alert警报、missing缺失；至少一项恢复数值或状态，不能仅备注。
-可选值：normal、rest、attention、alert、missing</t>
+normal正常、rest休息、attention关注、alert警报、missing缺失；至少一项恢复数值或状态，不能仅备注。 例：normal 可选：normal、rest、attention、alert、missing</t>
         </r>
       </text>
     </comment>
@@ -1742,9 +1735,9 @@
       <text>
         <r>
           <t xml:space="preserve">备注
-选填｜无单位
+选填
 例：本次实测
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：本次实测</t>
         </r>
       </text>
     </comment>
@@ -1762,9 +1755,9 @@
       <text>
         <r>
           <t xml:space="preserve">系统运动员编号
-系统预填｜无单位
+系统预填
 例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。</t>
+已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
         </r>
       </text>
     </comment>
@@ -1772,9 +1765,9 @@
       <text>
         <r>
           <t xml:space="preserve">姓名
-条件必填｜无单位
+条件必填：没有系统编号，或新建人员时填写
 例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。</t>
+无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
         </r>
       </text>
     </comment>
@@ -1782,9 +1775,9 @@
       <text>
         <r>
           <t xml:space="preserve">发生日期
-条件必填｜YYYY-MM-DD
+条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
 例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。</t>
+本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
         </r>
       </text>
     </comment>
@@ -1792,9 +1785,9 @@
       <text>
         <r>
           <t xml:space="preserve">伤病名称
-必填｜无单位
+必填
 例：踝关节扭伤
-填写实际记录。</t>
+填写实际记录。 例：踝关节扭伤</t>
         </r>
       </text>
     </comment>
@@ -1802,9 +1795,9 @@
       <text>
         <r>
           <t xml:space="preserve">部位
-必填｜无单位
+必填
 例：踝关节
-填写实际记录。</t>
+填写实际记录。 例：踝关节</t>
         </r>
       </text>
     </comment>
@@ -1812,10 +1805,9 @@
       <text>
         <r>
           <t xml:space="preserve">侧别
-选填｜无单位
+选填
 例：左
-仅填写实际已采集数据，未提供留空。
-可选值：左、右、双侧、未指定</t>
+仅填写实际已采集数据，未提供留空。 例：左 可选：左、右、双侧、未指定</t>
         </r>
       </text>
     </comment>
@@ -1823,10 +1815,9 @@
       <text>
         <r>
           <t xml:space="preserve">状态
-选填｜无单位
+选填
 例：观察
-空白新增时沿用观察状态，不自动推断诊断。
-可选值：健康、观察、限训、康复、停训</t>
+空白新增时沿用观察状态，不自动推断诊断。 例：观察 可选：健康、观察、限训、康复、停训</t>
         </r>
       </text>
     </comment>
@@ -1836,7 +1827,7 @@
           <t xml:space="preserve">疼痛评分
 选填｜分
 例：2
-0—10分；0表示无痛，未采集必须留空。</t>
+0—10分；0表示无痛，未采集必须留空。 例：2</t>
         </r>
       </text>
     </comment>
@@ -1844,9 +1835,9 @@
       <text>
         <r>
           <t xml:space="preserve">训练限制
-选填｜无单位
+选填
 例：避免跑跳
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：避免跑跳</t>
         </r>
       </text>
     </comment>
@@ -1854,9 +1845,9 @@
       <text>
         <r>
           <t xml:space="preserve">备注
-选填｜无单位
+选填
 例：本次实测
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：本次实测</t>
         </r>
       </text>
     </comment>
@@ -1864,9 +1855,9 @@
       <text>
         <r>
           <t xml:space="preserve">康复计划
-选填｜无单位
+选填
 例：按专业人员制定的方案填写
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：按专业人员制定的方案填写</t>
         </r>
       </text>
     </comment>
@@ -1876,7 +1867,7 @@
           <t xml:space="preserve">复查日期
 选填｜YYYY-MM-DD
 例：2026-10-01
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：2026-10-01</t>
         </r>
       </text>
     </comment>
@@ -1885,7 +1876,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="283">
   <si>
     <t>竞迹训练监控系统｜简化数据导入模板</t>
   </si>
@@ -1917,10 +1908,13 @@
     <t>8. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
   </si>
   <si>
-    <t>9. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
+    <t>9. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
   </si>
   <si>
-    <t>10. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
+    <t>10. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
+  </si>
+  <si>
+    <t>11. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
   </si>
   <si>
     <t>运动员基本资料</t>
@@ -1930,27 +1924,27 @@
   </si>
   <si>
     <t xml:space="preserve">系统运动员编号
-系统预填｜无单位
+系统预填
 例：系统生成</t>
   </si>
   <si>
     <t xml:space="preserve">姓名
-条件必填｜无单位
+条件必填：没有系统编号，或新建人员时填写
 例：张某</t>
   </si>
   <si>
     <t xml:space="preserve">运动项目
-条件必填｜无单位
+条件必填：未由当前项目、队伍预填时填写
 例：赛艇</t>
   </si>
   <si>
     <t xml:space="preserve">所属队伍
-条件必填｜无单位
+条件必填：未由当前项目、队伍预填时填写
 例：一队</t>
   </si>
   <si>
     <t xml:space="preserve">性别
-选填｜无单位
+选填
 例：男</t>
   </si>
   <si>
@@ -1960,87 +1954,87 @@
   </si>
   <si>
     <t xml:space="preserve">技术等级
-选填｜无单位
+选填
 例：一级运动员</t>
   </si>
   <si>
     <t xml:space="preserve">备注
-选填｜无单位
+选填
 例：本次实测</t>
   </si>
   <si>
     <t xml:space="preserve">省份
-选填｜无单位
+选填
 例：浙江省</t>
   </si>
   <si>
     <t xml:space="preserve">城市
-选填｜无单位
+选填
 例：杭州市</t>
   </si>
   <si>
     <t xml:space="preserve">区县
-选填｜无单位
+选填
 例：西湖区</t>
   </si>
   <si>
     <t xml:space="preserve">民族
-选填｜无单位
+选填
 例：汉族</t>
   </si>
   <si>
     <t xml:space="preserve">手机号
-选填｜无单位
+选填
 例：按实际号码填写</t>
   </si>
   <si>
     <t xml:space="preserve">血型
-选填｜无单位
+选填
 例：A</t>
   </si>
   <si>
     <t xml:space="preserve">紧急联系人
-选填｜无单位
+选填
 例：李某</t>
   </si>
   <si>
     <t xml:space="preserve">紧急电话
-选填｜无单位
+选填
 例：按实际号码填写</t>
   </si>
   <si>
     <t xml:space="preserve">学历
-选填｜无单位
+选填
 例：本科</t>
   </si>
   <si>
     <t xml:space="preserve">位置号位
-选填｜无单位
+选填
 例：1号位</t>
   </si>
   <si>
     <t xml:space="preserve">身体状态
-选填｜无单位
+选填
 例：健康</t>
   </si>
   <si>
     <t xml:space="preserve">最好成绩
-选填｜无单位
+选填
 例：原始成绩及单位</t>
   </si>
   <si>
     <t xml:space="preserve">籍贯
-选填｜无单位
+选填
 例：浙江杭州</t>
   </si>
   <si>
     <t xml:space="preserve">家庭住址
-选填｜无单位
+选填
 例：实际联系地址</t>
   </si>
   <si>
     <t xml:space="preserve">训练状态
-选填｜无单位
+选填
 例：在训</t>
   </si>
   <si>
@@ -2050,42 +2044,42 @@
   </si>
   <si>
     <t xml:space="preserve">训练场地
-选填｜无单位
+选填
 例：训练中心</t>
   </si>
   <si>
     <t xml:space="preserve">备战赛事
-选填｜无单位
+选填
 例：实际赛事名称</t>
   </si>
   <si>
     <t xml:space="preserve">备战阶段
-选填｜无单位
+选填
 例：基础期</t>
   </si>
   <si>
     <t xml:space="preserve">集训时间
-选填｜无单位
+选填
 例：2026-10-01至2026-10-15</t>
   </si>
   <si>
     <t xml:space="preserve">输送地
-选填｜无单位
+选填
 例：杭州</t>
   </si>
   <si>
     <t xml:space="preserve">输送单位
-选填｜无单位
+选填
 例：实际单位名称</t>
   </si>
   <si>
     <t xml:space="preserve">输送教练
-选填｜无单位
+选填
 例：王某</t>
   </si>
   <si>
     <t xml:space="preserve">优势项
-选填｜无单位
+选填
 例：专项耐力</t>
   </si>
   <si>
@@ -2096,7 +2090,7 @@
   </si>
   <si>
     <t xml:space="preserve">测量日期
-条件必填｜YYYY-MM-DD
+条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
 例：2026-10-01</t>
   </si>
   <si>
@@ -2171,7 +2165,7 @@
   </si>
   <si>
     <t xml:space="preserve">内脏脂肪等级
-选填｜无单位
+选填
 例：5</t>
   </si>
   <si>
@@ -2186,7 +2180,7 @@
   </si>
   <si>
     <t xml:space="preserve">细胞外水比
-选填｜无单位
+选填
 例：0.38</t>
   </si>
   <si>
@@ -2232,7 +2226,7 @@
   </si>
   <si>
     <t xml:space="preserve">测试日期
-条件必填｜YYYY-MM-DD
+条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
 例：2026-10-01</t>
   </si>
   <si>
@@ -2262,8 +2256,9 @@
   </si>
   <si>
     <t xml:space="preserve">测试协议
-条件必填｜无单位
-例：实际设备、方法与版本</t>
+测试方法：这个结果是怎样测出来的
+条件必填：填不对称指数时必须写明测法
+例：测力台单腿跳测试（按设备报告）</t>
   </si>
   <si>
     <t>FMS测试</t>
@@ -2314,22 +2309,22 @@
   </si>
   <si>
     <t xml:space="preserve">日期
-条件必填｜YYYY-MM-DD
+条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
 例：2026-10-01</t>
   </si>
   <si>
     <t xml:space="preserve">课次序号
-条件必填｜无单位
+条件必填：同一人同一天有多次训练时填写
 例：1</t>
   </si>
   <si>
     <t xml:space="preserve">时长分钟
-条件必填｜min
+条件必填：时长、距离至少填一项｜min
 例：60</t>
   </si>
   <si>
     <t xml:space="preserve">距离千米
-条件必填｜km
+条件必填：时长、距离至少填一项｜km
 例：12.5</t>
   </si>
   <si>
@@ -2339,36 +2334,40 @@
   </si>
   <si>
     <t xml:space="preserve">训练类型
-选填｜无单位
+选填
 例：基础力量</t>
   </si>
   <si>
     <t xml:space="preserve">训练内容
-选填｜无单位
+选填
 例：水上耐力训练</t>
   </si>
   <si>
     <t xml:space="preserve">RPE
-选填｜无单位
+主观用力程度：运动员觉得这次训练有多累
+选填
 例：6</t>
   </si>
   <si>
     <t xml:space="preserve">训练阶段
-选填｜无单位
+选填
 例：基础期</t>
   </si>
   <si>
     <t xml:space="preserve">强度区间
-选填｜无单位
+原训练记录采用的强度分区
+选填
 例：U2</t>
   </si>
   <si>
     <t xml:space="preserve">SRPE
+本次训练负荷：系统用时长和RPE计算
 选填｜AU
 例：360</t>
   </si>
   <si>
     <t xml:space="preserve">SMVL
+力量训练量：系统汇总实际次数和重量
 选填｜kg·次
 例：360</t>
   </si>
@@ -2400,17 +2399,17 @@
   </si>
   <si>
     <t xml:space="preserve">课次名称
-选填｜无单位
+选填
 例：上午力量</t>
   </si>
   <si>
     <t xml:space="preserve">动作
-必填｜无单位
+必填
 例：深蹲</t>
   </si>
   <si>
     <t xml:space="preserve">组序
-条件必填｜无单位
+条件必填：同一动作做了多组时填写
 例：1</t>
   </si>
   <si>
@@ -2425,7 +2424,7 @@
   </si>
   <si>
     <t xml:space="preserve">完成状态
-选填｜无单位
+选填
 例：已完成</t>
   </si>
   <si>
@@ -2435,22 +2434,23 @@
   </si>
   <si>
     <t xml:space="preserve">强度百分比
+按原训练记录给出的强度百分比
 选填｜%
 例：80</t>
   </si>
   <si>
     <t xml:space="preserve">类别
-选填｜无单位
+选填
 例：基础力量</t>
   </si>
   <si>
     <t xml:space="preserve">身体部位
-选填｜无单位
+选填
 例：下肢</t>
   </si>
   <si>
     <t xml:space="preserve">动作代码
-选填｜无单位
+选填
 例：squat</t>
   </si>
   <si>
@@ -2460,7 +2460,7 @@
   </si>
   <si>
     <t xml:space="preserve">训练环境
-选填｜无单位
+选填
 例：陆上</t>
   </si>
   <si>
@@ -2511,7 +2511,7 @@
   </si>
   <si>
     <t xml:space="preserve">状态
-选填｜无单位
+选填
 例：normal</t>
   </si>
   <si>
@@ -2522,27 +2522,27 @@
   </si>
   <si>
     <t xml:space="preserve">发生日期
-条件必填｜YYYY-MM-DD
+条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
 例：2026-10-01</t>
   </si>
   <si>
     <t xml:space="preserve">伤病名称
-必填｜无单位
+必填
 例：踝关节扭伤</t>
   </si>
   <si>
     <t xml:space="preserve">部位
-必填｜无单位
+必填
 例：踝关节</t>
   </si>
   <si>
     <t xml:space="preserve">侧别
-选填｜无单位
+选填
 例：左</t>
   </si>
   <si>
     <t xml:space="preserve">状态
-选填｜无单位
+选填
 例：观察</t>
   </si>
   <si>
@@ -2552,12 +2552,12 @@
   </si>
   <si>
     <t xml:space="preserve">训练限制
-选填｜无单位
+选填
 例：避免跑跳</t>
   </si>
   <si>
     <t xml:space="preserve">康复计划
-选填｜无单位
+选填
 例：按专业人员制定的方案填写</t>
   </si>
   <si>
@@ -2573,33 +2573,34 @@
   </si>
   <si>
     <t xml:space="preserve">评估日期
-条件必填｜YYYY-MM-DD
+条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
 例：2026-10-01</t>
   </si>
   <si>
     <t xml:space="preserve">总分
-条件必填｜分
-例：按既有评价协议原值填写</t>
+条件必填：填写专项耐力等竞技评价时提供真实总分｜分
+例：80（须按实际评分表打分）</t>
   </si>
   <si>
     <t xml:space="preserve">等级
-选填｜无单位
+选填
 例：建设</t>
   </si>
   <si>
     <t xml:space="preserve">一般耐力评分
 选填｜分
-例：按既有协议填写</t>
+例：80（须按实际评分表打分）</t>
   </si>
   <si>
     <t xml:space="preserve">核心力量评分
 选填｜分
-例：按既有协议填写</t>
+例：75（须按实际评分表打分）</t>
   </si>
   <si>
     <t xml:space="preserve">评估协议
-条件必填｜无单位
-例：本队已采用的评分协议名称及版本</t>
+评分标准：这些分数按哪张评分表打的
+条件必填：填一般耐力/核心力量评分时填写
+例：队内核心力量评分表（2026版）</t>
   </si>
   <si>
     <t xml:space="preserve">专项耐力
@@ -2639,12 +2640,13 @@
   </si>
   <si>
     <t xml:space="preserve">指标代码
-必填｜无单位
+测试项目编号：告诉系统测的是哪一项
+必填
 例：vertical_jump_cm</t>
   </si>
   <si>
     <t xml:space="preserve">指标名称
-选填｜无单位
+选填
 例：纵跳</t>
   </si>
   <si>
@@ -2654,22 +2656,23 @@
   </si>
   <si>
     <t xml:space="preserve">单位
-条件必填｜指标字典单位
+条件必填：系统不能从指标字典确定单位时填写｜指标字典单位
 例：cm</t>
   </si>
   <si>
     <t xml:space="preserve">测试类型
-选填｜无单位
+选填
 例：专项测试</t>
   </si>
   <si>
     <t xml:space="preserve">协议
-选填｜无单位
-例：实际测试方法及版本</t>
+测试方法：记录这个数值的实际测法
+选填
+例：纵跳摸高，测3次取最好成绩</t>
   </si>
   <si>
     <t xml:space="preserve">侧别
-条件必填｜无单位
+条件必填：测左侧、右侧或双侧时填写
 例：左</t>
   </si>
   <si>
@@ -3455,7 +3458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -3518,6 +3521,11 @@
     <row r="12" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3545,7 +3553,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3564,7 +3572,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3581,51 +3589,51 @@
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
     </row>
-    <row r="3" ht="82" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" ht="119" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -5634,59 +5642,95 @@
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
   </mergeCells>
-  <dataValidations count="18">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜分" prompt="新增竞技状态记录需有依据的原始总分；单项一般耐力/核心力量评分可单独填写并注明评估协议，不能编造总分。 例：按既有评价协议原值填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜分" prompt="新增竞技状态记录需有依据的原始总分；单项一般耐力/核心力量评分可单独填写并注明评估协议，不能编造总分。 例：按既有评价协议原值填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：建设" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：建设" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜分" prompt="仅填写实际已采集数据，未提供留空。 例：按既有协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜分" prompt="仅填写实际已采集数据，未提供留空。 例：按既有协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="一般耐力和核心力量评分必须填写协议；禁止虚构总分或维度得分。 例：本队已采用的评分协议名称及版本" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="一般耐力和核心力量评分必须填写协议；禁止虚构总分或维度得分。 例：本队已采用的评分协议名称及版本" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜分" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜分" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
+  <dataValidations count="30">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总分：怎么填" prompt="新增竞技状态记录需有依据的原始总分；单项一般耐力/核心力量评分可单独填写并注明评估协议，不能编造总分。 例：80（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总分：怎么填" prompt="新增竞技状态记录需有依据的原始总分；单项一般耐力/核心力量评分可单独填写并注明评估协议，不能编造总分。 例：80（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：建设" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：建设" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="一般耐力评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：80（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="一般耐力评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：80（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="核心力量评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="核心力量评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估协议：怎么填" prompt="评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估协议：怎么填" prompt="评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="专项耐力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="专项耐力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="力量爆发：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="力量爆发：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="技术效率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="技术效率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="负荷适应：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="负荷适应：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="恢复能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="恢复能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="比赛能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="比赛能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -5716,7 +5760,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5733,7 +5777,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -5748,45 +5792,45 @@
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
     </row>
-    <row r="3" ht="82" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" ht="104" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -7796,82 +7840,82 @@
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="26">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜无单位" prompt="按项目指标字典填写；一项指标一行。 例：vertical_jump_cm" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜无单位" prompt="按项目指标字典填写；一项指标一行。 例：vertical_jump_cm" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：纵跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：纵跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜指标字典单位" prompt="按项目指标字典填写；一项指标一行。 例：45" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜指标字典单位" prompt="按项目指标字典填写；一项指标一行。 例：45" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜指标字典单位" prompt="可由已知指标字典确定；不能确定时必须补充，冲突不得静默换算。 例：cm" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜指标字典单位" prompt="可由已知指标字典确定；不能确定时必须补充，冲突不得静默换算。 例：cm" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：实际测试方法及版本" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：实际测试方法及版本" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="J10:J503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="指标代码：怎么填" prompt="测试项目编号：告诉系统测的是哪一项。怎么填：从数据字典复制对应代码；例如纵跳用vertical_jump_cm，不用自己编编号。例：vertical_jump_cm。为什么：同一个数值可能是距离、重量或时间，需要明确对应的测试项目。不知道时：先找身体测量、体能测试等现成工作表；字典仍找不到时先确认项目，不随便套用别的代码。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="指标代码：怎么填" prompt="测试项目编号：告诉系统测的是哪一项。怎么填：从数据字典复制对应代码；例如纵跳用vertical_jump_cm，不用自己编编号。例：vertical_jump_cm。为什么：同一个数值可能是距离、重量或时间，需要明确对应的测试项目。不知道时：先找身体测量、体能测试等现成工作表；字典仍找不到时先确认项目，不随便套用别的代码。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="指标名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：纵跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="指标名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：纵跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="按项目指标字典填写；一项指标一行。 例：45" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="按项目指标字典填写；一项指标一行。 例：45" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="单位：怎么填" prompt="可由已知指标字典确定；不能确定时必须补充，冲突不得静默换算。 例：cm" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="单位：怎么填" prompt="可由已知指标字典确定；不能确定时必须补充，冲突不得静默换算。 例：cm" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="J10:J503">
       <formula1>"左,右,双侧,中央"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="J4:J503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="J4:J503">
       <formula1>"左,右,双侧,中央"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜min" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜min" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜与实测值同单位" prompt="仅填写实际已采集数据，未提供留空。 例：50" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜与实测值同单位" prompt="仅填写实际已采集数据，未提供留空。 例：50" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="目标值：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：50" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="目标值：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：50" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -7892,767 +7936,767 @@
   <sheetData>
     <row r="1" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" t="s">
         <v>181</v>
-      </c>
-      <c r="B3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" t="s">
         <v>202</v>
       </c>
-      <c r="B12" t="s">
-        <v>203</v>
-      </c>
-      <c r="C12" t="s">
-        <v>201</v>
-      </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C20" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C21" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E21" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E23" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B26" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E26" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C27" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E27" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>241</v>
+      </c>
+      <c r="B28" t="s">
+        <v>242</v>
+      </c>
+      <c r="C28" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" t="s">
         <v>240</v>
-      </c>
-      <c r="B28" t="s">
-        <v>241</v>
-      </c>
-      <c r="C28" t="s">
-        <v>188</v>
-      </c>
-      <c r="D28" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C29" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C30" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E30" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B31" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C31" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E31" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B32" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>256</v>
+      </c>
+      <c r="B33" t="s">
+        <v>257</v>
+      </c>
+      <c r="C33" t="s">
+        <v>254</v>
+      </c>
+      <c r="D33" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" t="s">
         <v>255</v>
-      </c>
-      <c r="B33" t="s">
-        <v>256</v>
-      </c>
-      <c r="C33" t="s">
-        <v>253</v>
-      </c>
-      <c r="D33" t="s">
-        <v>83</v>
-      </c>
-      <c r="E33" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B34" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C34" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D34" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E34" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B35" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C35" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E35" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B36" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C36" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E36" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B37" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C37" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E37" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B38" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C38" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E38" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C39" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D39" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E39" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>271</v>
+      </c>
+      <c r="B40" t="s">
+        <v>272</v>
+      </c>
+      <c r="C40" t="s">
+        <v>254</v>
+      </c>
+      <c r="D40" t="s">
+        <v>148</v>
+      </c>
+      <c r="E40" t="s">
         <v>270</v>
-      </c>
-      <c r="B40" t="s">
-        <v>271</v>
-      </c>
-      <c r="C40" t="s">
-        <v>253</v>
-      </c>
-      <c r="D40" t="s">
-        <v>147</v>
-      </c>
-      <c r="E40" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B41" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D41" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E41" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>275</v>
+      </c>
+      <c r="B42" t="s">
+        <v>276</v>
+      </c>
+      <c r="C42" t="s">
+        <v>186</v>
+      </c>
+      <c r="D42" t="s">
+        <v>162</v>
+      </c>
+      <c r="E42" t="s">
         <v>274</v>
-      </c>
-      <c r="B42" t="s">
-        <v>275</v>
-      </c>
-      <c r="C42" t="s">
-        <v>185</v>
-      </c>
-      <c r="D42" t="s">
-        <v>161</v>
-      </c>
-      <c r="E42" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B43" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C43" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D43" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E43" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B44" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C44" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D44" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E44" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C45" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D45" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E45" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -8686,7 +8730,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -8722,7 +8766,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -8758,100 +8802,100 @@
     </row>
     <row r="3" ht="82" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W3" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X3" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AB3" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AC3" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AD3" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AE3" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF3" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -12361,196 +12405,196 @@
     <mergeCell ref="A2:AF2"/>
   </mergeCells>
   <dataValidations count="64">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA10:AA503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA4:AA503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01至2026-10-15" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB10:AB503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01至2026-10-15" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB4:AB503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：杭州" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC10:AC503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：杭州" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC4:AC503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：实际单位名称" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AD10:AD503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：实际单位名称" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AD4:AD503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：王某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AE10:AE503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：王某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AE4:AE503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：专项耐力" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AF10:AF503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：专项耐力" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AF4:AF503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：赛艇" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：赛艇" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：男" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：男、女" sqref="E10:E503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA10:AA503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA4:AA503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="集训时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01至2026-10-15" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB10:AB503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="集训时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01至2026-10-15" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB4:AB503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC10:AC503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC4:AC503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送单位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际单位名称" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AD10:AD503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送单位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际单位名称" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AD4:AD503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送教练：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：王某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AE10:AE503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送教练：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：王某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AE4:AE503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="优势项：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项耐力" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AF10:AF503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="优势项：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项耐力" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AF4:AF503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="运动项目：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：赛艇" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="运动项目：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：赛艇" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="所属队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="所属队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="性别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男 可选：男、女" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：男、女" sqref="E10:E503">
       <formula1>"男,女"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：男" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：男、女" sqref="E4:E503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="性别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男 可选：男、女" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：男、女" sqref="E4:E503">
       <formula1>"男,女"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜YYYY-MM-DD" prompt="档案选填；不套用注册必填规则，不根据年龄反推生日。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜YYYY-MM-DD" prompt="档案选填；不套用注册必填规则，不根据年龄反推生日。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：一级运动员" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" sqref="G10:G503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="出生日期：怎么填" prompt="档案选填；不套用注册必填规则，不根据年龄反推生日。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="出生日期：怎么填" prompt="档案选填；不套用注册必填规则，不根据年龄反推生日。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="技术等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：一级运动员 可选：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" sqref="G10:G503">
       <formula1>"未定级,国际级运动健将,运动健将,一级运动员,二级运动员,三级运动员"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：一级运动员" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" sqref="G4:G503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="技术等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：一级运动员 可选：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" sqref="G4:G503">
       <formula1>"未定级,国际级运动健将,运动健将,一级运动员,二级运动员,三级运动员"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：浙江省" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：浙江省" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：杭州市" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：杭州市" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：西湖区" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：西湖区" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：汉族" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：汉族" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：A" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：A、B、AB、O" sqref="N10:N503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="省份：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江省" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="省份：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江省" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="城市：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州市" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="城市：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州市" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="区县：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：西湖区" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="区县：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：西湖区" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="民族：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：汉族" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="民族：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：汉族" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="手机号：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="手机号：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="血型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：A 可选：A、B、AB、O" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：A、B、AB、O" sqref="N10:N503">
       <formula1>"A,B,AB,O"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：A" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：A、B、AB、O" sqref="N4:N503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="血型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：A 可选：A、B、AB、O" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：A、B、AB、O" sqref="N4:N503">
       <formula1>"A,B,AB,O"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：李某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：李某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P10:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P4:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本科" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本科" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：1号位" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：1号位" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：健康" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S10:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：健康" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S4:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：原始成绩及单位" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：原始成绩及单位" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：浙江杭州" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：浙江杭州" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：实际联系地址" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V10:V503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：实际联系地址" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V4:V503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：在训" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W10:W503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：在训" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W4:W503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜YYYY-MM-DD" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X10:X503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜YYYY-MM-DD" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X4:X503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：训练中心" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y10:Y503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：训练中心" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y4:Y503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：实际赛事名称" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z10:Z503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：实际赛事名称" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z4:Z503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急联系人：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：李某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急联系人：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：李某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急电话：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P10:P503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急电话：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P4:P503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="学历：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本科" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="学历：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本科" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="位置号位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：1号位" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="位置号位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：1号位" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="身体状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：健康" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S10:S503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="身体状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：健康" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S4:S503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最好成绩：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：原始成绩及单位" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:T503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最好成绩：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：原始成绩及单位" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:T503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="籍贯：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江杭州" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="籍贯：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江杭州" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="家庭住址：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际联系地址" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V10:V503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="家庭住址：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际联系地址" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V4:V503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：在训" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W10:W503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：在训" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W4:W503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始运动日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X10:X503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始运动日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X4:X503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：训练中心" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y10:Y503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：训练中心" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y4:Y503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战赛事：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际赛事名称" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z10:Z503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战赛事：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际赛事名称" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z4:Z503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -12578,7 +12622,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -12611,7 +12655,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -12642,93 +12686,93 @@
       <c r="AB2" s="6"/>
       <c r="AC2" s="6"/>
     </row>
-    <row r="3" ht="82" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="89" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="W3" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X3" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AB3" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -14737,113 +14781,179 @@
     <mergeCell ref="A1:AC1"/>
     <mergeCell ref="A2:AC2"/>
   </mergeCells>
-  <dataValidations count="36">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA10:AB503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA4:AB503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC10:AC503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC4:AC503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：75" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：75" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜cm" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：180" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜cm" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：180" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜cm" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：185" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜cm" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：185" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜%" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：15" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜%" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：15" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜mm" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜mm" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kcal" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：1800" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S10:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kcal" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：1800" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S4:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：0.38" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：0.38" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜°" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V10:V503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜°" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V4:V503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜cm²" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W10:W503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜cm²" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W4:W503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X10:AB503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X4:AB503">
+  <dataValidations count="58">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA10:AA503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA4:AA503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB10:AB503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB4:AB503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC10:AC503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC4:AC503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测量日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测量日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：75" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：75" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="身高cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：180" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="身高cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：180" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="臂展cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：185" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="臂展cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：185" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体脂率%：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：15" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体脂率%：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：15" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="骨骼肌kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="骨骼肌kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉量kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉量kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="上肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="上肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="下肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="下肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="皮下脂肪mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="皮下脂肪mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肱三头肌皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肱三头肌皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="腹部皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="腹部皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="大腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P10:P503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="大腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P4:P503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="小腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="小腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪等级：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪等级：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="基础代谢kcal：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：1800" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S10:S503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="基础代谢kcal：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：1800" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S4:S503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总水分kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:T503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总水分kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:T503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="细胞外水比：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：0.38" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="细胞外水比：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：0.38" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="相位角°：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V10:V503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="相位角°：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V4:V503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪面积cm²：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W10:W503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪面积cm²：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W4:W503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X10:X503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X4:X503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y10:Y503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y4:Y503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z10:Z503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z4:Z503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -14871,7 +14981,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -14885,7 +14995,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -14897,36 +15007,36 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" ht="82" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" ht="119" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -16936,64 +17046,64 @@
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="20">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜ml/kg/min" prompt="本表至少一项实测成绩；不得以0代表未测。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜ml/kg/min" prompt="本表至少一项实测成绩；不得以0代表未测。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜W" prompt="本表至少一项实测成绩；不得以0代表未测。 例：3000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜W" prompt="本表至少一项实测成绩；不得以0代表未测。 例：3000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜W/kg" prompt="本表至少一项实测成绩；不得以0代表未测。 例：12" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜W/kg" prompt="本表至少一项实测成绩；不得以0代表未测。 例：12" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜N" prompt="本表至少一项实测成绩；不得以0代表未测。 例：2000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜N" prompt="本表至少一项实测成绩；不得以0代表未测。 例：2000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜%" prompt="本表至少一项实测成绩；不得以0代表未测。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜%" prompt="本表至少一项实测成绩；不得以0代表未测。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="不对称指数必须注明设备、方法或协议；其他成绩建议注明方法以便比较。 例：实际设备、方法与版本" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="不对称指数必须注明设备、方法或协议；其他成绩建议注明方法以便比较。 例：实际设备、方法与版本" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="VO2Max：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="VO2Max：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="CMJ峰值功率W：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：3000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="CMJ峰值功率W：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：3000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="无氧功率W/kg：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：12" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="无氧功率W/kg：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：12" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="IMTP峰值力量N：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：2000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="IMTP峰值力量N：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：2000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="不对称指数%：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="不对称指数%：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试协议：怎么填" prompt="测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试协议：怎么填" prompt="测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -17020,7 +17130,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -17035,7 +17145,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -17048,39 +17158,39 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" ht="82" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" ht="89" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -19089,35 +19199,71 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <dataValidations count="10">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜分" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="D10:J503">
+  <dataValidations count="22">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="深蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="D10:D503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜分" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="D4:J503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="深蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="D4:D503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="跨栏步：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="E10:E503">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="跨栏步：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="E4:E503">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="直线弓步蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="F10:F503">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="直线弓步蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="F4:F503">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="肩部灵活性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="G10:G503">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="肩部灵活性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="G4:G503">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="主动直腿上抬：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="H10:H503">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="主动直腿上抬：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="H4:H503">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="躯干稳定俯卧撑：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="I10:I503">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="躯干稳定俯卧撑：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="I4:I503">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="旋转稳定性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="J10:J503">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="旋转稳定性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="J4:J503">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -19146,7 +19292,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -19168,7 +19314,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -19188,60 +19334,60 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
     </row>
-    <row r="3" ht="82" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" ht="89" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -21251,112 +21397,112 @@
     <mergeCell ref="A2:R2"/>
   </mergeCells>
   <dataValidations count="36">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜min" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜min" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜km" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜km" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜HH:mm" prompt="仅填写实际已采集数据，未提供留空。 例：08:30" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜HH:mm" prompt="仅填写实际已采集数据，未提供留空。 例：08:30" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：水上耐力训练" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：水上耐力训练" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="0—10；未采集留空。时长与RPE齐全时系统计算SRPE；缺RPE仍可导入。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="0—10；未采集留空。时长与RPE齐全时系统计算SRPE；缺RPE仍可导入。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：U2" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="L10:L503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="时长分钟：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="时长分钟：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="距离千米：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="距离千米：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：08:30" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：08:30" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练内容：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：水上耐力训练" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练内容：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：水上耐力训练" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="L10:L503">
       <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：U2" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="L4:L503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="L4:L503">
       <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜AU" prompt="专业外部来源选填；日常无需手算。系统计算规则见填写说明，外部原值按既有冲突规则处理。 例：360" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜AU" prompt="专业外部来源选填；日常无需手算。系统计算规则见填写说明，外部原值按既有冲突规则处理。 例：360" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg·次" prompt="专业外部来源选填；日常无需手算。系统计算规则见填写说明，外部原值按既有冲突规则处理。 例：360" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg·次" prompt="专业外部来源选填；日常无需手算。系统计算规则见填写说明，外部原值按既有冲突规则处理。 例：360" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜bpm" prompt="仅填写实际已采集数据，未提供留空。 例：140" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜bpm" prompt="仅填写实际已采集数据，未提供留空。 例：140" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜bpm" prompt="仅填写实际已采集数据，未提供留空。 例：175" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P10:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜bpm" prompt="仅填写实际已采集数据，未提供留空。 例：175" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P4:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜W" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜W" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜SPM" prompt="仅填写实际已采集数据，未提供留空。 例：22" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜SPM" prompt="仅填写实际已采集数据，未提供留空。 例：22" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SRPE：怎么填" prompt="本次训练负荷：系统用时长和RPE计算。怎么填：日常不用填。填写训练时长和RPE后由系统计算；只有已有外部原始负荷值时才补这列。例：360。为什么：用于记录训练负荷，公式为分钟数×RPE。不知道时：没有外部原始值就留空；缺RPE时也不用自己估算。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SRPE：怎么填" prompt="本次训练负荷：系统用时长和RPE计算。怎么填：日常不用填。填写训练时长和RPE后由系统计算；只有已有外部原始负荷值时才补这列。例：360。为什么：用于记录训练负荷，公式为分钟数×RPE。不知道时：没有外部原始值就留空；缺RPE时也不用自己估算。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SMVL：怎么填" prompt="力量训练量：系统汇总实际次数和重量。怎么填：日常不用填，逐组填写实际次数和实际重量；只有外部记录已给出整课总量时才补本列。例：360。为什么：用于汇总力量训练完成量；计划重量不能当成实际重量。不知道时：不知道整课总量就留空，不必手算，也不要填0占位。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SMVL：怎么填" prompt="力量训练量：系统汇总实际次数和重量。怎么填：日常不用填，逐组填写实际次数和实际重量；只有外部记录已给出整课总量时才补本列。例：360。为什么：用于汇总力量训练完成量；计划重量不能当成实际重量。不知道时：不知道整课总量就留空，不必手算，也不要填0占位。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：140" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：140" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最大心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：175" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P10:P503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最大心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：175" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P4:P503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均功率W：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均功率W：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="桨频SPM：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：22" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="桨频SPM：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：22" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -21384,7 +21530,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -21410,7 +21556,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -21434,72 +21580,72 @@
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
     </row>
-    <row r="3" ht="82" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" ht="89" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -23509,136 +23655,136 @@
     <mergeCell ref="A2:V2"/>
   </mergeCells>
   <dataValidations count="44">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜无单位" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜无单位" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜次" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜次" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜kg" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜kg" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="0—10；未采集留空。时长与RPE齐全时系统计算SRPE；缺RPE仍可导入。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="0—10；未采集留空。时长与RPE齐全时系统计算SRPE；缺RPE仍可导入。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：已完成" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：已完成、未完成" sqref="K10:K503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组序：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组序：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="完成状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：已完成 可选：已完成、未完成" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：已完成、未完成" sqref="K10:K503">
       <formula1>"已完成,未完成"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：已完成" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：已完成、未完成" sqref="K4:K503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="完成状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：已完成 可选：已完成、未完成" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：已完成、未完成" sqref="K4:K503">
       <formula1>"已完成,未完成"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜次" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜次" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜%" prompt="仅填写实际已采集数据，未提供留空。 例：80" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜%" prompt="仅填写实际已采集数据，未提供留空。 例：80" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="O10:O503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度百分比：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度百分比：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="类别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="O10:O503">
       <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="O4:O503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="类别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="O4:O503">
       <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：下肢" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="P10:P503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体部位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="P10:P503">
       <formula1>"上肢,下肢,核心,全身"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：下肢" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="P4:P503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体部位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="P4:P503">
       <formula1>"上肢,下肢,核心,全身"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：squat" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：squat" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：陆上" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="S10:S503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作代码：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：squat" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作代码：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：squat" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="S10:S503">
       <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：陆上" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="S4:S503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="S4:S503">
       <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜min" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜min" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜km" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜km" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：U2" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="V10:V503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:T503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:T503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次距离千米：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次距离千米：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="V10:V503">
       <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：U2" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="V4:V503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="V4:V503">
       <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23666,7 +23812,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -23682,7 +23828,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -23696,42 +23842,42 @@
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
     </row>
-    <row r="3" ht="82" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" ht="89" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -25740,71 +25886,77 @@
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <dataValidations count="22">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜h" prompt="仅填写实际已采集数据，未提供留空。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜h" prompt="仅填写实际已采集数据，未提供留空。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜分" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜分" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜分" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜分" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜分" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜分" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜bpm" prompt="仅填写实际已采集数据，未提供留空。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜bpm" prompt="仅填写实际已采集数据，未提供留空。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="仅填写实际已采集数据，未提供留空。 例：75" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="仅填写实际已采集数据，未提供留空。 例：75" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="normal正常、rest休息、attention关注、alert警报、missing缺失；至少一项恢复数值或状态，不能仅备注。 例：normal" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：normal、rest、attention、alert、missing" sqref="K10:K503">
+  <dataValidations count="24">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠小时：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠小时：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠质量：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠质量：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疲劳：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疲劳：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉酸痛：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉酸痛：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="情绪：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="情绪：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="晨脉：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="晨脉：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="normal正常、rest休息、attention关注、alert警报、missing缺失；至少一项恢复数值或状态，不能仅备注。 例：normal 可选：normal、rest、attention、alert、missing" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：normal、rest、attention、alert、missing" sqref="K10:K503">
       <formula1>"normal,rest,attention,alert,missing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="normal正常、rest休息、attention关注、alert警报、missing缺失；至少一项恢复数值或状态，不能仅备注。 例：normal" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：normal、rest、attention、alert、missing" sqref="K4:K503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="normal正常、rest休息、attention关注、alert警报、missing缺失；至少一项恢复数值或状态，不能仅备注。 例：normal 可选：normal、rest、attention、alert、missing" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：normal、rest、attention、alert、missing" sqref="K4:K503">
       <formula1>"normal,rest,attention,alert,missing"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -25833,7 +25985,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -25849,7 +26001,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -25863,42 +26015,42 @@
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
     </row>
-    <row r="3" ht="82" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" ht="89" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -28408,76 +28560,76 @@
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <dataValidations count="24">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜YYYY-MM-DD" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜无单位" prompt="填写实际记录。 例：踝关节扭伤" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜无单位" prompt="填写实际记录。 例：踝关节扭伤" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜无单位" prompt="填写实际记录。 例：踝关节" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜无单位" prompt="填写实际记录。 例：踝关节" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：左" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、未指定" sqref="F10:F503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="发生日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="发生日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="伤病名称：怎么填" prompt="填写实际记录。 例：踝关节扭伤" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="伤病名称：怎么填" prompt="填写实际记录。 例：踝关节扭伤" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="部位：怎么填" prompt="填写实际记录。 例：踝关节" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="部位：怎么填" prompt="填写实际记录。 例：踝关节" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：左 可选：左、右、双侧、未指定" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、未指定" sqref="F10:F503">
       <formula1>"左,右,双侧,未指定"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：左" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、未指定" sqref="F4:F503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：左 可选：左、右、双侧、未指定" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、未指定" sqref="F4:F503">
       <formula1>"左,右,双侧,未指定"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="空白新增时沿用观察状态，不自动推断诊断。 例：观察" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：健康、观察、限训、康复、停训" sqref="G10:G503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="空白新增时沿用观察状态，不自动推断诊断。 例：观察 可选：健康、观察、限训、康复、停训" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：健康、观察、限训、康复、停训" sqref="G10:G503">
       <formula1>"健康,观察,限训,康复,停训"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="空白新增时沿用观察状态，不自动推断诊断。 例：观察" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：健康、观察、限训、康复、停训" sqref="G4:G503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="空白新增时沿用观察状态，不自动推断诊断。 例：观察 可选：健康、观察、限训、康复、停训" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：健康、观察、限训、康复、停训" sqref="G4:G503">
       <formula1>"健康,观察,限训,康复,停训"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜分" prompt="0—10分；0表示无痛，未采集必须留空。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜分" prompt="0—10分；0表示无痛，未采集必须留空。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：避免跑跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：避免跑跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：按专业人员制定的方案填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：按专业人员制定的方案填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜YYYY-MM-DD" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜YYYY-MM-DD" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疼痛评分：怎么填" prompt="0—10分；0表示无痛，未采集必须留空。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疼痛评分：怎么填" prompt="0—10分；0表示无痛，未采集必须留空。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练限制：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：避免跑跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练限制：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：避免跑跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="康复计划：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按专业人员制定的方案填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="康复计划：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按专业人员制定的方案填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="复查日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="复查日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/templates/竞迹统一数据导入模板.xlsx
+++ b/public/templates/竞迹统一数据导入模板.xlsx
@@ -73,6 +73,17 @@
     <comment ref="E3" authorId="0">
       <text>
         <r>
+          <t xml:space="preserve">评估协议
+评分标准：这些分数按哪张评分表打的
+条件必填：填一般耐力/核心力量评分时填写
+例：队内核心力量评分表（2026版）
+评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0">
+      <text>
+        <r>
           <t xml:space="preserve">等级
 选填
 例：建设
@@ -80,7 +91,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">一般耐力评分
@@ -90,24 +101,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">核心力量评分
 选填｜分
 例：75（须按实际评分表打分）
 仅填写实际已采集数据，未提供留空。 例：75（须按实际评分表打分）</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">评估协议
-评分标准：这些分数按哪张评分表打的
-条件必填：填一般耐力/核心力量评分时填写
-例：队内核心力量评分表（2026版）
-评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。</t>
         </r>
       </text>
     </comment>
@@ -235,16 +235,6 @@
     <comment ref="E3" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">指标名称
-选填
-例：纵跳
-仅填写实际已采集数据，未提供留空。 例：纵跳</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
           <t xml:space="preserve">数值
 必填｜指标字典单位
 例：45
@@ -252,7 +242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">单位
@@ -262,7 +252,27 @@
         </r>
       </text>
     </comment>
+    <comment ref="G3" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">侧别
+条件必填：测左侧、右侧或双侧时填写
+例：左
+侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="H3" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">指标名称
+选填
+例：纵跳
+仅填写实际已采集数据，未提供留空。 例：纵跳</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">测试类型
@@ -272,7 +282,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">协议
@@ -280,16 +290,6 @@
 选填
 例：纵跳摸高，测3次取最好成绩
 测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">侧别
-条件必填：测左侧、右侧或双侧时填写
-例：左
-侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央</t>
         </r>
       </text>
     </comment>
@@ -996,6 +996,17 @@
     <comment ref="D3" authorId="0">
       <text>
         <r>
+          <t xml:space="preserve">测试协议
+测试方法：这个结果是怎样测出来的
+条件必填：填不对称指数时必须写明测法
+例：测力台单腿跳测试（按设备报告）
+测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0">
+      <text>
+        <r>
           <t xml:space="preserve">VO2Max
 选填｜ml/kg/min
 例：55
@@ -1003,7 +1014,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">CMJ峰值功率W
@@ -1013,7 +1024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">无氧功率W/kg
@@ -1023,7 +1034,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">IMTP峰值力量N
@@ -1033,24 +1044,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">不对称指数%
 选填｜%
 例：8
 本表至少一项实测成绩；不得以0代表未测。 例：8</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">测试协议
-测试方法：这个结果是怎样测出来的
-条件必填：填不对称指数时必须写明测法
-例：测力台单腿跳测试（按设备报告）
-测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。</t>
         </r>
       </text>
     </comment>
@@ -1431,16 +1431,6 @@
     <comment ref="E3" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">课次名称
-选填
-例：上午力量
-仅填写实际已采集数据，未提供留空。 例：上午力量</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
           <t xml:space="preserve">动作
 必填
 例：深蹲
@@ -1448,7 +1438,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">组序
@@ -1458,7 +1448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">实际次数
@@ -1468,13 +1458,23 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">实际重量kg
 必填｜kg
 例：60
 真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">课次名称
+选填
+例：上午力量
+仅填写实际已采集数据，未提供留空。 例：上午力量</t>
         </r>
       </text>
     </comment>
@@ -1884,10 +1884,10 @@
     <t>jingji-import-v2</t>
   </si>
   <si>
-    <t>1. 常用列在前；专业选填列在右侧默认收起，点左上角分组级别“2”展开。不支持分组时使用取消隐藏列；不使用宏。</t>
+    <t>1. 必填项在前，选填项在后；常用选填项排在专业选填项前面，所有数据列直接显示，按需填写即可。</t>
   </si>
   <si>
-    <t>2. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。隐藏列有值仍会校验和导入。</t>
+    <t>2. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。所有已填写的数据都会校验和导入。</t>
   </si>
   <si>
     <t>3. 业务日期须在行内填写，或在上传页明确选择统一日期；新模板不静默使用今天，生日永不补填。</t>
@@ -1920,7 +1920,7 @@
     <t>运动员基本资料</t>
   </si>
   <si>
-    <t>建档需姓名、运动项目和所属队伍；编号供已有人员匹配，出生日期等资料选填。已有人员导入不调队。 专业选填列已收起，点左上角分组级别“2”展开；不支持分组时取消隐藏列。详情见列批注。</t>
+    <t>建档需姓名、运动项目和所属队伍；编号供已有人员匹配，出生日期等资料选填。已有人员导入不调队。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
   </si>
   <si>
     <t xml:space="preserve">系统运动员编号
@@ -2086,7 +2086,7 @@
     <t>身体测量</t>
   </si>
   <si>
-    <t>每人每次测量一行；身高、臂展、体重及身体成分按实测填写，不要在其它表重复填写。档案展示最近有效值。 专业选填列已收起，点左上角分组级别“2”展开；不支持分组时取消隐藏列。详情见列批注。</t>
+    <t>每人每次测量一行；身高、臂展、体重及身体成分按实测填写，不要在其它表重复填写。档案展示最近有效值。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
   </si>
   <si>
     <t xml:space="preserve">测量日期
@@ -2222,12 +2222,18 @@
     <t>体能测试</t>
   </si>
   <si>
-    <t>每人每次测试一行；只填已测成绩，并填写测试协议；不对称指数须注明测试方法。 专业选填列已收起，点左上角分组级别“2”展开；不支持分组时取消隐藏列。详情见列批注。</t>
+    <t>每人每次测试一行；只填已测成绩，并填写测试协议；不对称指数须注明测试方法。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
   </si>
   <si>
     <t xml:space="preserve">测试日期
 条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
 例：2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">测试协议
+测试方法：这个结果是怎样测出来的
+条件必填：填不对称指数时必须写明测法
+例：测力台单腿跳测试（按设备报告）</t>
   </si>
   <si>
     <t xml:space="preserve">VO2Max
@@ -2255,16 +2261,10 @@
 例：8</t>
   </si>
   <si>
-    <t xml:space="preserve">测试协议
-测试方法：这个结果是怎样测出来的
-条件必填：填不对称指数时必须写明测法
-例：测力台单腿跳测试（按设备报告）</t>
-  </si>
-  <si>
     <t>FMS测试</t>
   </si>
   <si>
-    <t>每项填写0、1、2或3，未测留空；合计由系统计算，七项未齐不视为完整总分。 专业选填列已收起，点左上角分组级别“2”展开；不支持分组时取消隐藏列。详情见列批注。</t>
+    <t>每项填写0、1、2或3，未测留空；合计由系统计算，七项未齐不视为完整总分。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
   </si>
   <si>
     <t xml:space="preserve">深蹲
@@ -2305,7 +2305,7 @@
     <t>训练课次</t>
   </si>
   <si>
-    <t>每人每课一行，时长与距离至少填写一项；仅承载已填力量组次的课次可同时留空。强度未测留空；SRPE未填时仅按已填时长×RPE计算。 专业选填列已收起，点左上角分组级别“2”展开；不支持分组时取消隐藏列。详情见列批注。</t>
+    <t>每人每课一行，时长与距离至少填写一项；仅承载已填力量组次的课次可同时留空。强度未测留空；SRPE未填时仅按已填时长×RPE计算。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
   </si>
   <si>
     <t xml:space="preserve">日期
@@ -2395,12 +2395,7 @@
     <t>力量训练组次</t>
   </si>
   <si>
-    <t>每人每动作每组一行；课次序号与训练课次表一致，旧文件缺省时仅唯一课次可自动关联。实际次数和实际重量必填；完成状态填0/1或未完成/已完成，其他字段按实填写。 专业选填列已收起，点左上角分组级别“2”展开；不支持分组时取消隐藏列。详情见列批注。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">课次名称
-选填
-例：上午力量</t>
+    <t>每人每动作每组一行；课次序号与训练课次表一致，旧文件缺省时仅唯一课次可自动关联。实际次数和实际重量必填；完成状态填0/1或未完成/已完成，其他字段按实填写。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
   </si>
   <si>
     <t xml:space="preserve">动作
@@ -2421,6 +2416,11 @@
     <t xml:space="preserve">实际重量kg
 必填｜kg
 例：60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">课次名称
+选填
+例：上午力量</t>
   </si>
   <si>
     <t xml:space="preserve">完成状态
@@ -2477,7 +2477,7 @@
     <t>每日恢复</t>
   </si>
   <si>
-    <t>每日每人一行；只填写实际采集值。每日体重不覆盖身体测量历史。 专业选填列已收起，点左上角分组级别“2”展开；不支持分组时取消隐藏列。详情见列批注。</t>
+    <t>每日每人一行；只填写实际采集值。每日体重不覆盖身体测量历史。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
   </si>
   <si>
     <t xml:space="preserve">睡眠小时
@@ -2518,7 +2518,7 @@
     <t>伤病记录</t>
   </si>
   <si>
-    <t>每次伤病一行；按实际情况填写发生日期、名称、部位及状态。 专业选填列已收起，点左上角分组级别“2”展开；不支持分组时取消隐藏列。详情见列批注。</t>
+    <t>每次伤病一行；按实际情况填写发生日期、名称、部位及状态。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
   </si>
   <si>
     <t xml:space="preserve">发生日期
@@ -2569,7 +2569,7 @@
     <t>竞技评估</t>
   </si>
   <si>
-    <t>选填：只记录有依据的人工评价；一般耐力、核心力量评分须填写评估协议，不虚构总分。 专业选填列已收起，点左上角分组级别“2”展开；不支持分组时取消隐藏列。详情见列批注。</t>
+    <t>选填：只记录有依据的人工评价；一般耐力、核心力量评分须填写评估协议，不虚构总分。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
   </si>
   <si>
     <t xml:space="preserve">评估日期
@@ -2580,6 +2580,12 @@
     <t xml:space="preserve">总分
 条件必填：填写专项耐力等竞技评价时提供真实总分｜分
 例：80（须按实际评分表打分）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">评估协议
+评分标准：这些分数按哪张评分表打的
+条件必填：填一般耐力/核心力量评分时填写
+例：队内核心力量评分表（2026版）</t>
   </si>
   <si>
     <t xml:space="preserve">等级
@@ -2595,12 +2601,6 @@
     <t xml:space="preserve">核心力量评分
 选填｜分
 例：75（须按实际评分表打分）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">评估协议
-评分标准：这些分数按哪张评分表打的
-条件必填：填一般耐力/核心力量评分时填写
-例：队内核心力量评分表（2026版）</t>
   </si>
   <si>
     <t xml:space="preserve">专项耐力
@@ -2636,18 +2636,13 @@
     <t>其他测试</t>
   </si>
   <si>
-    <t>高级选填：一项指标一行；代码和单位见数据字典；测试类型和目标值按原记录保留。常用指标优先填写对应专用表。 专业选填列已收起，点左上角分组级别“2”展开；不支持分组时取消隐藏列。详情见列批注。</t>
+    <t>高级选填：一项指标一行；代码和单位见数据字典；测试类型和目标值按原记录保留。常用指标优先填写对应专用表。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
   </si>
   <si>
     <t xml:space="preserve">指标代码
 测试项目编号：告诉系统测的是哪一项
 必填
 例：vertical_jump_cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">指标名称
-选填
-例：纵跳</t>
   </si>
   <si>
     <t xml:space="preserve">数值
@@ -2660,6 +2655,16 @@
 例：cm</t>
   </si>
   <si>
+    <t xml:space="preserve">侧别
+条件必填：测左侧、右侧或双侧时填写
+例：左</t>
+  </si>
+  <si>
+    <t xml:space="preserve">指标名称
+选填
+例：纵跳</t>
+  </si>
+  <si>
     <t xml:space="preserve">测试类型
 选填
 例：专项测试</t>
@@ -2669,11 +2674,6 @@
 测试方法：记录这个数值的实际测法
 选填
 例：纵跳摸高，测3次取最好成绩</t>
-  </si>
-  <si>
-    <t xml:space="preserve">侧别
-条件必填：测左侧、右侧或双侧时填写
-例：左</t>
   </si>
   <si>
     <t xml:space="preserve">测试时长分钟
@@ -3536,19 +3536,16 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
   <dimension ref="A1:O503"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="1" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="22" style="4" customWidth="1"/>
-    <col min="4" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="14" width="22" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
-    <col min="15" max="15" width="28" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3602,7 +3599,7 @@
       <c r="D3" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>152</v>
       </c>
       <c r="F3" s="9" t="s">
@@ -3611,7 +3608,7 @@
       <c r="G3" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I3" s="9" t="s">
@@ -5667,28 +5664,28 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总分：怎么填" prompt="新增竞技状态记录需有依据的原始总分；单项一般耐力/核心力量评分可单独填写并注明评估协议，不能编造总分。 例：80（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：建设" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：建设" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="一般耐力评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：80（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="一般耐力评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：80（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="核心力量评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="核心力量评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估协议：怎么填" prompt="评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估协议：怎么填" prompt="评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估协议：怎么填" prompt="评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估协议：怎么填" prompt="评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：建设" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：建设" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="一般耐力评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：80（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="一般耐力评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：80（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="核心力量评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="核心力量评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
       <formula1>TRUE</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="专项耐力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
@@ -5742,20 +5739,15 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
   <dimension ref="A1:M503"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="1" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="22" style="4" customWidth="1"/>
-    <col min="4" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="22" customWidth="1"/>
-    <col min="11" max="11" width="28" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
-    <col min="12" max="13" width="22" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
+    <col min="4" max="9" width="22" customWidth="1"/>
+    <col min="10" max="11" width="28" customWidth="1"/>
+    <col min="12" max="13" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -5805,10 +5797,10 @@
       <c r="D3" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="8" t="s">
         <v>166</v>
       </c>
       <c r="G3" s="8" t="s">
@@ -5820,7 +5812,7 @@
       <c r="I3" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>170</v>
       </c>
       <c r="K3" s="9" t="s">
@@ -7864,41 +7856,41 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="指标代码：怎么填" prompt="测试项目编号：告诉系统测的是哪一项。怎么填：从数据字典复制对应代码；例如纵跳用vertical_jump_cm，不用自己编编号。例：vertical_jump_cm。为什么：同一个数值可能是距离、重量或时间，需要明确对应的测试项目。不知道时：先找身体测量、体能测试等现成工作表；字典仍找不到时先确认项目，不随便套用别的代码。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="指标名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：纵跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="指标名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：纵跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="按项目指标字典填写；一项指标一行。 例：45" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="按项目指标字典填写；一项指标一行。 例：45" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="单位：怎么填" prompt="可由已知指标字典确定；不能确定时必须补充，冲突不得静默换算。 例：cm" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="单位：怎么填" prompt="可由已知指标字典确定；不能确定时必须补充，冲突不得静默换算。 例：cm" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="J10:J503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="按项目指标字典填写；一项指标一行。 例：45" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="按项目指标字典填写；一项指标一行。 例：45" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="单位：怎么填" prompt="可由已知指标字典确定；不能确定时必须补充，冲突不得静默换算。 例：cm" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="单位：怎么填" prompt="可由已知指标字典确定；不能确定时必须补充，冲突不得静默换算。 例：cm" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="G10:G503">
       <formula1>"左,右,双侧,中央"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="J4:J503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="G4:G503">
       <formula1>"左,右,双侧,中央"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="指标名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：纵跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="指标名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：纵跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
       <formula1>TRUE</formula1>
@@ -8707,11 +8699,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
   <dimension ref="A1:AF503"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="1" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -8719,13 +8708,13 @@
     <col min="6" max="6" width="22" style="4" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="12" width="22" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
-    <col min="13" max="13" width="22" style="3" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
-    <col min="14" max="15" width="22" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
-    <col min="16" max="16" width="22" style="3" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
-    <col min="17" max="23" width="22" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
-    <col min="24" max="24" width="22" style="4" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
-    <col min="25" max="32" width="22" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
+    <col min="9" max="12" width="22" customWidth="1"/>
+    <col min="13" max="13" width="22" style="3" customWidth="1"/>
+    <col min="14" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="22" style="3" customWidth="1"/>
+    <col min="17" max="23" width="22" customWidth="1"/>
+    <col min="24" max="24" width="22" style="4" customWidth="1"/>
+    <col min="25" max="32" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
@@ -12606,18 +12595,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
   <dimension ref="A1:AC503"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="1" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="22" style="4" customWidth="1"/>
-    <col min="4" max="7" width="22" customWidth="1"/>
-    <col min="8" max="28" width="22" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
-    <col min="29" max="29" width="28" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
+    <col min="4" max="28" width="22" customWidth="1"/>
+    <col min="29" max="29" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
@@ -14965,18 +14950,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
   <dimension ref="A1:J503"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="1" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="22" style="4" customWidth="1"/>
-    <col min="4" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="28" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -15017,7 +14999,7 @@
       <c r="C3" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>78</v>
       </c>
       <c r="E3" s="9" t="s">
@@ -15032,7 +15014,7 @@
       <c r="H3" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>83</v>
       </c>
       <c r="J3" s="9" t="s">
@@ -17064,40 +17046,40 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="VO2Max：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="VO2Max：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="CMJ峰值功率W：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：3000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="CMJ峰值功率W：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：3000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="无氧功率W/kg：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：12" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="无氧功率W/kg：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：12" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="IMTP峰值力量N：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：2000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="IMTP峰值力量N：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：2000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="不对称指数%：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="不对称指数%：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试协议：怎么填" prompt="测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试协议：怎么填" prompt="测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试协议：怎么填" prompt="测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试协议：怎么填" prompt="测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="VO2Max：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="VO2Max：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="CMJ峰值功率W：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：3000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="CMJ峰值功率W：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：3000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="无氧功率W/kg：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：12" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="无氧功率W/kg：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：12" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="IMTP峰值力量N：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：2000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="IMTP峰值力量N：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：2000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="不对称指数%：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="不对称指数%：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
       <formula1>TRUE</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
@@ -17115,17 +17097,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
   <dimension ref="A1:K503"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="1" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="22" style="4" customWidth="1"/>
     <col min="4" max="10" width="22" customWidth="1"/>
-    <col min="11" max="11" width="28" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -19275,19 +19254,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
   <dimension ref="A1:R503"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="1" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="22" style="4" customWidth="1"/>
     <col min="4" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="22" customWidth="1"/>
-    <col min="11" max="18" width="22" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
+    <col min="10" max="18" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -21514,18 +21489,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
   <dimension ref="A1:V503"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="1" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="22" style="4" customWidth="1"/>
     <col min="4" max="11" width="22" customWidth="1"/>
     <col min="12" max="12" width="28" customWidth="1"/>
-    <col min="13" max="22" width="22" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
+    <col min="13" max="22" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -21593,19 +21565,19 @@
       <c r="D3" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="12" t="s">
         <v>115</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="9" t="s">
         <v>117</v>
       </c>
       <c r="J3" s="9" t="s">
@@ -23679,34 +23651,34 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组序：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组序：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组序：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组序：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
       <formula1>TRUE</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
@@ -23796,18 +23768,14 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
   <dimension ref="A1:L503"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="1" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="22" style="4" customWidth="1"/>
-    <col min="4" max="8" width="22" customWidth="1"/>
-    <col min="9" max="11" width="22" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
-    <col min="12" max="12" width="28" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
+    <col min="4" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -25968,19 +25936,16 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
   <dimension ref="A1:L503"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="1" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="22" style="4" customWidth="1"/>
     <col min="4" max="9" width="22" customWidth="1"/>
     <col min="10" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="22" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
-    <col min="12" max="12" width="22" style="4" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="22" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">

--- a/public/templates/竞迹统一数据导入模板.xlsx
+++ b/public/templates/竞迹统一数据导入模板.xlsx
@@ -1876,7 +1876,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="284">
   <si>
     <t>竞迹训练监控系统｜简化数据导入模板</t>
   </si>
@@ -1884,37 +1884,40 @@
     <t>jingji-import-v2</t>
   </si>
   <si>
-    <t>1. 必填项在前，选填项在后；常用选填项排在专业选填项前面，所有数据列直接显示，按需填写即可。</t>
+    <t>1. 表头颜色：红色=必填，橙色=满足说明中的条件才必填，蓝色=选填，灰色=系统预填；具体填写要求以表头文字为准。</t>
   </si>
   <si>
-    <t>2. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。所有已填写的数据都会校验和导入。</t>
+    <t>2. 必填项在前，选填项在后；常用选填项排在专业选填项前面，所有数据列直接显示，按需填写即可。</t>
   </si>
   <si>
-    <t>3. 业务日期须在行内填写，或在上传页明确选择统一日期；新模板不静默使用今天，生日永不补填。</t>
+    <t>3. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。所有已填写的数据都会校验和导入。</t>
   </si>
   <si>
-    <t>4. 系统预填：授权范围内的人员编号、姓名、项目和队伍；不要自行编造编号，不预填测量成绩。</t>
+    <t>4. 业务日期须在行内填写，或在上传页明确选择统一日期；新模板不静默使用今天，生日永不补填。</t>
   </si>
   <si>
-    <t>5. SRPE：有效时长(min)×RPE，单位AU；缺时长或RPE保持未提供，不能根据距离推算时长。</t>
+    <t>5. 系统预填：授权范围内的人员编号、姓名、项目和队伍；不要自行编造编号，不预填测量成绩。</t>
   </si>
   <si>
-    <t>6. SMVL/力量训练量：按现有规则汇总实际次数×实际重量kg；计划数不是实际数，外部显式总量沿用既有优先策略。</t>
+    <t>6. SRPE：有效时长(min)×RPE，单位AU；缺时长或RPE保持未提供，不能根据距离推算时长。</t>
   </si>
   <si>
-    <t>7. FMS：七项齐全才生成完整21分制总分，未测不补0。专项：按有效轮次计算平均、最好及同条件排名；无可比历史显示缺失。</t>
+    <t>7. SMVL/力量训练量：按现有规则汇总实际次数×实际重量kg；计划数不是实际数，外部显式总量沿用既有优先策略。</t>
   </si>
   <si>
-    <t>8. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
+    <t>8. FMS：七项齐全才生成完整21分制总分，未测不补0。专项：按有效轮次计算平均、最好及同条件排名；无可比历史显示缺失。</t>
   </si>
   <si>
-    <t>9. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
+    <t>9. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
   </si>
   <si>
-    <t>10. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
+    <t>10. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
   </si>
   <si>
-    <t>11. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
+    <t>11. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
+  </si>
+  <si>
+    <t>12. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
   </si>
   <si>
     <t>运动员基本资料</t>
@@ -3023,7 +3026,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -3042,13 +3045,21 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF334155"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF422006"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <b/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3062,17 +3073,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF52747C"/>
+        <fgColor rgb="FFE2E8F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF345D68"/>
+        <fgColor rgb="FFF59E0B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF193A44"/>
+        <fgColor rgb="FF1D4ED8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF991B1B"/>
       </patternFill>
     </fill>
   </fills>
@@ -3088,7 +3104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3103,22 +3119,25 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3458,7 +3477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -3526,6 +3545,11 @@
     <row r="13" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3550,7 +3574,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3569,7 +3593,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3588,49 +3612,49 @@
     </row>
     <row r="3" ht="119" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>150</v>
+        <v>17</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>151</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -5752,7 +5776,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5769,7 +5793,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -5786,43 +5810,43 @@
     </row>
     <row r="3" ht="104" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="E3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>165</v>
       </c>
+      <c r="E3" s="13" t="s">
+        <v>166</v>
+      </c>
       <c r="F3" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -7926,769 +7950,769 @@
     <col min="5" max="5" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="B1" s="13" t="s">
+    <row r="1" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>177</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
         <v>182</v>
-      </c>
-      <c r="B3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" t="s">
         <v>203</v>
       </c>
-      <c r="B12" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" t="s">
-        <v>202</v>
-      </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C20" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C21" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C23" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C24" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C25" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C27" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E27" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>242</v>
+      </c>
+      <c r="B28" t="s">
+        <v>243</v>
+      </c>
+      <c r="C28" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" t="s">
         <v>241</v>
-      </c>
-      <c r="B28" t="s">
-        <v>242</v>
-      </c>
-      <c r="C28" t="s">
-        <v>189</v>
-      </c>
-      <c r="D28" t="s">
-        <v>75</v>
-      </c>
-      <c r="E28" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B29" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C29" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E29" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C30" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B31" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E31" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E32" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>257</v>
+      </c>
+      <c r="B33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C33" t="s">
+        <v>255</v>
+      </c>
+      <c r="D33" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" t="s">
         <v>256</v>
-      </c>
-      <c r="B33" t="s">
-        <v>257</v>
-      </c>
-      <c r="C33" t="s">
-        <v>254</v>
-      </c>
-      <c r="D33" t="s">
-        <v>84</v>
-      </c>
-      <c r="E33" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B34" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C34" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E34" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B35" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C35" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E35" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B36" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C36" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E36" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B37" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C37" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E37" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B38" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C38" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E38" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B39" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C39" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D39" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E39" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>272</v>
+      </c>
+      <c r="B40" t="s">
+        <v>273</v>
+      </c>
+      <c r="C40" t="s">
+        <v>255</v>
+      </c>
+      <c r="D40" t="s">
+        <v>149</v>
+      </c>
+      <c r="E40" t="s">
         <v>271</v>
-      </c>
-      <c r="B40" t="s">
-        <v>272</v>
-      </c>
-      <c r="C40" t="s">
-        <v>254</v>
-      </c>
-      <c r="D40" t="s">
-        <v>148</v>
-      </c>
-      <c r="E40" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B41" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C41" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D41" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E41" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>276</v>
+      </c>
+      <c r="B42" t="s">
+        <v>277</v>
+      </c>
+      <c r="C42" t="s">
+        <v>187</v>
+      </c>
+      <c r="D42" t="s">
+        <v>163</v>
+      </c>
+      <c r="E42" t="s">
         <v>275</v>
-      </c>
-      <c r="B42" t="s">
-        <v>276</v>
-      </c>
-      <c r="C42" t="s">
-        <v>186</v>
-      </c>
-      <c r="D42" t="s">
-        <v>162</v>
-      </c>
-      <c r="E42" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B43" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C43" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D43" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E43" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B44" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C44" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D44" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E44" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B45" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C45" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D45" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E45" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -8719,7 +8743,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -8755,7 +8779,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -8791,100 +8815,100 @@
     </row>
     <row r="3" ht="82" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="7" t="s">
         <v>27</v>
       </c>
+      <c r="M3" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="N3" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="7" t="s">
         <v>30</v>
       </c>
+      <c r="P3" s="11" t="s">
+        <v>31</v>
+      </c>
       <c r="Q3" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W3" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="X3" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AB3" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AC3" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AD3" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE3" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF3" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -12607,7 +12631,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -12640,7 +12664,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -12673,91 +12697,91 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>49</v>
+        <v>17</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>50</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="W3" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X3" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB3" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC3" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -14963,7 +14987,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -14977,7 +15001,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -14991,34 +15015,34 @@
     </row>
     <row r="3" ht="119" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>77</v>
+        <v>17</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -17109,7 +17133,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -17124,7 +17148,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -17139,37 +17163,37 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>77</v>
+        <v>17</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -19267,7 +19291,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -19289,7 +19313,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -19311,58 +19335,58 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>95</v>
+        <v>17</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -21502,7 +21526,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -21528,7 +21552,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -21554,70 +21578,70 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>95</v>
+        <v>17</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>113</v>
+        <v>97</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>114</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="G3" s="13" t="s">
         <v>116</v>
       </c>
+      <c r="H3" s="13" t="s">
+        <v>117</v>
+      </c>
       <c r="I3" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -23780,7 +23804,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -23796,7 +23820,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -23812,40 +23836,40 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>95</v>
+        <v>17</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -25950,7 +25974,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -25966,7 +25990,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -25982,40 +26006,40 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="D3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>141</v>
       </c>
+      <c r="E3" s="13" t="s">
+        <v>142</v>
+      </c>
       <c r="F3" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">

--- a/public/templates/竞迹统一数据导入模板.xlsx
+++ b/public/templates/竞迹统一数据导入模板.xlsx
@@ -19,6 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_JINGJI_IMPORT_TEMPLATE_VERSION">'填写说明'!$B$1</definedName>
+    <definedName name="_JINGJI_TEST_NAMES">'数据字典'!$A$2:$A$45</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
@@ -224,11 +225,11 @@
     <comment ref="D3" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">指标代码
-测试项目编号：告诉系统测的是哪一项
+          <t xml:space="preserve">测试项目
+本次测的项目：从中文下拉列表选择
 必填
-例：vertical_jump_cm
-测试项目编号：告诉系统测的是哪一项。怎么填：从数据字典复制对应代码；例如纵跳用vertical_jump_cm，不用自己编编号。例：vertical_jump_cm。为什么：同一个数值可能是距离、重量或时间，需要明确对应的测试项目。不知道时：先找身体测量、体能测试等现成工作表；字典仍找不到时先确认项目，不随便套用别的代码。</t>
+例：纵跳（cm）
+本次测的项目：从中文下拉列表选择。怎么填：例如测纵跳就选纵跳（cm），成绩45厘米就在数值列填45；单位由选项确定。例：纵跳（cm）。为什么：让成绩对应到正确的测试项目，系统自动处理内部编号。不知道时：先找身体测量、体能测试等现成工作表；下拉找不到时请管理员配置测试项目。</t>
         </r>
       </text>
     </comment>
@@ -238,21 +239,11 @@
           <t xml:space="preserve">数值
 必填｜指标字典单位
 例：45
-按项目指标字典填写；一项指标一行。 例：45</t>
+从下拉列表选择中文测试项目，单位随项目确定；一项测试一行，只填写实际成绩。 例：45</t>
         </r>
       </text>
     </comment>
     <comment ref="F3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">单位
-条件必填：系统不能从指标字典确定单位时填写｜指标字典单位
-例：cm
-可由已知指标字典确定；不能确定时必须补充，冲突不得静默换算。 例：cm</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">侧别
@@ -262,17 +253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">指标名称
-选填
-例：纵跳
-仅填写实际已采集数据，未提供留空。 例：纵跳</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">测试类型
@@ -282,7 +263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">协议
@@ -293,7 +274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">备注
@@ -303,7 +284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">测试时长分钟
@@ -313,7 +294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">目标值
@@ -1876,7 +1857,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="234">
   <si>
     <t>竞迹训练监控系统｜简化数据导入模板</t>
   </si>
@@ -1884,40 +1865,43 @@
     <t>jingji-import-v2</t>
   </si>
   <si>
-    <t>1. 表头颜色：红色=必填，橙色=满足说明中的条件才必填，蓝色=选填，灰色=系统预填；具体填写要求以表头文字为准。</t>
+    <t>1. 其他测试：选择中文测试项目（如纵跳（cm）），再填成绩（如45）；系统自动匹配指标和单位，无需填写代码。找不到项目时请管理员先配置，不要编造名称。</t>
   </si>
   <si>
-    <t>2. 必填项在前，选填项在后；常用选填项排在专业选填项前面，所有数据列直接显示，按需填写即可。</t>
+    <t>2. 表头颜色：红色=必填，橙色=满足说明中的条件才必填，蓝色=选填，灰色=系统预填；具体填写要求以表头文字为准。</t>
   </si>
   <si>
-    <t>3. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。所有已填写的数据都会校验和导入。</t>
+    <t>3. 必填项在前，选填项在后；常用选填项排在专业选填项前面，所有数据列直接显示，按需填写即可。</t>
   </si>
   <si>
-    <t>4. 业务日期须在行内填写，或在上传页明确选择统一日期；新模板不静默使用今天，生日永不补填。</t>
+    <t>4. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。所有已填写的数据都会校验和导入。</t>
   </si>
   <si>
-    <t>5. 系统预填：授权范围内的人员编号、姓名、项目和队伍；不要自行编造编号，不预填测量成绩。</t>
+    <t>5. 业务日期须在行内填写，或在上传页明确选择统一日期；新模板不静默使用今天，生日永不补填。</t>
   </si>
   <si>
-    <t>6. SRPE：有效时长(min)×RPE，单位AU；缺时长或RPE保持未提供，不能根据距离推算时长。</t>
+    <t>6. 系统预填：授权范围内的人员编号、姓名、项目和队伍；不要自行编造编号，不预填测量成绩。</t>
   </si>
   <si>
-    <t>7. SMVL/力量训练量：按现有规则汇总实际次数×实际重量kg；计划数不是实际数，外部显式总量沿用既有优先策略。</t>
+    <t>7. SRPE：有效时长(min)×RPE，单位AU；缺时长或RPE保持未提供，不能根据距离推算时长。</t>
   </si>
   <si>
-    <t>8. FMS：七项齐全才生成完整21分制总分，未测不补0。专项：按有效轮次计算平均、最好及同条件排名；无可比历史显示缺失。</t>
+    <t>8. SMVL/力量训练量：按现有规则汇总实际次数×实际重量kg；计划数不是实际数，外部显式总量沿用既有优先策略。</t>
   </si>
   <si>
-    <t>9. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
+    <t>9. FMS：七项齐全才生成完整21分制总分，未测不补0。专项：按有效轮次计算平均、最好及同条件排名；无可比历史显示缺失。</t>
   </si>
   <si>
-    <t>10. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
+    <t>10. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
   </si>
   <si>
-    <t>11. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
+    <t>11. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
   </si>
   <si>
-    <t>12. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
+    <t>12. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
+  </si>
+  <si>
+    <t>13. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
   </si>
   <si>
     <t>运动员基本资料</t>
@@ -2639,13 +2623,13 @@
     <t>其他测试</t>
   </si>
   <si>
-    <t>高级选填：一项指标一行；代码和单位见数据字典；测试类型和目标值按原记录保留。常用指标优先填写对应专用表。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
+    <t>选择中文测试项目，再填实测成绩；单位已在选项中，无需填写代码。一项测试一行，未测不填0。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
   </si>
   <si>
-    <t xml:space="preserve">指标代码
-测试项目编号：告诉系统测的是哪一项
+    <t xml:space="preserve">测试项目
+本次测的项目：从中文下拉列表选择
 必填
-例：vertical_jump_cm</t>
+例：纵跳（cm）</t>
   </si>
   <si>
     <t xml:space="preserve">数值
@@ -2653,19 +2637,9 @@
 例：45</t>
   </si>
   <si>
-    <t xml:space="preserve">单位
-条件必填：系统不能从指标字典确定单位时填写｜指标字典单位
-例：cm</t>
-  </si>
-  <si>
     <t xml:space="preserve">侧别
 条件必填：测左侧、右侧或双侧时填写
 例：左</t>
-  </si>
-  <si>
-    <t xml:space="preserve">指标名称
-选填
-例：纵跳</t>
   </si>
   <si>
     <t xml:space="preserve">测试类型
@@ -2689,121 +2663,70 @@
 例：50</t>
   </si>
   <si>
-    <t>指标代码</t>
-  </si>
-  <si>
-    <t>指标名称</t>
+    <t>测试项目（下拉选项）</t>
   </si>
   <si>
     <t>单位</t>
   </si>
   <si>
-    <t>填写工作表</t>
+    <t>填写说明</t>
   </si>
   <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>height_cm</t>
-  </si>
-  <si>
-    <t>身高</t>
+    <t>身高（cm）</t>
   </si>
   <si>
     <t>cm</t>
   </si>
   <si>
-    <t>实测数值，可留空；不在其它表重复填报</t>
+    <t>在其他测试中选择本项目，再填写实测成绩；不要与专用表重复填报</t>
   </si>
   <si>
-    <t>arm_span_cm</t>
+    <t>臂展（cm）</t>
   </si>
   <si>
-    <t>臂展</t>
-  </si>
-  <si>
-    <t>weight_kg</t>
-  </si>
-  <si>
-    <t>体重</t>
+    <t>体重（kg）</t>
   </si>
   <si>
     <t>kg</t>
   </si>
   <si>
-    <t>body_fat_pct</t>
-  </si>
-  <si>
-    <t>体脂率</t>
+    <t>体脂率（%）</t>
   </si>
   <si>
     <t>%</t>
   </si>
   <si>
-    <t>skeletal_muscle_kg</t>
+    <t>骨骼肌（kg）</t>
   </si>
   <si>
-    <t>骨骼肌</t>
+    <t>肌肉量（kg）</t>
   </si>
   <si>
-    <t>muscle_mass_kg</t>
+    <t>上肢肌肉（kg）</t>
   </si>
   <si>
-    <t>肌肉量</t>
+    <t>下肢肌肉（kg）</t>
   </si>
   <si>
-    <t>upper_limb_muscle_kg</t>
+    <t>躯干肌肉（kg）</t>
   </si>
   <si>
-    <t>上肢肌肉</t>
-  </si>
-  <si>
-    <t>lower_limb_muscle_kg</t>
-  </si>
-  <si>
-    <t>下肢肌肉</t>
-  </si>
-  <si>
-    <t>trunk_muscle_kg</t>
-  </si>
-  <si>
-    <t>躯干肌肉</t>
-  </si>
-  <si>
-    <t>subcutaneous_fat_mm</t>
-  </si>
-  <si>
-    <t>皮下脂肪</t>
+    <t>皮下脂肪（mm）</t>
   </si>
   <si>
     <t>mm</t>
   </si>
   <si>
-    <t>triceps_skinfold_mm</t>
+    <t>肱三头肌皮褶（mm）</t>
   </si>
   <si>
-    <t>肱三头肌皮褶</t>
+    <t>腹部皮褶（mm）</t>
   </si>
   <si>
-    <t>abdominal_skinfold_mm</t>
+    <t>大腿皮褶（mm）</t>
   </si>
   <si>
-    <t>腹部皮褶</t>
-  </si>
-  <si>
-    <t>thigh_skinfold_mm</t>
-  </si>
-  <si>
-    <t>大腿皮褶</t>
-  </si>
-  <si>
-    <t>calf_skinfold_mm</t>
-  </si>
-  <si>
-    <t>小腿皮褶</t>
-  </si>
-  <si>
-    <t>visceral_fat_level</t>
+    <t>小腿皮褶（mm）</t>
   </si>
   <si>
     <t>内脏脂肪等级</t>
@@ -2812,211 +2735,115 @@
     <t/>
   </si>
   <si>
-    <t>basal_metabolism_kcal</t>
-  </si>
-  <si>
-    <t>基础代谢</t>
+    <t>基础代谢（kcal）</t>
   </si>
   <si>
     <t>kcal</t>
   </si>
   <si>
-    <t>total_body_water_kg</t>
-  </si>
-  <si>
-    <t>总水分</t>
-  </si>
-  <si>
-    <t>ecw_tbw_ratio</t>
+    <t>总水分（kg）</t>
   </si>
   <si>
     <t>细胞外水比</t>
   </si>
   <si>
-    <t>phase_angle_deg</t>
-  </si>
-  <si>
-    <t>相位角</t>
+    <t>相位角（°）</t>
   </si>
   <si>
     <t>°</t>
   </si>
   <si>
-    <t>visceral_fat_area_cm2</t>
-  </si>
-  <si>
-    <t>内脏脂肪面积</t>
+    <t>内脏脂肪面积（cm²）</t>
   </si>
   <si>
     <t>cm²</t>
   </si>
   <si>
-    <t>left_arm_lean_kg</t>
+    <t>左上肢瘦体重（kg）</t>
   </si>
   <si>
-    <t>左上肢瘦体重</t>
+    <t>右上肢瘦体重（kg）</t>
   </si>
   <si>
-    <t>right_arm_lean_kg</t>
+    <t>躯干瘦体重（kg）</t>
   </si>
   <si>
-    <t>右上肢瘦体重</t>
+    <t>左下肢瘦体重（kg）</t>
   </si>
   <si>
-    <t>trunk_lean_kg</t>
+    <t>右下肢瘦体重（kg）</t>
   </si>
   <si>
-    <t>躯干瘦体重</t>
-  </si>
-  <si>
-    <t>left_leg_lean_kg</t>
-  </si>
-  <si>
-    <t>左下肢瘦体重</t>
-  </si>
-  <si>
-    <t>right_leg_lean_kg</t>
-  </si>
-  <si>
-    <t>右下肢瘦体重</t>
-  </si>
-  <si>
-    <t>vo2max_ml_kg_min</t>
-  </si>
-  <si>
-    <t>最大摄氧量</t>
+    <t>最大摄氧量（ml/kg/min）</t>
   </si>
   <si>
     <t>ml/kg/min</t>
   </si>
   <si>
-    <t>实测数值，注明测试协议或方法</t>
+    <t>不对称指数（%）</t>
   </si>
   <si>
-    <t>asymmetry_index_pct</t>
-  </si>
-  <si>
-    <t>不对称指数</t>
-  </si>
-  <si>
-    <t>cmj_peak_power_w</t>
-  </si>
-  <si>
-    <t>CMJ峰值功率</t>
+    <t>CMJ峰值功率（W）</t>
   </si>
   <si>
     <t>W</t>
   </si>
   <si>
-    <t>anaerobic_power_wkg</t>
-  </si>
-  <si>
-    <t>无氧功率</t>
+    <t>无氧功率（W/kg）</t>
   </si>
   <si>
     <t>W/kg</t>
   </si>
   <si>
-    <t>imtp_peak_force_n</t>
-  </si>
-  <si>
-    <t>IMTP峰值力量</t>
+    <t>IMTP峰值力量（N）</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>fms_deep_squat</t>
-  </si>
-  <si>
-    <t>深蹲</t>
+    <t>深蹲（分）</t>
   </si>
   <si>
     <t>分</t>
   </si>
   <si>
-    <t>原始得分0—3；合计由系统计算</t>
+    <t>跨栏步（分）</t>
   </si>
   <si>
-    <t>fms_hurdle_step</t>
+    <t>直线弓步蹲（分）</t>
   </si>
   <si>
-    <t>跨栏步</t>
+    <t>肩部灵活性（分）</t>
   </si>
   <si>
-    <t>fms_inline_lunge</t>
+    <t>主动直腿上抬（分）</t>
   </si>
   <si>
-    <t>直线弓步蹲</t>
+    <t>躯干稳定俯卧撑（分）</t>
   </si>
   <si>
-    <t>fms_shoulder_mobility</t>
+    <t>旋转稳定性（分）</t>
   </si>
   <si>
-    <t>肩部灵活性</t>
+    <t>一般耐力（分）</t>
   </si>
   <si>
-    <t>fms_active_straight_leg_raise</t>
+    <t>核心力量（分）</t>
   </si>
   <si>
-    <t>主动直腿上抬</t>
+    <t>深蹲（kg）</t>
   </si>
   <si>
-    <t>fms_trunk_stability_pushup</t>
+    <t>硬拉（kg）</t>
   </si>
   <si>
-    <t>躯干稳定俯卧撑</t>
+    <t>卧推（kg）</t>
   </si>
   <si>
-    <t>fms_rotary_stability</t>
+    <t>卧拉（kg）</t>
   </si>
   <si>
-    <t>旋转稳定性</t>
-  </si>
-  <si>
-    <t>general_endurance_score</t>
-  </si>
-  <si>
-    <t>一般耐力</t>
-  </si>
-  <si>
-    <t>仅在有明确评分协议时填写，不自动生成分数</t>
-  </si>
-  <si>
-    <t>core_strength_score</t>
-  </si>
-  <si>
-    <t>核心力量</t>
-  </si>
-  <si>
-    <t>squat_kg</t>
-  </si>
-  <si>
-    <t>每项一行，不与专用表重复填写</t>
-  </si>
-  <si>
-    <t>deadlift_kg</t>
-  </si>
-  <si>
-    <t>硬拉</t>
-  </si>
-  <si>
-    <t>bench_press_kg</t>
-  </si>
-  <si>
-    <t>卧推</t>
-  </si>
-  <si>
-    <t>bench_pull_kg</t>
-  </si>
-  <si>
-    <t>卧拉</t>
-  </si>
-  <si>
-    <t>vertical_jump_cm</t>
-  </si>
-  <si>
-    <t>纵跳</t>
+    <t>纵跳（cm）</t>
   </si>
 </sst>
 </file>
@@ -3477,7 +3304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -3550,6 +3377,11 @@
     <row r="14" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3574,7 +3406,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3593,7 +3425,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3612,49 +3444,49 @@
     </row>
     <row r="3" ht="119" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -5763,20 +5595,20 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M503"/>
+  <dimension ref="A1:K503"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="22" style="4" customWidth="1"/>
-    <col min="4" max="9" width="22" customWidth="1"/>
-    <col min="10" max="11" width="28" customWidth="1"/>
-    <col min="12" max="13" width="22" customWidth="1"/>
+    <col min="4" max="7" width="22" customWidth="1"/>
+    <col min="8" max="9" width="28" customWidth="1"/>
+    <col min="10" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5788,12 +5620,10 @@
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-    </row>
-    <row r="2" ht="48" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="48" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -5805,2057 +5635,2049 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-    </row>
-    <row r="3" ht="104" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" ht="104" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="G3" s="8" t="s">
         <v>168</v>
       </c>
+      <c r="G3" s="9" t="s">
+        <v>169</v>
+      </c>
       <c r="H3" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>170</v>
+        <v>24</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="M3" s="9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="C5" s="4"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="C7" s="4"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="C8" s="4"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="C9" s="4"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="C13" s="4"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="C15" s="4"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="C22" s="4"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="C23" s="4"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="C24" s="4"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="C26" s="4"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="C27" s="4"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="C28" s="4"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="C31" s="4"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="C32" s="4"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="C33" s="4"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="C34" s="4"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="C35" s="4"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="C36" s="4"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="C37" s="4"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="C38" s="4"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="C39" s="4"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="C40" s="4"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="C41" s="4"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="C42" s="4"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="C43" s="4"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="C44" s="4"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="C45" s="4"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="C46" s="4"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="C47" s="4"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="C48" s="4"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="C49" s="4"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="C50" s="4"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="C51" s="4"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="C52" s="4"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="C53" s="4"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="C54" s="4"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="C55" s="4"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="C56" s="4"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="C57" s="4"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="C58" s="4"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="C59" s="4"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="C60" s="4"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="C61" s="4"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="C62" s="4"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
       <c r="C63" s="4"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
       <c r="C64" s="4"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
       <c r="C65" s="4"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="C66" s="4"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
       <c r="C67" s="4"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="C68" s="4"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="C69" s="4"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
       <c r="C70" s="4"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
       <c r="C71" s="4"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="C72" s="4"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
       <c r="C73" s="4"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
       <c r="C74" s="4"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
       <c r="C75" s="4"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="C76" s="4"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
       <c r="C77" s="4"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
       <c r="C78" s="4"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
       <c r="C79" s="4"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
       <c r="C80" s="4"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
       <c r="C81" s="4"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
       <c r="C82" s="4"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
       <c r="C83" s="4"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
       <c r="C84" s="4"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
       <c r="C85" s="4"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
       <c r="C86" s="4"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
       <c r="C87" s="4"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
       <c r="C88" s="4"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
       <c r="C89" s="4"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
       <c r="C90" s="4"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
       <c r="C91" s="4"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
       <c r="C92" s="4"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
       <c r="C93" s="4"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="3"/>
       <c r="C94" s="4"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
       <c r="C95" s="4"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
       <c r="C96" s="4"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
       <c r="C97" s="4"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="C98" s="4"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="C99" s="4"/>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
       <c r="C100" s="4"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="3"/>
       <c r="C101" s="4"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="3"/>
       <c r="C102" s="4"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
       <c r="C103" s="4"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
       <c r="C104" s="4"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="3"/>
       <c r="C105" s="4"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="3"/>
       <c r="C106" s="4"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="3"/>
       <c r="C107" s="4"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="3"/>
       <c r="C108" s="4"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="3"/>
       <c r="C109" s="4"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="3"/>
       <c r="C110" s="4"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="3"/>
       <c r="C111" s="4"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="3"/>
       <c r="C112" s="4"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="3"/>
       <c r="C113" s="4"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="3"/>
       <c r="C114" s="4"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="3"/>
       <c r="C115" s="4"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="3"/>
       <c r="C116" s="4"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="3"/>
       <c r="C117" s="4"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="3"/>
       <c r="C118" s="4"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="3"/>
       <c r="C119" s="4"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="3"/>
       <c r="C120" s="4"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="3"/>
       <c r="C121" s="4"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="3"/>
       <c r="C122" s="4"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="3"/>
       <c r="C123" s="4"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="3"/>
       <c r="C124" s="4"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="3"/>
       <c r="C125" s="4"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="3"/>
       <c r="C126" s="4"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="3"/>
       <c r="C127" s="4"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="3"/>
       <c r="C128" s="4"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="3"/>
       <c r="C129" s="4"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="3"/>
       <c r="C130" s="4"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="3"/>
       <c r="C131" s="4"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="3"/>
       <c r="C132" s="4"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="3"/>
       <c r="C133" s="4"/>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="3"/>
       <c r="C134" s="4"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="3"/>
       <c r="C135" s="4"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="3"/>
       <c r="C136" s="4"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="3"/>
       <c r="C137" s="4"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="3"/>
       <c r="C138" s="4"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="3"/>
       <c r="C139" s="4"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="3"/>
       <c r="C140" s="4"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="3"/>
       <c r="C141" s="4"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="3"/>
       <c r="C142" s="4"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="3"/>
       <c r="C143" s="4"/>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="3"/>
       <c r="C144" s="4"/>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="3"/>
       <c r="C145" s="4"/>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="3"/>
       <c r="C146" s="4"/>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="3"/>
       <c r="C147" s="4"/>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="3"/>
       <c r="C148" s="4"/>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="3"/>
       <c r="C149" s="4"/>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="3"/>
       <c r="C150" s="4"/>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="3"/>
       <c r="C151" s="4"/>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="3"/>
       <c r="C152" s="4"/>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="3"/>
       <c r="C153" s="4"/>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="3"/>
       <c r="C154" s="4"/>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="3"/>
       <c r="C155" s="4"/>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="3"/>
       <c r="C156" s="4"/>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="3"/>
       <c r="C157" s="4"/>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="3"/>
       <c r="C158" s="4"/>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="3"/>
       <c r="C159" s="4"/>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="3"/>
       <c r="C160" s="4"/>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="3"/>
       <c r="C161" s="4"/>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="3"/>
       <c r="C162" s="4"/>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="3"/>
       <c r="C163" s="4"/>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="3"/>
       <c r="C164" s="4"/>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="3"/>
       <c r="C165" s="4"/>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="3"/>
       <c r="C166" s="4"/>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="3"/>
       <c r="C167" s="4"/>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="3"/>
       <c r="C168" s="4"/>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="3"/>
       <c r="C169" s="4"/>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="3"/>
       <c r="C170" s="4"/>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="3"/>
       <c r="C171" s="4"/>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="3"/>
       <c r="C172" s="4"/>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="3"/>
       <c r="C173" s="4"/>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="3"/>
       <c r="C174" s="4"/>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="3"/>
       <c r="C175" s="4"/>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="3"/>
       <c r="C176" s="4"/>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="3"/>
       <c r="C177" s="4"/>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="3"/>
       <c r="C178" s="4"/>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="3"/>
       <c r="C179" s="4"/>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="3"/>
       <c r="C180" s="4"/>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="3"/>
       <c r="C181" s="4"/>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="3"/>
       <c r="C182" s="4"/>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="3"/>
       <c r="C183" s="4"/>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="3"/>
       <c r="C184" s="4"/>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="3"/>
       <c r="C185" s="4"/>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="3"/>
       <c r="C186" s="4"/>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="3"/>
       <c r="C187" s="4"/>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="3"/>
       <c r="C188" s="4"/>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="3"/>
       <c r="C189" s="4"/>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="3"/>
       <c r="C190" s="4"/>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="3"/>
       <c r="C191" s="4"/>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="3"/>
       <c r="C192" s="4"/>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" s="3"/>
       <c r="C193" s="4"/>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="3"/>
       <c r="C194" s="4"/>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" s="3"/>
       <c r="C195" s="4"/>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" s="3"/>
       <c r="C196" s="4"/>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" s="3"/>
       <c r="C197" s="4"/>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" s="3"/>
       <c r="C198" s="4"/>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="3"/>
       <c r="C199" s="4"/>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="3"/>
       <c r="C200" s="4"/>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="3"/>
       <c r="C201" s="4"/>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="3"/>
       <c r="C202" s="4"/>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="3"/>
       <c r="C203" s="4"/>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="3"/>
       <c r="C204" s="4"/>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" s="3"/>
       <c r="C205" s="4"/>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="3"/>
       <c r="C206" s="4"/>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="3"/>
       <c r="C207" s="4"/>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="3"/>
       <c r="C208" s="4"/>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="3"/>
       <c r="C209" s="4"/>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" s="3"/>
       <c r="C210" s="4"/>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" s="3"/>
       <c r="C211" s="4"/>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="3"/>
       <c r="C212" s="4"/>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="3"/>
       <c r="C213" s="4"/>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="3"/>
       <c r="C214" s="4"/>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" s="3"/>
       <c r="C215" s="4"/>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" s="3"/>
       <c r="C216" s="4"/>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" s="3"/>
       <c r="C217" s="4"/>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" s="3"/>
       <c r="C218" s="4"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" s="3"/>
       <c r="C219" s="4"/>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" s="3"/>
       <c r="C220" s="4"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" s="3"/>
       <c r="C221" s="4"/>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" s="3"/>
       <c r="C222" s="4"/>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" s="3"/>
       <c r="C223" s="4"/>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" s="3"/>
       <c r="C224" s="4"/>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" s="3"/>
       <c r="C225" s="4"/>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" s="3"/>
       <c r="C226" s="4"/>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" s="3"/>
       <c r="C227" s="4"/>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" s="3"/>
       <c r="C228" s="4"/>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" s="3"/>
       <c r="C229" s="4"/>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" s="3"/>
       <c r="C230" s="4"/>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" s="3"/>
       <c r="C231" s="4"/>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" s="3"/>
       <c r="C232" s="4"/>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" s="3"/>
       <c r="C233" s="4"/>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" s="3"/>
       <c r="C234" s="4"/>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" s="3"/>
       <c r="C235" s="4"/>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" s="3"/>
       <c r="C236" s="4"/>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" s="3"/>
       <c r="C237" s="4"/>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" s="3"/>
       <c r="C238" s="4"/>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" s="3"/>
       <c r="C239" s="4"/>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" s="3"/>
       <c r="C240" s="4"/>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" s="3"/>
       <c r="C241" s="4"/>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" s="3"/>
       <c r="C242" s="4"/>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" s="3"/>
       <c r="C243" s="4"/>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" s="3"/>
       <c r="C244" s="4"/>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" s="3"/>
       <c r="C245" s="4"/>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" s="3"/>
       <c r="C246" s="4"/>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" s="3"/>
       <c r="C247" s="4"/>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" s="3"/>
       <c r="C248" s="4"/>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" s="3"/>
       <c r="C249" s="4"/>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" s="3"/>
       <c r="C250" s="4"/>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" s="3"/>
       <c r="C251" s="4"/>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" s="3"/>
       <c r="C252" s="4"/>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" s="3"/>
       <c r="C253" s="4"/>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" s="3"/>
       <c r="C254" s="4"/>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" s="3"/>
       <c r="C255" s="4"/>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" s="3"/>
       <c r="C256" s="4"/>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" s="3"/>
       <c r="C257" s="4"/>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" s="3"/>
       <c r="C258" s="4"/>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" s="3"/>
       <c r="C259" s="4"/>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" s="3"/>
       <c r="C260" s="4"/>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" s="3"/>
       <c r="C261" s="4"/>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" s="3"/>
       <c r="C262" s="4"/>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" s="3"/>
       <c r="C263" s="4"/>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" s="3"/>
       <c r="C264" s="4"/>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" s="3"/>
       <c r="C265" s="4"/>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" s="3"/>
       <c r="C266" s="4"/>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" s="3"/>
       <c r="C267" s="4"/>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" s="3"/>
       <c r="C268" s="4"/>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" s="3"/>
       <c r="C269" s="4"/>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" s="3"/>
       <c r="C270" s="4"/>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" s="3"/>
       <c r="C271" s="4"/>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" s="3"/>
       <c r="C272" s="4"/>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" s="3"/>
       <c r="C273" s="4"/>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" s="3"/>
       <c r="C274" s="4"/>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" s="3"/>
       <c r="C275" s="4"/>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" s="3"/>
       <c r="C276" s="4"/>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" s="3"/>
       <c r="C277" s="4"/>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" s="3"/>
       <c r="C278" s="4"/>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" s="3"/>
       <c r="C279" s="4"/>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" s="3"/>
       <c r="C280" s="4"/>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" s="3"/>
       <c r="C281" s="4"/>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" s="3"/>
       <c r="C282" s="4"/>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" s="3"/>
       <c r="C283" s="4"/>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" s="3"/>
       <c r="C284" s="4"/>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" s="3"/>
       <c r="C285" s="4"/>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" s="3"/>
       <c r="C286" s="4"/>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" s="3"/>
       <c r="C287" s="4"/>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" s="3"/>
       <c r="C288" s="4"/>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" s="3"/>
       <c r="C289" s="4"/>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290" s="3"/>
       <c r="C290" s="4"/>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" s="3"/>
       <c r="C291" s="4"/>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" s="3"/>
       <c r="C292" s="4"/>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" s="3"/>
       <c r="C293" s="4"/>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" s="3"/>
       <c r="C294" s="4"/>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" s="3"/>
       <c r="C295" s="4"/>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" s="3"/>
       <c r="C296" s="4"/>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" s="3"/>
       <c r="C297" s="4"/>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" s="3"/>
       <c r="C298" s="4"/>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" s="3"/>
       <c r="C299" s="4"/>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" s="3"/>
       <c r="C300" s="4"/>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" s="3"/>
       <c r="C301" s="4"/>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" s="3"/>
       <c r="C302" s="4"/>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" s="3"/>
       <c r="C303" s="4"/>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" s="3"/>
       <c r="C304" s="4"/>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" s="3"/>
       <c r="C305" s="4"/>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" s="3"/>
       <c r="C306" s="4"/>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" s="3"/>
       <c r="C307" s="4"/>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" s="3"/>
       <c r="C308" s="4"/>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" s="3"/>
       <c r="C309" s="4"/>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" s="3"/>
       <c r="C310" s="4"/>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" s="3"/>
       <c r="C311" s="4"/>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312" s="3"/>
       <c r="C312" s="4"/>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313" s="3"/>
       <c r="C313" s="4"/>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314" s="3"/>
       <c r="C314" s="4"/>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315" s="3"/>
       <c r="C315" s="4"/>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316" s="3"/>
       <c r="C316" s="4"/>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" s="3"/>
       <c r="C317" s="4"/>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318" s="3"/>
       <c r="C318" s="4"/>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319" s="3"/>
       <c r="C319" s="4"/>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" s="3"/>
       <c r="C320" s="4"/>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321" s="3"/>
       <c r="C321" s="4"/>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322" s="3"/>
       <c r="C322" s="4"/>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323" s="3"/>
       <c r="C323" s="4"/>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" s="3"/>
       <c r="C324" s="4"/>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325" s="3"/>
       <c r="C325" s="4"/>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A326" s="3"/>
       <c r="C326" s="4"/>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327" s="3"/>
       <c r="C327" s="4"/>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" s="3"/>
       <c r="C328" s="4"/>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329" s="3"/>
       <c r="C329" s="4"/>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" s="3"/>
       <c r="C330" s="4"/>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331" s="3"/>
       <c r="C331" s="4"/>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332" s="3"/>
       <c r="C332" s="4"/>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333" s="3"/>
       <c r="C333" s="4"/>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334" s="3"/>
       <c r="C334" s="4"/>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335" s="3"/>
       <c r="C335" s="4"/>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336" s="3"/>
       <c r="C336" s="4"/>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337" s="3"/>
       <c r="C337" s="4"/>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" s="3"/>
       <c r="C338" s="4"/>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" s="3"/>
       <c r="C339" s="4"/>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340" s="3"/>
       <c r="C340" s="4"/>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341" s="3"/>
       <c r="C341" s="4"/>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342" s="3"/>
       <c r="C342" s="4"/>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343" s="3"/>
       <c r="C343" s="4"/>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344" s="3"/>
       <c r="C344" s="4"/>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345" s="3"/>
       <c r="C345" s="4"/>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346" s="3"/>
       <c r="C346" s="4"/>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347" s="3"/>
       <c r="C347" s="4"/>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348" s="3"/>
       <c r="C348" s="4"/>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349" s="3"/>
       <c r="C349" s="4"/>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" s="3"/>
       <c r="C350" s="4"/>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351" s="3"/>
       <c r="C351" s="4"/>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352" s="3"/>
       <c r="C352" s="4"/>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A353" s="3"/>
       <c r="C353" s="4"/>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A354" s="3"/>
       <c r="C354" s="4"/>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A355" s="3"/>
       <c r="C355" s="4"/>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A356" s="3"/>
       <c r="C356" s="4"/>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A357" s="3"/>
       <c r="C357" s="4"/>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A358" s="3"/>
       <c r="C358" s="4"/>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A359" s="3"/>
       <c r="C359" s="4"/>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A360" s="3"/>
       <c r="C360" s="4"/>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A361" s="3"/>
       <c r="C361" s="4"/>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A362" s="3"/>
       <c r="C362" s="4"/>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A363" s="3"/>
       <c r="C363" s="4"/>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A364" s="3"/>
       <c r="C364" s="4"/>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A365" s="3"/>
       <c r="C365" s="4"/>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A366" s="3"/>
       <c r="C366" s="4"/>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A367" s="3"/>
       <c r="C367" s="4"/>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A368" s="3"/>
       <c r="C368" s="4"/>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A369" s="3"/>
       <c r="C369" s="4"/>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A370" s="3"/>
       <c r="C370" s="4"/>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A371" s="3"/>
       <c r="C371" s="4"/>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A372" s="3"/>
       <c r="C372" s="4"/>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A373" s="3"/>
       <c r="C373" s="4"/>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A374" s="3"/>
       <c r="C374" s="4"/>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A375" s="3"/>
       <c r="C375" s="4"/>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A376" s="3"/>
       <c r="C376" s="4"/>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A377" s="3"/>
       <c r="C377" s="4"/>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A378" s="3"/>
       <c r="C378" s="4"/>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379" s="3"/>
       <c r="C379" s="4"/>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A380" s="3"/>
       <c r="C380" s="4"/>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A381" s="3"/>
       <c r="C381" s="4"/>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A382" s="3"/>
       <c r="C382" s="4"/>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A383" s="3"/>
       <c r="C383" s="4"/>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A384" s="3"/>
       <c r="C384" s="4"/>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A385" s="3"/>
       <c r="C385" s="4"/>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386" s="3"/>
       <c r="C386" s="4"/>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A387" s="3"/>
       <c r="C387" s="4"/>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A388" s="3"/>
       <c r="C388" s="4"/>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A389" s="3"/>
       <c r="C389" s="4"/>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390" s="3"/>
       <c r="C390" s="4"/>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391" s="3"/>
       <c r="C391" s="4"/>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392" s="3"/>
       <c r="C392" s="4"/>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A393" s="3"/>
       <c r="C393" s="4"/>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A394" s="3"/>
       <c r="C394" s="4"/>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A395" s="3"/>
       <c r="C395" s="4"/>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A396" s="3"/>
       <c r="C396" s="4"/>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397" s="3"/>
       <c r="C397" s="4"/>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398" s="3"/>
       <c r="C398" s="4"/>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399" s="3"/>
       <c r="C399" s="4"/>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400" s="3"/>
       <c r="C400" s="4"/>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401" s="3"/>
       <c r="C401" s="4"/>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A402" s="3"/>
       <c r="C402" s="4"/>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A403" s="3"/>
       <c r="C403" s="4"/>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A404" s="3"/>
       <c r="C404" s="4"/>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A405" s="3"/>
       <c r="C405" s="4"/>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A406" s="3"/>
       <c r="C406" s="4"/>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A407" s="3"/>
       <c r="C407" s="4"/>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A408" s="3"/>
       <c r="C408" s="4"/>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A409" s="3"/>
       <c r="C409" s="4"/>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A410" s="3"/>
       <c r="C410" s="4"/>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A411" s="3"/>
       <c r="C411" s="4"/>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A412" s="3"/>
       <c r="C412" s="4"/>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A413" s="3"/>
       <c r="C413" s="4"/>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A414" s="3"/>
       <c r="C414" s="4"/>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A415" s="3"/>
       <c r="C415" s="4"/>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A416" s="3"/>
       <c r="C416" s="4"/>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A417" s="3"/>
       <c r="C417" s="4"/>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A418" s="3"/>
       <c r="C418" s="4"/>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A419" s="3"/>
       <c r="C419" s="4"/>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A420" s="3"/>
       <c r="C420" s="4"/>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A421" s="3"/>
       <c r="C421" s="4"/>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A422" s="3"/>
       <c r="C422" s="4"/>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A423" s="3"/>
       <c r="C423" s="4"/>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A424" s="3"/>
       <c r="C424" s="4"/>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A425" s="3"/>
       <c r="C425" s="4"/>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A426" s="3"/>
       <c r="C426" s="4"/>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A427" s="3"/>
       <c r="C427" s="4"/>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A428" s="3"/>
       <c r="C428" s="4"/>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A429" s="3"/>
       <c r="C429" s="4"/>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A430" s="3"/>
       <c r="C430" s="4"/>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A431" s="3"/>
       <c r="C431" s="4"/>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A432" s="3"/>
       <c r="C432" s="4"/>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A433" s="3"/>
       <c r="C433" s="4"/>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A434" s="3"/>
       <c r="C434" s="4"/>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A435" s="3"/>
       <c r="C435" s="4"/>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A436" s="3"/>
       <c r="C436" s="4"/>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A437" s="3"/>
       <c r="C437" s="4"/>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A438" s="3"/>
       <c r="C438" s="4"/>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A439" s="3"/>
       <c r="C439" s="4"/>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A440" s="3"/>
       <c r="C440" s="4"/>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A441" s="3"/>
       <c r="C441" s="4"/>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A442" s="3"/>
       <c r="C442" s="4"/>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A443" s="3"/>
       <c r="C443" s="4"/>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A444" s="3"/>
       <c r="C444" s="4"/>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A445" s="3"/>
       <c r="C445" s="4"/>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A446" s="3"/>
       <c r="C446" s="4"/>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A447" s="3"/>
       <c r="C447" s="4"/>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A448" s="3"/>
       <c r="C448" s="4"/>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A449" s="3"/>
       <c r="C449" s="4"/>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A450" s="3"/>
       <c r="C450" s="4"/>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A451" s="3"/>
       <c r="C451" s="4"/>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A452" s="3"/>
       <c r="C452" s="4"/>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A453" s="3"/>
       <c r="C453" s="4"/>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A454" s="3"/>
       <c r="C454" s="4"/>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A455" s="3"/>
       <c r="C455" s="4"/>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A456" s="3"/>
       <c r="C456" s="4"/>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A457" s="3"/>
       <c r="C457" s="4"/>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A458" s="3"/>
       <c r="C458" s="4"/>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A459" s="3"/>
       <c r="C459" s="4"/>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A460" s="3"/>
       <c r="C460" s="4"/>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A461" s="3"/>
       <c r="C461" s="4"/>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A462" s="3"/>
       <c r="C462" s="4"/>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A463" s="3"/>
       <c r="C463" s="4"/>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A464" s="3"/>
       <c r="C464" s="4"/>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A465" s="3"/>
       <c r="C465" s="4"/>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A466" s="3"/>
       <c r="C466" s="4"/>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A467" s="3"/>
       <c r="C467" s="4"/>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A468" s="3"/>
       <c r="C468" s="4"/>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A469" s="3"/>
       <c r="C469" s="4"/>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A470" s="3"/>
       <c r="C470" s="4"/>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A471" s="3"/>
       <c r="C471" s="4"/>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A472" s="3"/>
       <c r="C472" s="4"/>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A473" s="3"/>
       <c r="C473" s="4"/>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A474" s="3"/>
       <c r="C474" s="4"/>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A475" s="3"/>
       <c r="C475" s="4"/>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A476" s="3"/>
       <c r="C476" s="4"/>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A477" s="3"/>
       <c r="C477" s="4"/>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A478" s="3"/>
       <c r="C478" s="4"/>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A479" s="3"/>
       <c r="C479" s="4"/>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A480" s="3"/>
       <c r="C480" s="4"/>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A481" s="3"/>
       <c r="C481" s="4"/>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A482" s="3"/>
       <c r="C482" s="4"/>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A483" s="3"/>
       <c r="C483" s="4"/>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A484" s="3"/>
       <c r="C484" s="4"/>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A485" s="3"/>
       <c r="C485" s="4"/>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A486" s="3"/>
       <c r="C486" s="4"/>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A487" s="3"/>
       <c r="C487" s="4"/>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A488" s="3"/>
       <c r="C488" s="4"/>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A489" s="3"/>
       <c r="C489" s="4"/>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A490" s="3"/>
       <c r="C490" s="4"/>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A491" s="3"/>
       <c r="C491" s="4"/>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A492" s="3"/>
       <c r="C492" s="4"/>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A493" s="3"/>
       <c r="C493" s="4"/>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A494" s="3"/>
       <c r="C494" s="4"/>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A495" s="3"/>
       <c r="C495" s="4"/>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A496" s="3"/>
       <c r="C496" s="4"/>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A497" s="3"/>
       <c r="C497" s="4"/>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A498" s="3"/>
       <c r="C498" s="4"/>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A499" s="3"/>
       <c r="C499" s="4"/>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A500" s="3"/>
       <c r="C500" s="4"/>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A501" s="3"/>
       <c r="C501" s="4"/>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A502" s="3"/>
       <c r="C502" s="4"/>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A503" s="3"/>
       <c r="C503" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M3"/>
+  <autoFilter ref="A3:K3"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <dataValidations count="26">
+  <dataValidations count="22">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
       <formula1>TRUE</formula1>
     </dataValidation>
@@ -7874,64 +7696,52 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="指标代码：怎么填" prompt="测试项目编号：告诉系统测的是哪一项。怎么填：从数据字典复制对应代码；例如纵跳用vertical_jump_cm，不用自己编编号。例：vertical_jump_cm。为什么：同一个数值可能是距离、重量或时间，需要明确对应的测试项目。不知道时：先找身体测量、体能测试等现成工作表；字典仍找不到时先确认项目，不随便套用别的代码。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="指标代码：怎么填" prompt="测试项目编号：告诉系统测的是哪一项。怎么填：从数据字典复制对应代码；例如纵跳用vertical_jump_cm，不用自己编编号。例：vertical_jump_cm。为什么：同一个数值可能是距离、重量或时间，需要明确对应的测试项目。不知道时：先找身体测量、体能测试等现成工作表；字典仍找不到时先确认项目，不随便套用别的代码。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="按项目指标字典填写；一项指标一行。 例：45" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="按项目指标字典填写；一项指标一行。 例：45" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="单位：怎么填" prompt="可由已知指标字典确定；不能确定时必须补充，冲突不得静默换算。 例：cm" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="单位：怎么填" prompt="可由已知指标字典确定；不能确定时必须补充，冲突不得静默换算。 例：cm" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="G10:G503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="指标名称：怎么填" prompt="本次测的项目：从中文下拉列表选择。怎么填：例如测纵跳就选纵跳（cm），成绩45厘米就在数值列填45；单位由选项确定。例：纵跳（cm）。为什么：让成绩对应到正确的测试项目，系统自动处理内部编号。不知道时：先找身体测量、体能测试等现成工作表；下拉找不到时请管理员配置测试项目。" showErrorMessage="1" errorTitle="请检查填写值" error="请从下拉列表选择测试项目；找不到时请管理员先配置。" sqref="D10:D503">
+      <formula1>_JINGJI_TEST_NAMES</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="指标名称：怎么填" prompt="本次测的项目：从中文下拉列表选择。怎么填：例如测纵跳就选纵跳（cm），成绩45厘米就在数值列填45；单位由选项确定。例：纵跳（cm）。为什么：让成绩对应到正确的测试项目，系统自动处理内部编号。不知道时：先找身体测量、体能测试等现成工作表；下拉找不到时请管理员配置测试项目。" showErrorMessage="1" errorTitle="请检查填写值" error="请从下拉列表选择测试项目；找不到时请管理员先配置。" sqref="D4:D503">
+      <formula1>_JINGJI_TEST_NAMES</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="从下拉列表选择中文测试项目，单位随项目确定；一项测试一行，只填写实际成绩。 例：45" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="从下拉列表选择中文测试项目，单位随项目确定；一项测试一行，只填写实际成绩。 例：45" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="F10:F503">
       <formula1>"左,右,双侧,中央"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="G4:G503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="F4:F503">
       <formula1>"左,右,双侧,中央"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="指标名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：纵跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="指标名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：纵跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="目标值：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：50" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="目标值：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：50" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="目标值：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：50" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="目标值：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：50" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -7943,776 +7753,506 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="55" customWidth="1"/>
+    <col min="1" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="C1" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="C1" s="14" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>176</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="B2" t="s">
         <v>177</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="C2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>179</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>180</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B4" t="s">
         <v>181</v>
       </c>
-      <c r="D2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B5" t="s">
         <v>183</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>184</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B6" t="s">
         <v>181</v>
       </c>
-      <c r="D3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>185</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>186</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>187</v>
       </c>
-      <c r="D4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>188</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>189</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B11" t="s">
         <v>190</v>
       </c>
-      <c r="D5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>191</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B12" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>192</v>
       </c>
-      <c r="C6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>193</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B14" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>194</v>
       </c>
-      <c r="C7" t="s">
-        <v>187</v>
-      </c>
-      <c r="D7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B15" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>195</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B16" t="s">
         <v>196</v>
       </c>
-      <c r="C8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C16" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>197</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B17" t="s">
         <v>198</v>
       </c>
-      <c r="C9" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C17" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>199</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>200</v>
       </c>
-      <c r="C10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B19" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>201</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B20" t="s">
         <v>202</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C20" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>203</v>
       </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B21" t="s">
         <v>204</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C21" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>205</v>
       </c>
-      <c r="C12" t="s">
-        <v>203</v>
-      </c>
-      <c r="D12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B22" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>206</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B23" t="s">
+        <v>181</v>
+      </c>
+      <c r="C23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>207</v>
       </c>
-      <c r="C13" t="s">
-        <v>203</v>
-      </c>
-      <c r="D13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B24" t="s">
+        <v>181</v>
+      </c>
+      <c r="C24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>208</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B25" t="s">
+        <v>181</v>
+      </c>
+      <c r="C25" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>209</v>
       </c>
-      <c r="C14" t="s">
-        <v>203</v>
-      </c>
-      <c r="D14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B26" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>210</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B27" t="s">
         <v>211</v>
       </c>
-      <c r="C15" t="s">
-        <v>203</v>
-      </c>
-      <c r="D15" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="C27" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>212</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B28" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>213</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B29" t="s">
         <v>214</v>
       </c>
-      <c r="D16" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="C29" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>215</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B30" t="s">
         <v>216</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C30" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>217</v>
       </c>
-      <c r="D17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B31" t="s">
         <v>218</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C31" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>219</v>
       </c>
-      <c r="C18" t="s">
-        <v>187</v>
-      </c>
-      <c r="D18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B32" t="s">
         <v>220</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>221</v>
       </c>
-      <c r="C19" t="s">
-        <v>214</v>
-      </c>
-      <c r="D19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B33" t="s">
+        <v>220</v>
+      </c>
+      <c r="C33" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>222</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B34" t="s">
+        <v>220</v>
+      </c>
+      <c r="C34" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>223</v>
       </c>
-      <c r="C20" t="s">
+      <c r="B35" t="s">
+        <v>220</v>
+      </c>
+      <c r="C35" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>224</v>
       </c>
-      <c r="D20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B36" t="s">
+        <v>220</v>
+      </c>
+      <c r="C36" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>225</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B37" t="s">
+        <v>220</v>
+      </c>
+      <c r="C37" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>226</v>
       </c>
-      <c r="C21" t="s">
+      <c r="B38" t="s">
+        <v>220</v>
+      </c>
+      <c r="C38" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>227</v>
       </c>
-      <c r="D21" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B39" t="s">
+        <v>220</v>
+      </c>
+      <c r="C39" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>228</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B40" t="s">
+        <v>220</v>
+      </c>
+      <c r="C40" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>229</v>
       </c>
-      <c r="C22" t="s">
-        <v>187</v>
-      </c>
-      <c r="D22" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B41" t="s">
+        <v>181</v>
+      </c>
+      <c r="C41" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>230</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B42" t="s">
+        <v>181</v>
+      </c>
+      <c r="C42" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>231</v>
       </c>
-      <c r="C23" t="s">
-        <v>187</v>
-      </c>
-      <c r="D23" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B43" t="s">
+        <v>181</v>
+      </c>
+      <c r="C43" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>232</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B44" t="s">
+        <v>181</v>
+      </c>
+      <c r="C44" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>233</v>
       </c>
-      <c r="C24" t="s">
-        <v>187</v>
-      </c>
-      <c r="D24" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>234</v>
-      </c>
-      <c r="B25" t="s">
-        <v>235</v>
-      </c>
-      <c r="C25" t="s">
-        <v>187</v>
-      </c>
-      <c r="D25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>236</v>
-      </c>
-      <c r="B26" t="s">
-        <v>237</v>
-      </c>
-      <c r="C26" t="s">
-        <v>187</v>
-      </c>
-      <c r="D26" t="s">
-        <v>48</v>
-      </c>
-      <c r="E26" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>238</v>
-      </c>
-      <c r="B27" t="s">
-        <v>239</v>
-      </c>
-      <c r="C27" t="s">
-        <v>240</v>
-      </c>
-      <c r="D27" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>242</v>
-      </c>
-      <c r="B28" t="s">
-        <v>243</v>
-      </c>
-      <c r="C28" t="s">
-        <v>190</v>
-      </c>
-      <c r="D28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>244</v>
-      </c>
-      <c r="B29" t="s">
-        <v>245</v>
-      </c>
-      <c r="C29" t="s">
-        <v>246</v>
-      </c>
-      <c r="D29" t="s">
-        <v>76</v>
-      </c>
-      <c r="E29" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>247</v>
-      </c>
-      <c r="B30" t="s">
-        <v>248</v>
-      </c>
-      <c r="C30" t="s">
-        <v>249</v>
-      </c>
-      <c r="D30" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>250</v>
-      </c>
-      <c r="B31" t="s">
-        <v>251</v>
-      </c>
-      <c r="C31" t="s">
-        <v>252</v>
-      </c>
-      <c r="D31" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>253</v>
-      </c>
-      <c r="B32" t="s">
-        <v>254</v>
-      </c>
-      <c r="C32" t="s">
-        <v>255</v>
-      </c>
-      <c r="D32" t="s">
-        <v>85</v>
-      </c>
-      <c r="E32" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>257</v>
-      </c>
-      <c r="B33" t="s">
-        <v>258</v>
-      </c>
-      <c r="C33" t="s">
-        <v>255</v>
-      </c>
-      <c r="D33" t="s">
-        <v>85</v>
-      </c>
-      <c r="E33" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>259</v>
-      </c>
-      <c r="B34" t="s">
-        <v>260</v>
-      </c>
-      <c r="C34" t="s">
-        <v>255</v>
-      </c>
-      <c r="D34" t="s">
-        <v>85</v>
-      </c>
-      <c r="E34" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>261</v>
-      </c>
-      <c r="B35" t="s">
-        <v>262</v>
-      </c>
-      <c r="C35" t="s">
-        <v>255</v>
-      </c>
-      <c r="D35" t="s">
-        <v>85</v>
-      </c>
-      <c r="E35" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>263</v>
-      </c>
-      <c r="B36" t="s">
-        <v>264</v>
-      </c>
-      <c r="C36" t="s">
-        <v>255</v>
-      </c>
-      <c r="D36" t="s">
-        <v>85</v>
-      </c>
-      <c r="E36" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>265</v>
-      </c>
-      <c r="B37" t="s">
-        <v>266</v>
-      </c>
-      <c r="C37" t="s">
-        <v>255</v>
-      </c>
-      <c r="D37" t="s">
-        <v>85</v>
-      </c>
-      <c r="E37" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>267</v>
-      </c>
-      <c r="B38" t="s">
-        <v>268</v>
-      </c>
-      <c r="C38" t="s">
-        <v>255</v>
-      </c>
-      <c r="D38" t="s">
-        <v>85</v>
-      </c>
-      <c r="E38" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>269</v>
-      </c>
-      <c r="B39" t="s">
-        <v>270</v>
-      </c>
-      <c r="C39" t="s">
-        <v>255</v>
-      </c>
-      <c r="D39" t="s">
-        <v>149</v>
-      </c>
-      <c r="E39" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>272</v>
-      </c>
-      <c r="B40" t="s">
-        <v>273</v>
-      </c>
-      <c r="C40" t="s">
-        <v>255</v>
-      </c>
-      <c r="D40" t="s">
-        <v>149</v>
-      </c>
-      <c r="E40" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>274</v>
-      </c>
-      <c r="B41" t="s">
-        <v>254</v>
-      </c>
-      <c r="C41" t="s">
-        <v>187</v>
-      </c>
-      <c r="D41" t="s">
-        <v>163</v>
-      </c>
-      <c r="E41" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>276</v>
-      </c>
-      <c r="B42" t="s">
-        <v>277</v>
-      </c>
-      <c r="C42" t="s">
-        <v>187</v>
-      </c>
-      <c r="D42" t="s">
-        <v>163</v>
-      </c>
-      <c r="E42" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>278</v>
-      </c>
-      <c r="B43" t="s">
-        <v>279</v>
-      </c>
-      <c r="C43" t="s">
-        <v>187</v>
-      </c>
-      <c r="D43" t="s">
-        <v>163</v>
-      </c>
-      <c r="E43" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>280</v>
-      </c>
-      <c r="B44" t="s">
-        <v>281</v>
-      </c>
-      <c r="C44" t="s">
-        <v>187</v>
-      </c>
-      <c r="D44" t="s">
-        <v>163</v>
-      </c>
-      <c r="E44" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>282</v>
-      </c>
       <c r="B45" t="s">
-        <v>283</v>
+        <v>177</v>
       </c>
       <c r="C45" t="s">
-        <v>181</v>
-      </c>
-      <c r="D45" t="s">
-        <v>163</v>
-      </c>
-      <c r="E45" t="s">
-        <v>275</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -8743,7 +8283,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -8779,7 +8319,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -8815,100 +8355,100 @@
     </row>
     <row r="3" ht="82" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W3" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X3" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AB3" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC3" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD3" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AE3" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF3" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -12631,7 +12171,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -12664,7 +12204,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -12697,91 +12237,91 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="W3" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="X3" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB3" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC3" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -14987,7 +14527,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -15001,7 +14541,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -15015,34 +14555,34 @@
     </row>
     <row r="3" ht="119" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -17133,7 +16673,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -17148,7 +16688,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -17163,37 +16703,37 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -19291,7 +18831,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -19313,7 +18853,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -19335,58 +18875,58 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -21526,7 +21066,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -21552,7 +21092,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -21578,70 +21118,70 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -23804,7 +23344,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -23820,7 +23360,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -23836,40 +23376,40 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -25974,7 +25514,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -25990,7 +25530,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -26006,40 +25546,40 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">

--- a/public/templates/竞迹统一数据导入模板.xlsx
+++ b/public/templates/竞迹统一数据导入模板.xlsx
@@ -88,7 +88,7 @@
           <t xml:space="preserve">等级
 选填
 例：建设
-仅填写实际已采集数据，未提供留空。 例：建设</t>
+仅填写实际已采集数据，未提供留空。 例：建设 可选：巅峰、良好、建设、调整</t>
         </r>
       </text>
     </comment>
@@ -259,7 +259,7 @@
           <t xml:space="preserve">测试类型
 选填
 例：专项测试
-仅填写实际已采集数据，未提供留空。 例：专项测试</t>
+仅填写实际已采集数据，未提供留空。 例：专项测试 可选：专项测试、体能测试、FMS测试、身体测量、竞技评估</t>
         </r>
       </text>
     </comment>
@@ -340,7 +340,7 @@
           <t xml:space="preserve">运动项目
 条件必填：未由当前项目、队伍预填时填写
 例：赛艇
-使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：赛艇</t>
+使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：赛艇 可选：游泳、马拉松游泳、花样游泳、跳水、水球、射箭、田径、羽毛球、棒球、垒球、篮球、三人篮球、拳击、激流、皮划艇、公路自行车、场地自行车、山地自行车、小轮车竞速、小轮车自由式、马术盛装舞步、马术三项赛、马术场地障碍、击剑、足球、高尔夫、竞技体操、艺术体操、蹦床、手球、曲棍球、柔道、空手道“型”、空手道“组手”、现代五项、赛艇、七人制橄榄球、帆船、射击、滑板、运动攀岩、冲浪、乒乓球、跆拳道、网球、铁人三项、排球、沙滩排球、举重、摔跤</t>
         </r>
       </text>
     </comment>
@@ -500,7 +500,7 @@
           <t xml:space="preserve">身体状态
 选填
 例：健康
-仅填写实际已采集数据，未提供留空。 例：健康</t>
+仅填写实际已采集数据，未提供留空。 例：健康 可选：健康、观察、训练受限、康复中</t>
         </r>
       </text>
     </comment>
@@ -540,7 +540,7 @@
           <t xml:space="preserve">训练状态
 选填
 例：在训
-仅填写实际已采集数据，未提供留空。 例：在训</t>
+仅填写实际已采集数据，未提供留空。 例：在训 可选：在训、集训、休整、离队</t>
         </r>
       </text>
     </comment>
@@ -1707,8 +1707,8 @@
         <r>
           <t xml:space="preserve">状态
 选填
-例：normal
-normal正常、rest休息、attention关注、alert警报、missing缺失；至少一项恢复数值或状态，不能仅备注。 例：normal 可选：normal、rest、attention、alert、missing</t>
+例：正常
+从下拉选择正常、休息、关注、警报或缺失；至少一项恢复数值或状态，不能仅备注。 例：正常 可选：正常、休息、关注、警报、缺失</t>
         </r>
       </text>
     </comment>
@@ -1857,7 +1857,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="235">
   <si>
     <t>竞迹训练监控系统｜简化数据导入模板</t>
   </si>
@@ -1871,37 +1871,40 @@
     <t>2. 表头颜色：红色=必填，橙色=满足说明中的条件才必填，蓝色=选填，灰色=系统预填；具体填写要求以表头文字为准。</t>
   </si>
   <si>
-    <t>3. 必填项在前，选填项在后；常用选填项排在专业选填项前面，所有数据列直接显示，按需填写即可。</t>
+    <t>3. 有固定选项的字段直接点击单元格下拉选择；无需手写内部代码。空白表示未提供，不用选择任意值占位。</t>
   </si>
   <si>
-    <t>4. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。所有已填写的数据都会校验和导入。</t>
+    <t>4. 必填项在前，选填项在后；常用选填项排在专业选填项前面，所有数据列直接显示，按需填写即可。</t>
   </si>
   <si>
-    <t>5. 业务日期须在行内填写，或在上传页明确选择统一日期；新模板不静默使用今天，生日永不补填。</t>
+    <t>5. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。所有已填写的数据都会校验和导入。</t>
   </si>
   <si>
-    <t>6. 系统预填：授权范围内的人员编号、姓名、项目和队伍；不要自行编造编号，不预填测量成绩。</t>
+    <t>6. 业务日期须在行内填写，或在上传页明确选择统一日期；新模板不静默使用今天，生日永不补填。</t>
   </si>
   <si>
-    <t>7. SRPE：有效时长(min)×RPE，单位AU；缺时长或RPE保持未提供，不能根据距离推算时长。</t>
+    <t>7. 系统预填：授权范围内的人员编号、姓名、项目和队伍；不要自行编造编号，不预填测量成绩。</t>
   </si>
   <si>
-    <t>8. SMVL/力量训练量：按现有规则汇总实际次数×实际重量kg；计划数不是实际数，外部显式总量沿用既有优先策略。</t>
+    <t>8. SRPE：有效时长(min)×RPE，单位AU；缺时长或RPE保持未提供，不能根据距离推算时长。</t>
   </si>
   <si>
-    <t>9. FMS：七项齐全才生成完整21分制总分，未测不补0。专项：按有效轮次计算平均、最好及同条件排名；无可比历史显示缺失。</t>
+    <t>9. SMVL/力量训练量：按现有规则汇总实际次数×实际重量kg；计划数不是实际数，外部显式总量沿用既有优先策略。</t>
   </si>
   <si>
-    <t>10. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
+    <t>10. FMS：七项齐全才生成完整21分制总分，未测不补0。专项：按有效轮次计算平均、最好及同条件排名；无可比历史显示缺失。</t>
   </si>
   <si>
-    <t>11. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
+    <t>11. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
   </si>
   <si>
-    <t>12. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
+    <t>12. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
   </si>
   <si>
-    <t>13. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
+    <t>13. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
+  </si>
+  <si>
+    <t>14. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
   </si>
   <si>
     <t>运动员基本资料</t>
@@ -2499,7 +2502,7 @@
   <si>
     <t xml:space="preserve">状态
 选填
-例：normal</t>
+例：正常</t>
   </si>
   <si>
     <t>伤病记录</t>
@@ -3304,7 +3307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -3382,6 +3385,11 @@
     <row r="15" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3406,7 +3414,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3425,7 +3433,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3444,49 +3452,49 @@
     </row>
     <row r="3" ht="119" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -5496,94 +5504,94 @@
     <mergeCell ref="A2:O2"/>
   </mergeCells>
   <dataValidations count="30">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总分：怎么填" prompt="新增竞技状态记录需有依据的原始总分；单项一般耐力/核心力量评分可单独填写并注明评估协议，不能编造总分。 例：80（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总分：怎么填" prompt="新增竞技状态记录需有依据的原始总分；单项一般耐力/核心力量评分可单独填写并注明评估协议，不能编造总分。 例：80（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估协议：怎么填" prompt="评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估协议：怎么填" prompt="评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：建设" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：建设" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="一般耐力评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：80（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="一般耐力评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：80（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="核心力量评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="核心力量评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75（须按实际评分表打分）" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="专项耐力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="专项耐力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="力量爆发：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="力量爆发：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="技术效率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="技术效率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="负荷适应：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="负荷适应：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="恢复能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="恢复能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="比赛能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="比赛能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总分：怎么填" prompt="新增竞技状态记录需有依据的原始总分；单项一般耐力/核心力量评分可单独填写并注明评估协议，不能编造总分。 例：80（须按实际评分表打分）" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总分：怎么填" prompt="新增竞技状态记录需有依据的原始总分；单项一般耐力/核心力量评分可单独填写并注明评估协议，不能编造总分。 例：80（须按实际评分表打分）" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估协议：怎么填" prompt="评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估协议：怎么填" prompt="评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：建设 可选：巅峰、良好、建设、调整" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：巅峰、良好、建设、调整" sqref="F10:F503">
+      <formula1>"巅峰,良好,建设,调整"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：建设 可选：巅峰、良好、建设、调整" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：巅峰、良好、建设、调整" sqref="F4:F503">
+      <formula1>"巅峰,良好,建设,调整"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="一般耐力评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：80（须按实际评分表打分）" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="一般耐力评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：80（须按实际评分表打分）" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="核心力量评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75（须按实际评分表打分）" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="核心力量评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75（须按实际评分表打分）" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="专项耐力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="专项耐力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="力量爆发：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="力量爆发：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="技术效率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="技术效率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="负荷适应：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="负荷适应：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="恢复能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="恢复能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="比赛能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="比赛能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -5608,7 +5616,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5623,7 +5631,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -5638,37 +5646,37 @@
     </row>
     <row r="3" ht="104" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -7678,70 +7686,70 @@
     <mergeCell ref="A2:K2"/>
   </mergeCells>
   <dataValidations count="22">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="指标名称：怎么填" prompt="本次测的项目：从中文下拉列表选择。怎么填：例如测纵跳就选纵跳（cm），成绩45厘米就在数值列填45；单位由选项确定。例：纵跳（cm）。为什么：让成绩对应到正确的测试项目，系统自动处理内部编号。不知道时：先找身体测量、体能测试等现成工作表；下拉找不到时请管理员配置测试项目。" showErrorMessage="1" errorTitle="请检查填写值" error="请从下拉列表选择测试项目；找不到时请管理员先配置。" sqref="D10:D503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="测试项目：怎么填" prompt="本次测的项目：从中文下拉列表选择。怎么填：例如测纵跳就选纵跳（cm），成绩45厘米就在数值列填45；单位由选项确定。例：纵跳（cm）。为什么：让成绩对应到正确的测试项目，系统自动处理内部编号。不知道时：先找身体测量、体能测试等现成工作表；下拉找不到时请管理员配置测试项目。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请从下拉列表选择；找不到选项时请核对项目或联系管理员。" sqref="D10:D503">
       <formula1>_JINGJI_TEST_NAMES</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="指标名称：怎么填" prompt="本次测的项目：从中文下拉列表选择。怎么填：例如测纵跳就选纵跳（cm），成绩45厘米就在数值列填45；单位由选项确定。例：纵跳（cm）。为什么：让成绩对应到正确的测试项目，系统自动处理内部编号。不知道时：先找身体测量、体能测试等现成工作表；下拉找不到时请管理员配置测试项目。" showErrorMessage="1" errorTitle="请检查填写值" error="请从下拉列表选择测试项目；找不到时请管理员先配置。" sqref="D4:D503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="测试项目：怎么填" prompt="本次测的项目：从中文下拉列表选择。怎么填：例如测纵跳就选纵跳（cm），成绩45厘米就在数值列填45；单位由选项确定。例：纵跳（cm）。为什么：让成绩对应到正确的测试项目，系统自动处理内部编号。不知道时：先找身体测量、体能测试等现成工作表；下拉找不到时请管理员配置测试项目。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请从下拉列表选择；找不到选项时请核对项目或联系管理员。" sqref="D4:D503">
       <formula1>_JINGJI_TEST_NAMES</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="从下拉列表选择中文测试项目，单位随项目确定；一项测试一行，只填写实际成绩。 例：45" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="从下拉列表选择中文测试项目，单位随项目确定；一项测试一行，只填写实际成绩。 例：45" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="F10:F503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="从下拉列表选择中文测试项目，单位随项目确定；一项测试一行，只填写实际成绩。 例：45" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="从下拉列表选择中文测试项目，单位随项目确定；一项测试一行，只填写实际成绩。 例：45" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="F10:F503">
       <formula1>"左,右,双侧,中央"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="F4:F503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="F4:F503">
       <formula1>"左,右,双侧,中央"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="目标值：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：50" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="目标值：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：50" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试 可选：专项测试、体能测试、FMS测试、身体测量、竞技评估" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：专项测试、体能测试、FMS测试、身体测量、竞技评估" sqref="G10:G503">
+      <formula1>"专项测试,体能测试,FMS测试,身体测量,竞技评估"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试 可选：专项测试、体能测试、FMS测试、身体测量、竞技评估" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：专项测试、体能测试、FMS测试、身体测量、竞技评估" sqref="G4:G503">
+      <formula1>"专项测试,体能测试,FMS测试,身体测量,竞技评估"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="目标值：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：50" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="目标值：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：50" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -7762,497 +7770,497 @@
   <sheetData>
     <row r="1" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" t="s">
         <v>179</v>
-      </c>
-      <c r="B3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C3" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B12" t="s">
         <v>191</v>
       </c>
-      <c r="B12" t="s">
-        <v>190</v>
-      </c>
       <c r="C12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C24" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B25" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B27" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C27" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B29" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B30" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C30" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B31" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B32" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>222</v>
+      </c>
+      <c r="B33" t="s">
         <v>221</v>
       </c>
-      <c r="B33" t="s">
-        <v>220</v>
-      </c>
       <c r="C33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B34" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B35" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B36" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C36" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B37" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C37" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B38" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C38" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B39" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C39" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C40" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B41" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C41" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B42" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C42" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B43" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C43" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B44" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C44" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B45" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C45" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -8283,7 +8291,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -8319,7 +8327,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -8355,100 +8363,100 @@
     </row>
     <row r="3" ht="82" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W3" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X3" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB3" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC3" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AD3" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE3" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF3" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -11958,196 +11966,196 @@
     <mergeCell ref="A2:AF2"/>
   </mergeCells>
   <dataValidations count="64">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA10:AA503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA4:AA503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="集训时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01至2026-10-15" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB10:AB503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="集训时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01至2026-10-15" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB4:AB503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC10:AC503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC4:AC503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送单位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际单位名称" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AD10:AD503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送单位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际单位名称" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AD4:AD503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送教练：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：王某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AE10:AE503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送教练：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：王某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AE4:AE503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="优势项：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项耐力" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AF10:AF503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="优势项：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项耐力" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AF4:AF503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="运动项目：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：赛艇" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="运动项目：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：赛艇" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="所属队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="所属队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="性别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男 可选：男、女" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：男、女" sqref="E10:E503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA10:AA503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA4:AA503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="集训时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01至2026-10-15" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB10:AB503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="集训时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01至2026-10-15" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB4:AB503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC10:AC503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC4:AC503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送单位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际单位名称" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AD10:AD503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送单位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际单位名称" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AD4:AD503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送教练：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：王某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AE10:AE503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送教练：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：王某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AE4:AE503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="优势项：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项耐力" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AF10:AF503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="优势项：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项耐力" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AF4:AF503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="运动项目：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：赛艇 可选：游泳、马拉松游泳、花样游泳、跳水、水球、射箭、田径、羽毛球、棒球、垒球、篮球、三人篮球、拳击、激流、皮划艇、公路自行车、场地自行车、山地自行车、小轮车竞速、小轮车自由式、马术盛装舞步、马术三项赛、马术场地障碍、击剑、足球、高尔夫、竞技体操、艺术体操、蹦床、手球、曲棍球、柔道、空手道“型”、空手道“组手”、现代五项、赛艇、七人制橄榄球、帆船、射击、滑板、运动攀岩、冲浪、乒乓球、跆拳道、网球、铁人三项、排球、沙滩排球、举重" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：游泳、马拉松游泳、花样游泳、跳水、水球、射箭、田径、羽毛球、棒球、垒球、篮球、三人篮球、拳击、激流、皮划艇、公路自行车、场地自行车、山地自行车、小轮车竞速、小轮车自由式、马术盛装舞步、马术三项赛、马术场地障碍、击剑、足球、高尔夫、竞技体操、艺术体操、蹦床、手球、曲棍球、柔道、空手道“型”、空手道“组手”、现代五项、赛艇、七人制橄榄球、帆船、射击、滑板、运动攀岩、冲浪、乒乓球、跆拳道、网球、铁人三项、排球、沙滩排球、举重、摔跤" sqref="C10:C503">
+      <formula1>"游泳,马拉松游泳,花样游泳,跳水,水球,射箭,田径,羽毛球,棒球,垒球,篮球,三人篮球,拳击,激流,皮划艇,公路自行车,场地自行车,山地自行车,小轮车竞速,小轮车自由式,马术盛装舞步,马术三项赛,马术场地障碍,击剑,足球,高尔夫,竞技体操,艺术体操,蹦床,手球,曲棍球,柔道,空手道“型”,空手道“组手”,现代五项,赛艇,七人制橄榄球,帆船,射击,滑板,运动攀岩,冲浪,乒乓球,跆拳道,网球,铁人三项,排球,沙滩排球,举重,摔跤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="运动项目：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：赛艇 可选：游泳、马拉松游泳、花样游泳、跳水、水球、射箭、田径、羽毛球、棒球、垒球、篮球、三人篮球、拳击、激流、皮划艇、公路自行车、场地自行车、山地自行车、小轮车竞速、小轮车自由式、马术盛装舞步、马术三项赛、马术场地障碍、击剑、足球、高尔夫、竞技体操、艺术体操、蹦床、手球、曲棍球、柔道、空手道“型”、空手道“组手”、现代五项、赛艇、七人制橄榄球、帆船、射击、滑板、运动攀岩、冲浪、乒乓球、跆拳道、网球、铁人三项、排球、沙滩排球、举重" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：游泳、马拉松游泳、花样游泳、跳水、水球、射箭、田径、羽毛球、棒球、垒球、篮球、三人篮球、拳击、激流、皮划艇、公路自行车、场地自行车、山地自行车、小轮车竞速、小轮车自由式、马术盛装舞步、马术三项赛、马术场地障碍、击剑、足球、高尔夫、竞技体操、艺术体操、蹦床、手球、曲棍球、柔道、空手道“型”、空手道“组手”、现代五项、赛艇、七人制橄榄球、帆船、射击、滑板、运动攀岩、冲浪、乒乓球、跆拳道、网球、铁人三项、排球、沙滩排球、举重、摔跤" sqref="C4:C503">
+      <formula1>"游泳,马拉松游泳,花样游泳,跳水,水球,射箭,田径,羽毛球,棒球,垒球,篮球,三人篮球,拳击,激流,皮划艇,公路自行车,场地自行车,山地自行车,小轮车竞速,小轮车自由式,马术盛装舞步,马术三项赛,马术场地障碍,击剑,足球,高尔夫,竞技体操,艺术体操,蹦床,手球,曲棍球,柔道,空手道“型”,空手道“组手”,现代五项,赛艇,七人制橄榄球,帆船,射击,滑板,运动攀岩,冲浪,乒乓球,跆拳道,网球,铁人三项,排球,沙滩排球,举重,摔跤"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="所属队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="所属队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="性别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男 可选：男、女" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：男、女" sqref="E10:E503">
       <formula1>"男,女"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="性别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男 可选：男、女" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：男、女" sqref="E4:E503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="性别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男 可选：男、女" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：男、女" sqref="E4:E503">
       <formula1>"男,女"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="出生日期：怎么填" prompt="档案选填；不套用注册必填规则，不根据年龄反推生日。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="出生日期：怎么填" prompt="档案选填；不套用注册必填规则，不根据年龄反推生日。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="技术等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：一级运动员 可选：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" sqref="G10:G503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="出生日期：怎么填" prompt="档案选填；不套用注册必填规则，不根据年龄反推生日。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="出生日期：怎么填" prompt="档案选填；不套用注册必填规则，不根据年龄反推生日。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="技术等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：一级运动员 可选：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" sqref="G10:G503">
       <formula1>"未定级,国际级运动健将,运动健将,一级运动员,二级运动员,三级运动员"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="技术等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：一级运动员 可选：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" sqref="G4:G503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="技术等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：一级运动员 可选：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" sqref="G4:G503">
       <formula1>"未定级,国际级运动健将,运动健将,一级运动员,二级运动员,三级运动员"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="省份：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江省" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="省份：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江省" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="城市：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州市" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="城市：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州市" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="区县：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：西湖区" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="区县：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：西湖区" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="民族：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：汉族" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="民族：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：汉族" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="手机号：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="手机号：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="血型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：A 可选：A、B、AB、O" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：A、B、AB、O" sqref="N10:N503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="省份：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江省" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="省份：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江省" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="城市：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州市" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="城市：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州市" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="区县：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：西湖区" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="区县：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：西湖区" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="民族：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：汉族" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="民族：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：汉族" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="手机号：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="手机号：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="血型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：A 可选：A、B、AB、O" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：A、B、AB、O" sqref="N10:N503">
       <formula1>"A,B,AB,O"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="血型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：A 可选：A、B、AB、O" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：A、B、AB、O" sqref="N4:N503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="血型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：A 可选：A、B、AB、O" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：A、B、AB、O" sqref="N4:N503">
       <formula1>"A,B,AB,O"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急联系人：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：李某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急联系人：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：李某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急电话：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P10:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急电话：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P4:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="学历：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本科" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="学历：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本科" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="位置号位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：1号位" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="位置号位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：1号位" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="身体状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：健康" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S10:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="身体状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：健康" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S4:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最好成绩：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：原始成绩及单位" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最好成绩：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：原始成绩及单位" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="籍贯：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江杭州" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="籍贯：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江杭州" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="家庭住址：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际联系地址" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V10:V503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="家庭住址：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际联系地址" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V4:V503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：在训" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W10:W503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：在训" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W4:W503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始运动日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X10:X503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始运动日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X4:X503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：训练中心" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y10:Y503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：训练中心" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y4:Y503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战赛事：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际赛事名称" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z10:Z503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战赛事：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际赛事名称" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z4:Z503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急联系人：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：李某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急联系人：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：李某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急电话：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P10:P503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急电话：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P4:P503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="学历：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本科" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="学历：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本科" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="位置号位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：1号位" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="位置号位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：1号位" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：健康 可选：健康、观察、训练受限、康复中" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：健康、观察、训练受限、康复中" sqref="S10:S503">
+      <formula1>"健康,观察,训练受限,康复中"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：健康 可选：健康、观察、训练受限、康复中" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：健康、观察、训练受限、康复中" sqref="S4:S503">
+      <formula1>"健康,观察,训练受限,康复中"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最好成绩：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：原始成绩及单位" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:T503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最好成绩：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：原始成绩及单位" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:T503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="籍贯：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江杭州" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="籍贯：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江杭州" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="家庭住址：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际联系地址" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V10:V503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="家庭住址：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际联系地址" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V4:V503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：在训 可选：在训、集训、休整、离队" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：在训、集训、休整、离队" sqref="W10:W503">
+      <formula1>"在训,集训,休整,离队"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：在训 可选：在训、集训、休整、离队" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：在训、集训、休整、离队" sqref="W4:W503">
+      <formula1>"在训,集训,休整,离队"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始运动日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X10:X503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始运动日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X4:X503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：训练中心" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y10:Y503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：训练中心" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y4:Y503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战赛事：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际赛事名称" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z10:Z503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战赛事：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际赛事名称" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z4:Z503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -12171,7 +12179,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -12204,7 +12212,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -12237,91 +12245,91 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="W3" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X3" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB3" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -14331,178 +14339,178 @@
     <mergeCell ref="A2:AC2"/>
   </mergeCells>
   <dataValidations count="58">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA10:AA503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA4:AA503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB10:AB503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB4:AB503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC10:AC503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC4:AC503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测量日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测量日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：75" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：75" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="身高cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：180" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="身高cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：180" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="臂展cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：185" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="臂展cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：185" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体脂率%：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：15" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体脂率%：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：15" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="骨骼肌kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="骨骼肌kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉量kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉量kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="上肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="上肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="下肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="下肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="皮下脂肪mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="皮下脂肪mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肱三头肌皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肱三头肌皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="腹部皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="腹部皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="大腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P10:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="大腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P4:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="小腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="小腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪等级：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪等级：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="基础代谢kcal：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：1800" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S10:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="基础代谢kcal：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：1800" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S4:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总水分kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总水分kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="细胞外水比：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：0.38" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="细胞外水比：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：0.38" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="相位角°：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V10:V503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="相位角°：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V4:V503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪面积cm²：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W10:W503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪面积cm²：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W4:W503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X10:X503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X4:X503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y10:Y503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y4:Y503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z10:Z503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z4:Z503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA10:AA503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA4:AA503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB10:AB503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB4:AB503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC10:AC503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC4:AC503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测量日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测量日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：75" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：75" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="身高cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：180" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="身高cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：180" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="臂展cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：185" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="臂展cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：185" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体脂率%：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：15" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体脂率%：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：15" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="骨骼肌kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="骨骼肌kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉量kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉量kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="上肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="上肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="下肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="下肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="皮下脂肪mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="皮下脂肪mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肱三头肌皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肱三头肌皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="腹部皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="腹部皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="大腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P10:P503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="大腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P4:P503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="小腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="小腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪等级：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪等级：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="基础代谢kcal：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：1800" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S10:S503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="基础代谢kcal：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：1800" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S4:S503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总水分kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:T503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总水分kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:T503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="细胞外水比：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：0.38" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="细胞外水比：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：0.38" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="相位角°：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V10:V503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="相位角°：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V4:V503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪面积cm²：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W10:W503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪面积cm²：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W4:W503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X10:X503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X4:X503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y10:Y503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y4:Y503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z10:Z503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z4:Z503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -14527,7 +14535,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -14541,7 +14549,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -14555,34 +14563,34 @@
     </row>
     <row r="3" ht="119" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -16592,64 +16600,64 @@
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="20">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试协议：怎么填" prompt="测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试协议：怎么填" prompt="测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="VO2Max：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="VO2Max：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="CMJ峰值功率W：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：3000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="CMJ峰值功率W：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：3000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="无氧功率W/kg：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：12" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="无氧功率W/kg：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：12" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="IMTP峰值力量N：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：2000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="IMTP峰值力量N：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：2000" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="不对称指数%：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="不对称指数%：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试协议：怎么填" prompt="测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试协议：怎么填" prompt="测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="VO2Max：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：55" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="VO2Max：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：55" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="CMJ峰值功率W：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：3000" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="CMJ峰值功率W：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：3000" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="无氧功率W/kg：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：12" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="无氧功率W/kg：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：12" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="IMTP峰值力量N：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：2000" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="IMTP峰值力量N：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：2000" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="不对称指数%：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：8" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="不对称指数%：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：8" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -16673,7 +16681,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -16688,7 +16696,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -16703,37 +16711,37 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -18743,70 +18751,70 @@
     <mergeCell ref="A2:K2"/>
   </mergeCells>
   <dataValidations count="22">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="深蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="D10:D503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="深蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="D10:D503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="深蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="D4:D503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="深蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="D4:D503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="跨栏步：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="E10:E503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="跨栏步：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="E10:E503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="跨栏步：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="E4:E503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="跨栏步：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="E4:E503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="直线弓步蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="F10:F503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="直线弓步蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="F10:F503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="直线弓步蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="F4:F503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="直线弓步蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="F4:F503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="肩部灵活性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="G10:G503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="肩部灵活性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="G10:G503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="肩部灵活性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="G4:G503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="肩部灵活性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="G4:G503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="主动直腿上抬：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="H10:H503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="主动直腿上抬：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="H10:H503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="主动直腿上抬：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="H4:H503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="主动直腿上抬：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="H4:H503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="躯干稳定俯卧撑：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="I10:I503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="躯干稳定俯卧撑：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="I10:I503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="躯干稳定俯卧撑：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="I4:I503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="躯干稳定俯卧撑：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="I4:I503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="旋转稳定性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="J10:J503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="旋转稳定性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="J10:J503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="旋转稳定性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="J4:J503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="旋转稳定性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="J4:J503">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -18831,7 +18839,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -18853,7 +18861,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -18875,58 +18883,58 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -20936,112 +20944,112 @@
     <mergeCell ref="A2:R2"/>
   </mergeCells>
   <dataValidations count="36">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="时长分钟：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="时长分钟：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="距离千米：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="距离千米：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：08:30" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：08:30" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练内容：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：水上耐力训练" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练内容：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：水上耐力训练" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="L10:L503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="时长分钟：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="时长分钟：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="距离千米：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="距离千米：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：08:30" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：08:30" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练内容：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：水上耐力训练" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练内容：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：水上耐力训练" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="L10:L503">
       <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="L4:L503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="L4:L503">
       <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SRPE：怎么填" prompt="本次训练负荷：系统用时长和RPE计算。怎么填：日常不用填。填写训练时长和RPE后由系统计算；只有已有外部原始负荷值时才补这列。例：360。为什么：用于记录训练负荷，公式为分钟数×RPE。不知道时：没有外部原始值就留空；缺RPE时也不用自己估算。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SRPE：怎么填" prompt="本次训练负荷：系统用时长和RPE计算。怎么填：日常不用填。填写训练时长和RPE后由系统计算；只有已有外部原始负荷值时才补这列。例：360。为什么：用于记录训练负荷，公式为分钟数×RPE。不知道时：没有外部原始值就留空；缺RPE时也不用自己估算。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SMVL：怎么填" prompt="力量训练量：系统汇总实际次数和重量。怎么填：日常不用填，逐组填写实际次数和实际重量；只有外部记录已给出整课总量时才补本列。例：360。为什么：用于汇总力量训练完成量；计划重量不能当成实际重量。不知道时：不知道整课总量就留空，不必手算，也不要填0占位。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SMVL：怎么填" prompt="力量训练量：系统汇总实际次数和重量。怎么填：日常不用填，逐组填写实际次数和实际重量；只有外部记录已给出整课总量时才补本列。例：360。为什么：用于汇总力量训练完成量；计划重量不能当成实际重量。不知道时：不知道整课总量就留空，不必手算，也不要填0占位。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：140" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：140" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最大心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：175" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P10:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最大心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：175" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P4:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均功率W：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均功率W：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="桨频SPM：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：22" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="桨频SPM：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：22" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SRPE：怎么填" prompt="本次训练负荷：系统用时长和RPE计算。怎么填：日常不用填。填写训练时长和RPE后由系统计算；只有已有外部原始负荷值时才补这列。例：360。为什么：用于记录训练负荷，公式为分钟数×RPE。不知道时：没有外部原始值就留空；缺RPE时也不用自己估算。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SRPE：怎么填" prompt="本次训练负荷：系统用时长和RPE计算。怎么填：日常不用填。填写训练时长和RPE后由系统计算；只有已有外部原始负荷值时才补这列。例：360。为什么：用于记录训练负荷，公式为分钟数×RPE。不知道时：没有外部原始值就留空；缺RPE时也不用自己估算。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SMVL：怎么填" prompt="力量训练量：系统汇总实际次数和重量。怎么填：日常不用填，逐组填写实际次数和实际重量；只有外部记录已给出整课总量时才补本列。例：360。为什么：用于汇总力量训练完成量；计划重量不能当成实际重量。不知道时：不知道整课总量就留空，不必手算，也不要填0占位。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SMVL：怎么填" prompt="力量训练量：系统汇总实际次数和重量。怎么填：日常不用填，逐组填写实际次数和实际重量；只有外部记录已给出整课总量时才补本列。例：360。为什么：用于汇总力量训练完成量；计划重量不能当成实际重量。不知道时：不知道整课总量就留空，不必手算，也不要填0占位。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：140" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：140" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最大心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：175" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P10:P503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最大心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：175" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P4:P503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均功率W：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均功率W：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="桨频SPM：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：22" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="桨频SPM：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：22" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -21066,7 +21074,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -21092,7 +21100,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -21118,70 +21126,70 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -23191,136 +23199,136 @@
     <mergeCell ref="A2:V2"/>
   </mergeCells>
   <dataValidations count="44">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组序：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组序：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="完成状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：已完成 可选：已完成、未完成" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：已完成、未完成" sqref="K10:K503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组序：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组序：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：上午力量" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：上午力量" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="完成状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：已完成 可选：已完成、未完成" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：已完成、未完成" sqref="K10:K503">
       <formula1>"已完成,未完成"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="完成状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：已完成 可选：已完成、未完成" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：已完成、未完成" sqref="K4:K503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="完成状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：已完成 可选：已完成、未完成" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：已完成、未完成" sqref="K4:K503">
       <formula1>"已完成,未完成"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度百分比：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度百分比：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="类别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="O10:O503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度百分比：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度百分比：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="类别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="O10:O503">
       <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="类别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="O4:O503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="类别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="O4:O503">
       <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体部位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="P10:P503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体部位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="P10:P503">
       <formula1>"上肢,下肢,核心,全身"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体部位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="P4:P503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体部位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="P4:P503">
       <formula1>"上肢,下肢,核心,全身"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作代码：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：squat" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作代码：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：squat" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="S10:S503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作代码：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：squat" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作代码：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：squat" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="S10:S503">
       <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="S4:S503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="S4:S503">
       <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次距离千米：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次距离千米：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="V10:V503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:T503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:T503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次距离千米：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次距离千米：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="V10:V503">
       <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="V4:V503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="V4:V503">
       <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23344,7 +23352,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -23360,7 +23368,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -23376,40 +23384,40 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -25419,76 +25427,76 @@
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <dataValidations count="24">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠小时：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠小时：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：8" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠质量：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠质量：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疲劳：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疲劳：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉酸痛：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉酸痛：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="情绪：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="情绪：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="晨脉：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="晨脉：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：55" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="normal正常、rest休息、attention关注、alert警报、missing缺失；至少一项恢复数值或状态，不能仅备注。 例：normal 可选：normal、rest、attention、alert、missing" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：normal、rest、attention、alert、missing" sqref="K10:K503">
-      <formula1>"normal,rest,attention,alert,missing"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="normal正常、rest休息、attention关注、alert警报、missing缺失；至少一项恢复数值或状态，不能仅备注。 例：normal 可选：normal、rest、attention、alert、missing" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：normal、rest、attention、alert、missing" sqref="K4:K503">
-      <formula1>"normal,rest,attention,alert,missing"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠小时：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：8" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠小时：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：8" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠质量：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠质量：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疲劳：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疲劳：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉酸痛：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉酸痛：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="情绪：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="情绪：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="晨脉：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：55" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="晨脉：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：55" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="从下拉选择正常、休息、关注、警报或缺失；至少一项恢复数值或状态，不能仅备注。 例：正常 可选：正常、休息、关注、警报、缺失" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：正常、休息、关注、警报、缺失" sqref="K10:K503">
+      <formula1>"正常,休息,关注,警报,缺失"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="从下拉选择正常、休息、关注、警报或缺失；至少一项恢复数值或状态，不能仅备注。 例：正常 可选：正常、休息、关注、警报、缺失" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：正常、休息、关注、警报、缺失" sqref="K4:K503">
+      <formula1>"正常,休息,关注,警报,缺失"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
@@ -25514,7 +25522,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -25530,7 +25538,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -25546,40 +25554,40 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -28089,76 +28097,76 @@
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <dataValidations count="24">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="发生日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="发生日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="伤病名称：怎么填" prompt="填写实际记录。 例：踝关节扭伤" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="伤病名称：怎么填" prompt="填写实际记录。 例：踝关节扭伤" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="部位：怎么填" prompt="填写实际记录。 例：踝关节" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="部位：怎么填" prompt="填写实际记录。 例：踝关节" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：左 可选：左、右、双侧、未指定" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、未指定" sqref="F10:F503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="发生日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="发生日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="伤病名称：怎么填" prompt="填写实际记录。 例：踝关节扭伤" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="伤病名称：怎么填" prompt="填写实际记录。 例：踝关节扭伤" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="部位：怎么填" prompt="填写实际记录。 例：踝关节" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="部位：怎么填" prompt="填写实际记录。 例：踝关节" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：左 可选：左、右、双侧、未指定" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：左、右、双侧、未指定" sqref="F10:F503">
       <formula1>"左,右,双侧,未指定"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：左 可选：左、右、双侧、未指定" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：左、右、双侧、未指定" sqref="F4:F503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：左 可选：左、右、双侧、未指定" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：左、右、双侧、未指定" sqref="F4:F503">
       <formula1>"左,右,双侧,未指定"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="空白新增时沿用观察状态，不自动推断诊断。 例：观察 可选：健康、观察、限训、康复、停训" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：健康、观察、限训、康复、停训" sqref="G10:G503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="空白新增时沿用观察状态，不自动推断诊断。 例：观察 可选：健康、观察、限训、康复、停训" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：健康、观察、限训、康复、停训" sqref="G10:G503">
       <formula1>"健康,观察,限训,康复,停训"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="空白新增时沿用观察状态，不自动推断诊断。 例：观察 可选：健康、观察、限训、康复、停训" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：健康、观察、限训、康复、停训" sqref="G4:G503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="空白新增时沿用观察状态，不自动推断诊断。 例：观察 可选：健康、观察、限训、康复、停训" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：健康、观察、限训、康复、停训" sqref="G4:G503">
       <formula1>"健康,观察,限训,康复,停训"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疼痛评分：怎么填" prompt="0—10分；0表示无痛，未采集必须留空。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疼痛评分：怎么填" prompt="0—10分；0表示无痛，未采集必须留空。 例：2" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练限制：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：避免跑跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练限制：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：避免跑跳" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="康复计划：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按专业人员制定的方案填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="康复计划：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按专业人员制定的方案填写" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="复查日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="复查日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疼痛评分：怎么填" prompt="0—10分；0表示无痛，未采集必须留空。 例：2" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疼痛评分：怎么填" prompt="0—10分；0表示无痛，未采集必须留空。 例：2" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练限制：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：避免跑跳" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练限制：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：避免跑跳" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="康复计划：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按专业人员制定的方案填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="康复计划：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按专业人员制定的方案填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="复查日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="复查日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/templates/竞迹统一数据导入模板.xlsx
+++ b/public/templates/竞迹统一数据导入模板.xlsx
@@ -23,1837 +23,6 @@
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
-</file>
-
-<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">系统运动员编号
-系统预填
-例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">姓名
-条件必填：没有系统编号，或新建人员时填写
-例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">评估日期
-条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
-例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">总分
-条件必填：填写专项耐力等竞技评价时提供真实总分｜分
-例：80（须按实际评分表打分）
-新增竞技状态记录需有依据的原始总分；单项一般耐力/核心力量评分可单独填写并注明评估协议，不能编造总分。 例：80（须按实际评分表打分）</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">评估协议
-评分标准：这些分数按哪张评分表打的
-条件必填：填一般耐力/核心力量评分时填写
-例：队内核心力量评分表（2026版）
-评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">等级
-选填
-例：建设
-仅填写实际已采集数据，未提供留空。 例：建设 可选：巅峰、良好、建设、调整</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">一般耐力评分
-选填｜分
-例：80（须按实际评分表打分）
-仅填写实际已采集数据，未提供留空。 例：80（须按实际评分表打分）</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">核心力量评分
-选填｜分
-例：75（须按实际评分表打分）
-仅填写实际已采集数据，未提供留空。 例：75（须按实际评分表打分）</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">专项耐力
-选填｜分
-例：按现有评分协议填写
-仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">力量爆发
-选填｜分
-例：按现有评分协议填写
-仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">技术效率
-选填｜分
-例：按现有评分协议填写
-仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">负荷适应
-选填｜分
-例：按现有评分协议填写
-仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">恢复能力
-选填｜分
-例：按现有评分协议填写
-仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">比赛能力
-选填｜分
-例：按现有评分协议填写
-仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">备注
-选填
-例：本次实测
-仅填写实际已采集数据，未提供留空。 例：本次实测</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">系统运动员编号
-系统预填
-例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">姓名
-条件必填：没有系统编号，或新建人员时填写
-例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">测试日期
-条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
-例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">测试项目
-本次测的项目：从中文下拉列表选择
-必填
-例：纵跳（cm）
-本次测的项目：从中文下拉列表选择。怎么填：例如测纵跳就选纵跳（cm），成绩45厘米就在数值列填45；单位由选项确定。例：纵跳（cm）。为什么：让成绩对应到正确的测试项目，系统自动处理内部编号。不知道时：先找身体测量、体能测试等现成工作表；下拉找不到时请管理员配置测试项目。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">数值
-必填｜指标字典单位
-例：45
-从下拉列表选择中文测试项目，单位随项目确定；一项测试一行，只填写实际成绩。 例：45</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">侧别
-条件必填：测左侧、右侧或双侧时填写
-例：左
-侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">测试类型
-选填
-例：专项测试
-仅填写实际已采集数据，未提供留空。 例：专项测试 可选：专项测试、体能测试、FMS测试、身体测量、竞技评估</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">协议
-测试方法：记录这个数值的实际测法
-选填
-例：纵跳摸高，测3次取最好成绩
-测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">备注
-选填
-例：本次实测
-仅填写实际已采集数据，未提供留空。 例：本次实测</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">测试时长分钟
-选填｜min
-例：12.5
-仅填写实际已采集数据，未提供留空。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">目标值
-选填｜与实测值同单位
-例：50
-仅填写实际已采集数据，未提供留空。 例：50</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">系统运动员编号
-系统预填
-例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">姓名
-条件必填：没有系统编号，或新建人员时填写
-例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">运动项目
-条件必填：未由当前项目、队伍预填时填写
-例：赛艇
-使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：赛艇 可选：游泳、马拉松游泳、花样游泳、跳水、水球、射箭、田径、羽毛球、棒球、垒球、篮球、三人篮球、拳击、激流、皮划艇、公路自行车、场地自行车、山地自行车、小轮车竞速、小轮车自由式、马术盛装舞步、马术三项赛、马术场地障碍、击剑、足球、高尔夫、竞技体操、艺术体操、蹦床、手球、曲棍球、柔道、空手道“型”、空手道“组手”、现代五项、赛艇、七人制橄榄球、帆船、射击、滑板、运动攀岩、冲浪、乒乓球、跆拳道、网球、铁人三项、排球、沙滩排球、举重、摔跤</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">所属队伍
-条件必填：未由当前项目、队伍预填时填写
-例：一队
-使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">性别
-选填
-例：男
-仅填写实际已采集数据，未提供留空。 例：男 可选：男、女</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">出生日期
-选填｜YYYY-MM-DD
-例：2026-10-01
-档案选填；不套用注册必填规则，不根据年龄反推生日。 例：2026-10-01</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">技术等级
-选填
-例：一级运动员
-仅填写实际已采集数据，未提供留空。 例：一级运动员 可选：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">备注
-选填
-例：本次实测
-仅填写实际已采集数据，未提供留空。 例：本次实测</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">省份
-选填
-例：浙江省
-仅填写实际已采集数据，未提供留空。 例：浙江省</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">城市
-选填
-例：杭州市
-仅填写实际已采集数据，未提供留空。 例：杭州市</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">区县
-选填
-例：西湖区
-仅填写实际已采集数据，未提供留空。 例：西湖区</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">民族
-选填
-例：汉族
-仅填写实际已采集数据，未提供留空。 例：汉族</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">手机号
-选填
-例：按实际号码填写
-仅填写实际已采集数据，未提供留空。 例：按实际号码填写</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">血型
-选填
-例：A
-仅填写实际已采集数据，未提供留空。 例：A 可选：A、B、AB、O</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">紧急联系人
-选填
-例：李某
-仅填写实际已采集数据，未提供留空。 例：李某</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">紧急电话
-选填
-例：按实际号码填写
-仅填写实际已采集数据，未提供留空。 例：按实际号码填写</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">学历
-选填
-例：本科
-仅填写实际已采集数据，未提供留空。 例：本科</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">位置号位
-选填
-例：1号位
-仅填写实际已采集数据，未提供留空。 例：1号位</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">身体状态
-选填
-例：健康
-仅填写实际已采集数据，未提供留空。 例：健康 可选：健康、观察、训练受限、康复中</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">最好成绩
-选填
-例：原始成绩及单位
-仅填写实际已采集数据，未提供留空。 例：原始成绩及单位</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">籍贯
-选填
-例：浙江杭州
-仅填写实际已采集数据，未提供留空。 例：浙江杭州</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">家庭住址
-选填
-例：实际联系地址
-仅填写实际已采集数据，未提供留空。 例：实际联系地址</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">训练状态
-选填
-例：在训
-仅填写实际已采集数据，未提供留空。 例：在训 可选：在训、集训、休整、离队</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="X3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">开始运动日期
-选填｜YYYY-MM-DD
-例：2026-10-01
-仅填写实际已采集数据，未提供留空。 例：2026-10-01</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">训练场地
-选填
-例：训练中心
-仅填写实际已采集数据，未提供留空。 例：训练中心</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Z3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">备战赛事
-选填
-例：实际赛事名称
-仅填写实际已采集数据，未提供留空。 例：实际赛事名称</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AA3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">备战阶段
-选填
-例：基础期
-仅填写实际已采集数据，未提供留空。 例：基础期</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AB3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">集训时间
-选填
-例：2026-10-01至2026-10-15
-仅填写实际已采集数据，未提供留空。 例：2026-10-01至2026-10-15</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AC3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">输送地
-选填
-例：杭州
-仅填写实际已采集数据，未提供留空。 例：杭州</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AD3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">输送单位
-选填
-例：实际单位名称
-仅填写实际已采集数据，未提供留空。 例：实际单位名称</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AE3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">输送教练
-选填
-例：王某
-仅填写实际已采集数据，未提供留空。 例：王某</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AF3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">优势项
-选填
-例：专项耐力
-仅填写实际已采集数据，未提供留空。 例：专项耐力</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">系统运动员编号
-系统预填
-例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">姓名
-条件必填：没有系统编号，或新建人员时填写
-例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">测量日期
-条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
-例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">体重kg
-选填｜kg
-例：75
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：75</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">身高cm
-选填｜cm
-例：180
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：180</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">臂展cm
-选填｜cm
-例：185
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：185</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">体脂率%
-选填｜%
-例：15
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：15</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">骨骼肌kg
-选填｜kg
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">肌肉量kg
-选填｜kg
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">上肢肌肉kg
-选填｜kg
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">下肢肌肉kg
-选填｜kg
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">躯干肌肉kg
-选填｜kg
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">皮下脂肪mm
-选填｜mm
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">肱三头肌皮褶mm
-选填｜mm
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">腹部皮褶mm
-选填｜mm
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">大腿皮褶mm
-选填｜mm
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">小腿皮褶mm
-选填｜mm
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">内脏脂肪等级
-选填
-例：5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">基础代谢kcal
-选填｜kcal
-例：1800
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：1800</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">总水分kg
-选填｜kg
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">细胞外水比
-选填
-例：0.38
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：0.38</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">相位角°
-选填｜°
-例：6
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：6</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">内脏脂肪面积cm²
-选填｜cm²
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="X3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">左上肢瘦体重kg
-选填｜kg
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">右上肢瘦体重kg
-选填｜kg
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Z3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">躯干瘦体重kg
-选填｜kg
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AA3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">左下肢瘦体重kg
-选填｜kg
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AB3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">右下肢瘦体重kg
-选填｜kg
-例：12.5
-本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AC3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">备注
-选填
-例：本次实测
-仅填写实际已采集数据，未提供留空。 例：本次实测</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">系统运动员编号
-系统预填
-例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">姓名
-条件必填：没有系统编号，或新建人员时填写
-例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">测试日期
-条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
-例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">测试协议
-测试方法：这个结果是怎样测出来的
-条件必填：填不对称指数时必须写明测法
-例：测力台单腿跳测试（按设备报告）
-测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">VO2Max
-选填｜ml/kg/min
-例：55
-本表至少一项实测成绩；不得以0代表未测。 例：55</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">CMJ峰值功率W
-选填｜W
-例：3000
-本表至少一项实测成绩；不得以0代表未测。 例：3000</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">无氧功率W/kg
-选填｜W/kg
-例：12
-本表至少一项实测成绩；不得以0代表未测。 例：12</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">IMTP峰值力量N
-选填｜N
-例：2000
-本表至少一项实测成绩；不得以0代表未测。 例：2000</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">不对称指数%
-选填｜%
-例：8
-本表至少一项实测成绩；不得以0代表未测。 例：8</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">备注
-选填
-例：本次实测
-仅填写实际已采集数据，未提供留空。 例：本次实测</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">系统运动员编号
-系统预填
-例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">姓名
-条件必填：没有系统编号，或新建人员时填写
-例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">测试日期
-条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
-例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">深蹲
-选填｜分
-例：2
-整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">跨栏步
-选填｜分
-例：2
-整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">直线弓步蹲
-选填｜分
-例：2
-整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">肩部灵活性
-选填｜分
-例：2
-整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">主动直腿上抬
-选填｜分
-例：2
-整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">躯干稳定俯卧撑
-选填｜分
-例：2
-整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">旋转稳定性
-选填｜分
-例：2
-整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">备注
-选填
-例：本次实测
-仅填写实际已采集数据，未提供留空。 例：本次实测</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">系统运动员编号
-系统预填
-例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">姓名
-条件必填：没有系统编号，或新建人员时填写
-例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">日期
-条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
-例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">课次序号
-条件必填：同一人同一天有多次训练时填写
-例：1
-同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">时长分钟
-条件必填：时长、距离至少填一项｜min
-例：60
-时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：60</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">距离千米
-条件必填：时长、距离至少填一项｜km
-例：12.5
-时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">开始时间
-选填｜HH:mm
-例：08:30
-仅填写实际已采集数据，未提供留空。 例：08:30</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">训练类型
-选填
-例：基础力量
-仅填写实际已采集数据，未提供留空。 例：基础力量</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">训练内容
-选填
-例：水上耐力训练
-仅填写实际已采集数据，未提供留空。 例：水上耐力训练</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">RPE
-主观用力程度：运动员觉得这次训练有多累
-选填
-例：6
-主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">训练阶段
-选填
-例：基础期
-仅填写实际已采集数据，未提供留空。 例：基础期</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">强度区间
-原训练记录采用的强度分区
-选填
-例：U2
-原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">SRPE
-本次训练负荷：系统用时长和RPE计算
-选填｜AU
-例：360
-本次训练负荷：系统用时长和RPE计算。怎么填：日常不用填。填写训练时长和RPE后由系统计算；只有已有外部原始负荷值时才补这列。例：360。为什么：用于记录训练负荷，公式为分钟数×RPE。不知道时：没有外部原始值就留空；缺RPE时也不用自己估算。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">SMVL
-力量训练量：系统汇总实际次数和重量
-选填｜kg·次
-例：360
-力量训练量：系统汇总实际次数和重量。怎么填：日常不用填，逐组填写实际次数和实际重量；只有外部记录已给出整课总量时才补本列。例：360。为什么：用于汇总力量训练完成量；计划重量不能当成实际重量。不知道时：不知道整课总量就留空，不必手算，也不要填0占位。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">平均心率
-选填｜bpm
-例：140
-仅填写实际已采集数据，未提供留空。 例：140</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">最大心率
-选填｜bpm
-例：175
-仅填写实际已采集数据，未提供留空。 例：175</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">平均功率W
-选填｜W
-例：12.5
-仅填写实际已采集数据，未提供留空。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">桨频SPM
-选填｜SPM
-例：22
-仅填写实际已采集数据，未提供留空。 例：22</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">系统运动员编号
-系统预填
-例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">姓名
-条件必填：没有系统编号，或新建人员时填写
-例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">日期
-条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
-例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">课次序号
-条件必填：同一人同一天有多次训练时填写
-例：1
-同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">动作
-必填
-例：深蹲
-填写实际记录。 例：深蹲</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">组序
-条件必填：同一动作做了多组时填写
-例：1
-同动作多组必须区分组序；仅一组可默认1。 例：1</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">实际次数
-必填｜次
-例：6
-填写实际记录。 例：6</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">实际重量kg
-必填｜kg
-例：60
-真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">课次名称
-选填
-例：上午力量
-仅填写实际已采集数据，未提供留空。 例：上午力量</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">RPE
-主观用力程度：运动员觉得这次训练有多累
-选填
-例：6
-主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">完成状态
-选填
-例：已完成
-仅填写实际已采集数据，未提供留空。 例：已完成 可选：已完成、未完成</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">备注
-选填
-例：本次实测
-仅填写实际已采集数据，未提供留空。 例：本次实测</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">计划次数
-选填｜次
-例：6
-仅填写实际已采集数据，未提供留空。 例：6</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">强度百分比
-按原训练记录给出的强度百分比
-选填｜%
-例：80
-按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">类别
-选填
-例：基础力量
-仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">身体部位
-选填
-例：下肢
-仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">动作代码
-选填
-例：squat
-仅填写实际已采集数据，未提供留空。 例：squat</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">计划重量kg
-选填｜kg
-例：60
-仅填写实际已采集数据，未提供留空。 例：60</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">训练环境
-选填
-例：陆上
-仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">组次时长分钟
-选填｜min
-例：12.5
-仅填写实际已采集数据，未提供留空。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">组次距离千米
-选填｜km
-例：12.5
-仅填写实际已采集数据，未提供留空。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">强度区间
-原训练记录采用的强度分区
-选填
-例：U2
-原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">系统运动员编号
-系统预填
-例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">姓名
-条件必填：没有系统编号，或新建人员时填写
-例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">日期
-条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
-例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">睡眠小时
-选填｜h
-例：8
-仅填写实际已采集数据，未提供留空。 例：8</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">睡眠质量
-选填｜分
-例：4
-0—10分，越高越好；仅填本人实际报告。 例：4</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">疲劳
-选填｜分
-例：2
-0—10分，越高越严重；仅填本人实际报告。 例：2</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">肌肉酸痛
-选填｜分
-例：2
-0—10分，越高越严重；仅填本人实际报告。 例：2</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">情绪
-选填｜分
-例：4
-0—10分，越高越好；仅填本人实际报告。 例：4</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">晨脉
-选填｜bpm
-例：55
-仅填写实际已采集数据，未提供留空。 例：55</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">体重kg
-选填｜kg
-例：75
-仅填写实际已采集数据，未提供留空。 例：75</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">状态
-选填
-例：正常
-从下拉选择正常、休息、关注、警报或缺失；至少一项恢复数值或状态，不能仅备注。 例：正常 可选：正常、休息、关注、警报、缺失</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">备注
-选填
-例：本次实测
-仅填写实际已采集数据，未提供留空。 例：本次实测</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">系统运动员编号
-系统预填
-例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">姓名
-条件必填：没有系统编号，或新建人员时填写
-例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">发生日期
-条件必填：上传时未选统一日期，就在本列填日期｜YYYY-MM-DD
-例：2026-10-01
-本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">伤病名称
-必填
-例：踝关节扭伤
-填写实际记录。 例：踝关节扭伤</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">部位
-必填
-例：踝关节
-填写实际记录。 例：踝关节</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">侧别
-选填
-例：左
-仅填写实际已采集数据，未提供留空。 例：左 可选：左、右、双侧、未指定</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">状态
-选填
-例：观察
-空白新增时沿用观察状态，不自动推断诊断。 例：观察 可选：健康、观察、限训、康复、停训</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">疼痛评分
-选填｜分
-例：2
-0—10分；0表示无痛，未采集必须留空。 例：2</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">训练限制
-选填
-例：避免跑跳
-仅填写实际已采集数据，未提供留空。 例：避免跑跳</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">备注
-选填
-例：本次实测
-仅填写实际已采集数据，未提供留空。 例：本次实测</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">康复计划
-选填
-例：按专业人员制定的方案填写
-仅填写实际已采集数据，未提供留空。 例：按专业人员制定的方案填写</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">复查日期
-选填｜YYYY-MM-DD
-例：2026-10-01
-仅填写实际已采集数据，未提供留空。 例：2026-10-01</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1898,10 +67,10 @@
     <t>11. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
   </si>
   <si>
-    <t>12. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
+    <t>12. 表头写明何时填写、通俗解释和填写示例，不设置单元格弹出提示或批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
   </si>
   <si>
-    <t>13. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
+    <t>13. 必填条件见表头。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
   </si>
   <si>
     <t>14. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
@@ -1910,7 +79,7 @@
     <t>运动员基本资料</t>
   </si>
   <si>
-    <t>建档需姓名、运动项目和所属队伍；编号供已有人员匹配，出生日期等资料选填。已有人员导入不调队。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
+    <t>建档需姓名、运动项目和所属队伍；编号供已有人员匹配，出生日期等资料选填。已有人员导入不调队。 必填项在前，选填项在后；所有数据列直接显示，按需填写。填写要求见表头。</t>
   </si>
   <si>
     <t xml:space="preserve">系统运动员编号
@@ -2076,7 +245,7 @@
     <t>身体测量</t>
   </si>
   <si>
-    <t>每人每次测量一行；身高、臂展、体重及身体成分按实测填写，不要在其它表重复填写。档案展示最近有效值。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
+    <t>每人每次测量一行；身高、臂展、体重及身体成分按实测填写，不要在其它表重复填写。档案展示最近有效值。 必填项在前，选填项在后；所有数据列直接显示，按需填写。填写要求见表头。</t>
   </si>
   <si>
     <t xml:space="preserve">测量日期
@@ -2212,7 +381,7 @@
     <t>体能测试</t>
   </si>
   <si>
-    <t>每人每次测试一行；只填已测成绩，并填写测试协议；不对称指数须注明测试方法。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
+    <t>每人每次测试一行；只填已测成绩，并填写测试协议；不对称指数须注明测试方法。 必填项在前，选填项在后；所有数据列直接显示，按需填写。填写要求见表头。</t>
   </si>
   <si>
     <t xml:space="preserve">测试日期
@@ -2254,7 +423,7 @@
     <t>FMS测试</t>
   </si>
   <si>
-    <t>每项填写0、1、2或3，未测留空；合计由系统计算，七项未齐不视为完整总分。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
+    <t>每项填写0、1、2或3，未测留空；合计由系统计算，七项未齐不视为完整总分。 必填项在前，选填项在后；所有数据列直接显示，按需填写。填写要求见表头。</t>
   </si>
   <si>
     <t xml:space="preserve">深蹲
@@ -2295,7 +464,7 @@
     <t>训练课次</t>
   </si>
   <si>
-    <t>每人每课一行，时长与距离至少填写一项；仅承载已填力量组次的课次可同时留空。强度未测留空；SRPE未填时仅按已填时长×RPE计算。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
+    <t>每人每课一行，时长与距离至少填写一项；仅承载已填力量组次的课次可同时留空。强度未测留空；SRPE未填时仅按已填时长×RPE计算。 必填项在前，选填项在后；所有数据列直接显示，按需填写。填写要求见表头。</t>
   </si>
   <si>
     <t xml:space="preserve">日期
@@ -2385,7 +554,7 @@
     <t>力量训练组次</t>
   </si>
   <si>
-    <t>每人每动作每组一行；课次序号与训练课次表一致，旧文件缺省时仅唯一课次可自动关联。实际次数和实际重量必填；完成状态填0/1或未完成/已完成，其他字段按实填写。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
+    <t>每人每动作每组一行；课次序号与训练课次表一致，旧文件缺省时仅唯一课次可自动关联。实际次数和实际重量必填；完成状态填0/1或未完成/已完成，其他字段按实填写。 必填项在前，选填项在后；所有数据列直接显示，按需填写。填写要求见表头。</t>
   </si>
   <si>
     <t xml:space="preserve">动作
@@ -2467,7 +636,7 @@
     <t>每日恢复</t>
   </si>
   <si>
-    <t>每日每人一行；只填写实际采集值。每日体重不覆盖身体测量历史。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
+    <t>每日每人一行；只填写实际采集值。每日体重不覆盖身体测量历史。 必填项在前，选填项在后；所有数据列直接显示，按需填写。填写要求见表头。</t>
   </si>
   <si>
     <t xml:space="preserve">睡眠小时
@@ -2508,7 +677,7 @@
     <t>伤病记录</t>
   </si>
   <si>
-    <t>每次伤病一行；按实际情况填写发生日期、名称、部位及状态。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
+    <t>每次伤病一行；按实际情况填写发生日期、名称、部位及状态。 必填项在前，选填项在后；所有数据列直接显示，按需填写。填写要求见表头。</t>
   </si>
   <si>
     <t xml:space="preserve">发生日期
@@ -2559,7 +728,7 @@
     <t>竞技评估</t>
   </si>
   <si>
-    <t>选填：只记录有依据的人工评价；一般耐力、核心力量评分须填写评估协议，不虚构总分。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
+    <t>选填：只记录有依据的人工评价；一般耐力、核心力量评分须填写评估协议，不虚构总分。 必填项在前，选填项在后；所有数据列直接显示，按需填写。填写要求见表头。</t>
   </si>
   <si>
     <t xml:space="preserve">评估日期
@@ -2626,7 +795,7 @@
     <t>其他测试</t>
   </si>
   <si>
-    <t>选择中文测试项目，再填实测成绩；单位已在选项中，无需填写代码。一项测试一行，未测不填0。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
+    <t>选择中文测试项目，再填实测成绩；单位已在选项中，无需填写代码。一项测试一行，未测不填0。 必填项在前，选填项在后；所有数据列直接显示，按需填写。填写要求见表头。</t>
   </si>
   <si>
     <t xml:space="preserve">测试项目
@@ -5503,101 +3672,28 @@
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
   </mergeCells>
-  <dataValidations count="30">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+  <dataValidations count="6">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:E503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:E503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：巅峰、良好、建设、调整" sqref="F10:F503">
+      <formula1>"巅峰,良好,建设,调整"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：巅峰、良好、建设、调整" sqref="F4:F503">
+      <formula1>"巅峰,良好,建设,调整"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:O503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总分：怎么填" prompt="新增竞技状态记录需有依据的原始总分；单项一般耐力/核心力量评分可单独填写并注明评估协议，不能编造总分。 例：80（须按实际评分表打分）" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总分：怎么填" prompt="新增竞技状态记录需有依据的原始总分；单项一般耐力/核心力量评分可单独填写并注明评估协议，不能编造总分。 例：80（须按实际评分表打分）" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估协议：怎么填" prompt="评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="评估协议：怎么填" prompt="评分标准：这些分数按哪张评分表打的。什么时候填：填一般耐力/核心力量评分时填写。怎么填：写实际使用的评分表名称，有年份或版本就一起写；不是让你签协议或上传文件。例：队内核心力量评分表（2026版）。为什么：同样80分，按不同评分表打分，含义可能不同；需要保留打分依据。不知道时：没有评分标准时，本列和对应评分都留空；实测成绩填到体能测试或其他测试，不要编造评分表。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：建设 可选：巅峰、良好、建设、调整" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：巅峰、良好、建设、调整" sqref="F10:F503">
-      <formula1>"巅峰,良好,建设,调整"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：建设 可选：巅峰、良好、建设、调整" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：巅峰、良好、建设、调整" sqref="F4:F503">
-      <formula1>"巅峰,良好,建设,调整"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="一般耐力评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：80（须按实际评分表打分）" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="一般耐力评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：80（须按实际评分表打分）" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="核心力量评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75（须按实际评分表打分）" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="核心力量评分：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75（须按实际评分表打分）" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="专项耐力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="专项耐力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="力量爆发：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="力量爆发：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="技术效率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="技术效率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="负荷适应：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="负荷适应：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="恢复能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="恢复能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="比赛能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="比赛能力：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按现有评分协议填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:O503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7685,77 +5781,46 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <dataValidations count="22">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+  <dataValidations count="12">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:C503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:C503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请从下拉列表选择；找不到选项时请核对项目或联系管理员。" sqref="D10:D503">
+      <formula1>_JINGJI_TEST_NAMES</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请从下拉列表选择；找不到选项时请核对项目或联系管理员。" sqref="D4:D503">
+      <formula1>_JINGJI_TEST_NAMES</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="F10:F503">
+      <formula1>"左,右,双侧,中央"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="F4:F503">
+      <formula1>"左,右,双侧,中央"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：专项测试、体能测试、FMS测试、身体测量、竞技评估" sqref="G10:G503">
+      <formula1>"专项测试,体能测试,FMS测试,身体测量,竞技评估"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：专项测试、体能测试、FMS测试、身体测量、竞技评估" sqref="G4:G503">
+      <formula1>"专项测试,体能测试,FMS测试,身体测量,竞技评估"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:K503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="测试项目：怎么填" prompt="本次测的项目：从中文下拉列表选择。怎么填：例如测纵跳就选纵跳（cm），成绩45厘米就在数值列填45；单位由选项确定。例：纵跳（cm）。为什么：让成绩对应到正确的测试项目，系统自动处理内部编号。不知道时：先找身体测量、体能测试等现成工作表；下拉找不到时请管理员配置测试项目。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请从下拉列表选择；找不到选项时请核对项目或联系管理员。" sqref="D10:D503">
-      <formula1>_JINGJI_TEST_NAMES</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="测试项目：怎么填" prompt="本次测的项目：从中文下拉列表选择。怎么填：例如测纵跳就选纵跳（cm），成绩45厘米就在数值列填45；单位由选项确定。例：纵跳（cm）。为什么：让成绩对应到正确的测试项目，系统自动处理内部编号。不知道时：先找身体测量、体能测试等现成工作表；下拉找不到时请管理员配置测试项目。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请从下拉列表选择；找不到选项时请核对项目或联系管理员。" sqref="D4:D503">
-      <formula1>_JINGJI_TEST_NAMES</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="从下拉列表选择中文测试项目，单位随项目确定；一项测试一行，只填写实际成绩。 例：45" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="数值：怎么填" prompt="从下拉列表选择中文测试项目，单位随项目确定；一项测试一行，只填写实际成绩。 例：45" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="F10:F503">
-      <formula1>"左,右,双侧,中央"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="侧别指标按实际方法填写；普通中央指标可留空，按既有规则处理。 例：左 可选：左、右、双侧、中央" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：左、右、双侧、中央" sqref="F4:F503">
-      <formula1>"左,右,双侧,中央"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试 可选：专项测试、体能测试、FMS测试、身体测量、竞技评估" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：专项测试、体能测试、FMS测试、身体测量、竞技评估" sqref="G10:G503">
-      <formula1>"专项测试,体能测试,FMS测试,身体测量,竞技评估"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="测试类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项测试 可选：专项测试、体能测试、FMS测试、身体测量、竞技评估" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：专项测试、体能测试、FMS测试、身体测量、竞技评估" sqref="G4:G503">
-      <formula1>"专项测试,体能测试,FMS测试,身体测量,竞技评估"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="协议：怎么填" prompt="测试方法：记录这个数值的实际测法。怎么填：写原记录里的测试步骤或方法名称，不是合同，也不是接口协议。例：纵跳摸高，测3次取最好成绩。为什么：让以后查看成绩的人知道这次怎么测，避免把不同测法直接当成相同测试。不知道时：不知道可先留空；若该项校验要求测法，向测试人员确认，不要猜。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="目标值：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：50" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="目标值：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：50" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:K503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -11965,203 +10030,94 @@
     <mergeCell ref="A1:AF1"/>
     <mergeCell ref="A2:AF2"/>
   </mergeCells>
-  <dataValidations count="64">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+  <dataValidations count="28">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:B503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:B503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA10:AA503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA10:AF503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA4:AA503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA4:AF503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="集训时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01至2026-10-15" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB10:AB503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：游泳、马拉松游泳、花样游泳、跳水、水球、射箭、田径、羽毛球、棒球、垒球、篮球、三人篮球、拳击、激流、皮划艇、公路自行车、场地自行车、山地自行车、小轮车竞速、小轮车自由式、马术盛装舞步、马术三项赛、马术场地障碍、击剑、足球、高尔夫、竞技体操、艺术体操、蹦床、手球、曲棍球、柔道、空手道“型”、空手道“组手”、现代五项、赛艇、七人制橄榄球、帆船、射击、滑板、运动攀岩、冲浪、乒乓球、跆拳道、网球、铁人三项、排球、沙滩排球、举重、摔跤" sqref="C10:C503">
+      <formula1>"游泳,马拉松游泳,花样游泳,跳水,水球,射箭,田径,羽毛球,棒球,垒球,篮球,三人篮球,拳击,激流,皮划艇,公路自行车,场地自行车,山地自行车,小轮车竞速,小轮车自由式,马术盛装舞步,马术三项赛,马术场地障碍,击剑,足球,高尔夫,竞技体操,艺术体操,蹦床,手球,曲棍球,柔道,空手道“型”,空手道“组手”,现代五项,赛艇,七人制橄榄球,帆船,射击,滑板,运动攀岩,冲浪,乒乓球,跆拳道,网球,铁人三项,排球,沙滩排球,举重,摔跤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：游泳、马拉松游泳、花样游泳、跳水、水球、射箭、田径、羽毛球、棒球、垒球、篮球、三人篮球、拳击、激流、皮划艇、公路自行车、场地自行车、山地自行车、小轮车竞速、小轮车自由式、马术盛装舞步、马术三项赛、马术场地障碍、击剑、足球、高尔夫、竞技体操、艺术体操、蹦床、手球、曲棍球、柔道、空手道“型”、空手道“组手”、现代五项、赛艇、七人制橄榄球、帆船、射击、滑板、运动攀岩、冲浪、乒乓球、跆拳道、网球、铁人三项、排球、沙滩排球、举重、摔跤" sqref="C4:C503">
+      <formula1>"游泳,马拉松游泳,花样游泳,跳水,水球,射箭,田径,羽毛球,棒球,垒球,篮球,三人篮球,拳击,激流,皮划艇,公路自行车,场地自行车,山地自行车,小轮车竞速,小轮车自由式,马术盛装舞步,马术三项赛,马术场地障碍,击剑,足球,高尔夫,竞技体操,艺术体操,蹦床,手球,曲棍球,柔道,空手道“型”,空手道“组手”,现代五项,赛艇,七人制橄榄球,帆船,射击,滑板,运动攀岩,冲浪,乒乓球,跆拳道,网球,铁人三项,排球,沙滩排球,举重,摔跤"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="集训时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01至2026-10-15" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB4:AB503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC10:AC503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：男、女" sqref="E10:E503">
+      <formula1>"男,女"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：男、女" sqref="E4:E503">
+      <formula1>"男,女"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC4:AC503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送单位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际单位名称" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AD10:AD503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" sqref="G10:G503">
+      <formula1>"未定级,国际级运动健将,运动健将,一级运动员,二级运动员,三级运动员"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" sqref="G4:G503">
+      <formula1>"未定级,国际级运动健将,运动健将,一级运动员,二级运动员,三级运动员"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:M503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送单位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际单位名称" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AD4:AD503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:M503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送教练：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：王某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AE10:AE503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：A、B、AB、O" sqref="N10:N503">
+      <formula1>"A,B,AB,O"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：A、B、AB、O" sqref="N4:N503">
+      <formula1>"A,B,AB,O"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:R503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="输送教练：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：王某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AE4:AE503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:R503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="优势项：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项耐力" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AF10:AF503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：健康、观察、训练受限、康复中" sqref="S10:S503">
+      <formula1>"健康,观察,训练受限,康复中"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：健康、观察、训练受限、康复中" sqref="S4:S503">
+      <formula1>"健康,观察,训练受限,康复中"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:V503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="优势项：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：专项耐力" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AF4:AF503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:V503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：在训、集训、休整、离队" sqref="W10:W503">
+      <formula1>"在训,集训,休整,离队"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：在训、集训、休整、离队" sqref="W4:W503">
+      <formula1>"在训,集训,休整,离队"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X10:AF503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="运动项目：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：赛艇 可选：游泳、马拉松游泳、花样游泳、跳水、水球、射箭、田径、羽毛球、棒球、垒球、篮球、三人篮球、拳击、激流、皮划艇、公路自行车、场地自行车、山地自行车、小轮车竞速、小轮车自由式、马术盛装舞步、马术三项赛、马术场地障碍、击剑、足球、高尔夫、竞技体操、艺术体操、蹦床、手球、曲棍球、柔道、空手道“型”、空手道“组手”、现代五项、赛艇、七人制橄榄球、帆船、射击、滑板、运动攀岩、冲浪、乒乓球、跆拳道、网球、铁人三项、排球、沙滩排球、举重" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：游泳、马拉松游泳、花样游泳、跳水、水球、射箭、田径、羽毛球、棒球、垒球、篮球、三人篮球、拳击、激流、皮划艇、公路自行车、场地自行车、山地自行车、小轮车竞速、小轮车自由式、马术盛装舞步、马术三项赛、马术场地障碍、击剑、足球、高尔夫、竞技体操、艺术体操、蹦床、手球、曲棍球、柔道、空手道“型”、空手道“组手”、现代五项、赛艇、七人制橄榄球、帆船、射击、滑板、运动攀岩、冲浪、乒乓球、跆拳道、网球、铁人三项、排球、沙滩排球、举重、摔跤" sqref="C10:C503">
-      <formula1>"游泳,马拉松游泳,花样游泳,跳水,水球,射箭,田径,羽毛球,棒球,垒球,篮球,三人篮球,拳击,激流,皮划艇,公路自行车,场地自行车,山地自行车,小轮车竞速,小轮车自由式,马术盛装舞步,马术三项赛,马术场地障碍,击剑,足球,高尔夫,竞技体操,艺术体操,蹦床,手球,曲棍球,柔道,空手道“型”,空手道“组手”,现代五项,赛艇,七人制橄榄球,帆船,射击,滑板,运动攀岩,冲浪,乒乓球,跆拳道,网球,铁人三项,排球,沙滩排球,举重,摔跤"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="运动项目：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：赛艇 可选：游泳、马拉松游泳、花样游泳、跳水、水球、射箭、田径、羽毛球、棒球、垒球、篮球、三人篮球、拳击、激流、皮划艇、公路自行车、场地自行车、山地自行车、小轮车竞速、小轮车自由式、马术盛装舞步、马术三项赛、马术场地障碍、击剑、足球、高尔夫、竞技体操、艺术体操、蹦床、手球、曲棍球、柔道、空手道“型”、空手道“组手”、现代五项、赛艇、七人制橄榄球、帆船、射击、滑板、运动攀岩、冲浪、乒乓球、跆拳道、网球、铁人三项、排球、沙滩排球、举重" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：游泳、马拉松游泳、花样游泳、跳水、水球、射箭、田径、羽毛球、棒球、垒球、篮球、三人篮球、拳击、激流、皮划艇、公路自行车、场地自行车、山地自行车、小轮车竞速、小轮车自由式、马术盛装舞步、马术三项赛、马术场地障碍、击剑、足球、高尔夫、竞技体操、艺术体操、蹦床、手球、曲棍球、柔道、空手道“型”、空手道“组手”、现代五项、赛艇、七人制橄榄球、帆船、射击、滑板、运动攀岩、冲浪、乒乓球、跆拳道、网球、铁人三项、排球、沙滩排球、举重、摔跤" sqref="C4:C503">
-      <formula1>"游泳,马拉松游泳,花样游泳,跳水,水球,射箭,田径,羽毛球,棒球,垒球,篮球,三人篮球,拳击,激流,皮划艇,公路自行车,场地自行车,山地自行车,小轮车竞速,小轮车自由式,马术盛装舞步,马术三项赛,马术场地障碍,击剑,足球,高尔夫,竞技体操,艺术体操,蹦床,手球,曲棍球,柔道,空手道“型”,空手道“组手”,现代五项,赛艇,七人制橄榄球,帆船,射击,滑板,运动攀岩,冲浪,乒乓球,跆拳道,网球,铁人三项,排球,沙滩排球,举重,摔跤"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="所属队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="所属队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="性别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男 可选：男、女" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：男、女" sqref="E10:E503">
-      <formula1>"男,女"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="性别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男 可选：男、女" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：男、女" sqref="E4:E503">
-      <formula1>"男,女"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="出生日期：怎么填" prompt="档案选填；不套用注册必填规则，不根据年龄反推生日。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="出生日期：怎么填" prompt="档案选填；不套用注册必填规则，不根据年龄反推生日。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="技术等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：一级运动员 可选：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" sqref="G10:G503">
-      <formula1>"未定级,国际级运动健将,运动健将,一级运动员,二级运动员,三级运动员"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="技术等级：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：一级运动员 可选：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：未定级、国际级运动健将、运动健将、一级运动员、二级运动员、三级运动员" sqref="G4:G503">
-      <formula1>"未定级,国际级运动健将,运动健将,一级运动员,二级运动员,三级运动员"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="省份：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江省" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="省份：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江省" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="城市：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州市" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="城市：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：杭州市" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="区县：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：西湖区" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="区县：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：西湖区" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="民族：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：汉族" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="民族：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：汉族" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="手机号：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="手机号：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="血型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：A 可选：A、B、AB、O" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：A、B、AB、O" sqref="N10:N503">
-      <formula1>"A,B,AB,O"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="血型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：A 可选：A、B、AB、O" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：A、B、AB、O" sqref="N4:N503">
-      <formula1>"A,B,AB,O"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急联系人：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：李某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急联系人：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：李某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急电话：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P10:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="紧急电话：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按实际号码填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P4:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="学历：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本科" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="学历：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本科" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="位置号位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：1号位" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="位置号位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：1号位" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：健康 可选：健康、观察、训练受限、康复中" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：健康、观察、训练受限、康复中" sqref="S10:S503">
-      <formula1>"健康,观察,训练受限,康复中"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：健康 可选：健康、观察、训练受限、康复中" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：健康、观察、训练受限、康复中" sqref="S4:S503">
-      <formula1>"健康,观察,训练受限,康复中"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最好成绩：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：原始成绩及单位" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最好成绩：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：原始成绩及单位" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="籍贯：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江杭州" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="籍贯：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：浙江杭州" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="家庭住址：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际联系地址" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V10:V503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="家庭住址：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际联系地址" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V4:V503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：在训 可选：在训、集训、休整、离队" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：在训、集训、休整、离队" sqref="W10:W503">
-      <formula1>"在训,集训,休整,离队"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：在训 可选：在训、集训、休整、离队" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：在训、集训、休整、离队" sqref="W4:W503">
-      <formula1>"在训,集训,休整,离队"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始运动日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X10:X503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始运动日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X4:X503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：训练中心" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y10:Y503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场地：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：训练中心" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y4:Y503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战赛事：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际赛事名称" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z10:Z503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备战赛事：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：实际赛事名称" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z4:Z503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X4:AF503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -14338,185 +12294,16 @@
     <mergeCell ref="A1:AC1"/>
     <mergeCell ref="A2:AC2"/>
   </mergeCells>
-  <dataValidations count="58">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:AC503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA10:AA503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AA4:AA503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB10:AB503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右下肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AB4:AB503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC10:AC503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="AC4:AC503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测量日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测量日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：75" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：75" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="身高cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：180" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="身高cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：180" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="臂展cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：185" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="臂展cm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：185" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体脂率%：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：15" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体脂率%：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：15" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="骨骼肌kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="骨骼肌kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉量kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉量kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="上肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="上肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="下肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="下肢肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干肌肉kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="皮下脂肪mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="皮下脂肪mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肱三头肌皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肱三头肌皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="腹部皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="腹部皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="大腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P10:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="大腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P4:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="小腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="小腿皮褶mm：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪等级：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪等级：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="基础代谢kcal：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：1800" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S10:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="基础代谢kcal：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：1800" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S4:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总水分kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="总水分kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="细胞外水比：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：0.38" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="细胞外水比：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：0.38" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="相位角°：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V10:V503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="相位角°：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V4:V503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪面积cm²：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W10:W503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="内脏脂肪面积cm²：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="W4:W503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X10:X503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="左上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="X4:X503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y10:Y503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="右上肢瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Y4:Y503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z10:Z503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="躯干瘦体重kg：怎么填" prompt="本表至少填写一项实测指标，未测留空；不要与每日体重重复作为同一事实填报。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Z4:Z503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:AC503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -16599,71 +14386,16 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <dataValidations count="20">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:J503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试协议：怎么填" prompt="测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试协议：怎么填" prompt="测试方法：这个结果是怎样测出来的。什么时候填：填不对称指数时必须写明测法。怎么填：写实际做的测试、使用的设备或报告中的方法名称；有版本再写版本，不必编版本号。例：测力台单腿跳测试（按设备报告）。为什么：帮助判断两次成绩是否采用同一种测法；不对称指数尤其需要说明测法。不知道时：先查看原检测报告或询问测试人员。填不对称指数却不清楚测法时，先不填该指数；其他已知成绩可保留。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="VO2Max：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：55" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="VO2Max：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：55" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="CMJ峰值功率W：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：3000" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="CMJ峰值功率W：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：3000" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="无氧功率W/kg：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：12" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="无氧功率W/kg：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：12" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="IMTP峰值力量N：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：2000" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="IMTP峰值力量N：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：2000" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="不对称指数%：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：8" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="不对称指数%：怎么填" prompt="本表至少一项实测成绩；不得以0代表未测。 例：8" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:J503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -18750,77 +16482,28 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <dataValidations count="22">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+  <dataValidations count="6">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:C503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:C503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="D10:J503">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="D4:J503">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="测试日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="深蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="D10:D503">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="深蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="D4:D503">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="跨栏步：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="E10:E503">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="跨栏步：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="E4:E503">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="直线弓步蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="F10:F503">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="直线弓步蹲：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="F4:F503">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="肩部灵活性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="G10:G503">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="肩部灵活性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="G4:G503">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="主动直腿上抬：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="H10:H503">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="主动直腿上抬：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="H4:H503">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="躯干稳定俯卧撑：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="I10:I503">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="躯干稳定俯卧撑：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="I4:I503">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="旋转稳定性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="J10:J503">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="旋转稳定性：怎么填" prompt="整数0—3，未测留空；至少一项；七项齐全才生成完整21分制总分。 例：2 可选：0、1、2、3" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：0、1、2、3" sqref="J4:J503">
-      <formula1>"0,1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -20943,119 +18626,28 @@
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:R2"/>
   </mergeCells>
-  <dataValidations count="36">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+  <dataValidations count="6">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:K503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:K503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="L10:L503">
+      <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="L4:L503">
+      <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:R503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="时长分钟：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="时长分钟：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="距离千米：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="距离千米：怎么填" prompt="时长或距离至少一项；仅承载有效力量组次的课次可同时留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：08:30" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="开始时间：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：08:30" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练内容：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：水上耐力训练" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练内容：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：水上耐力训练" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练阶段：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础期" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="L10:L503">
-      <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="L4:L503">
-      <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SRPE：怎么填" prompt="本次训练负荷：系统用时长和RPE计算。怎么填：日常不用填。填写训练时长和RPE后由系统计算；只有已有外部原始负荷值时才补这列。例：360。为什么：用于记录训练负荷，公式为分钟数×RPE。不知道时：没有外部原始值就留空；缺RPE时也不用自己估算。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SRPE：怎么填" prompt="本次训练负荷：系统用时长和RPE计算。怎么填：日常不用填。填写训练时长和RPE后由系统计算；只有已有外部原始负荷值时才补这列。例：360。为什么：用于记录训练负荷，公式为分钟数×RPE。不知道时：没有外部原始值就留空；缺RPE时也不用自己估算。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SMVL：怎么填" prompt="力量训练量：系统汇总实际次数和重量。怎么填：日常不用填，逐组填写实际次数和实际重量；只有外部记录已给出整课总量时才补本列。例：360。为什么：用于汇总力量训练完成量；计划重量不能当成实际重量。不知道时：不知道整课总量就留空，不必手算，也不要填0占位。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="SMVL：怎么填" prompt="力量训练量：系统汇总实际次数和重量。怎么填：日常不用填，逐组填写实际次数和实际重量；只有外部记录已给出整课总量时才补本列。例：360。为什么：用于汇总力量训练完成量；计划重量不能当成实际重量。不知道时：不知道整课总量就留空，不必手算，也不要填0占位。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：140" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O10:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：140" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="O4:O503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最大心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：175" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P10:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="最大心率：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：175" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="P4:P503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均功率W：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="平均功率W：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="桨频SPM：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：22" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="桨频SPM：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：22" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:R503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -23198,143 +20790,64 @@
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:V2"/>
   </mergeCells>
-  <dataValidations count="44">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+  <dataValidations count="18">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:J503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:J503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：已完成、未完成" sqref="K10:K503">
+      <formula1>"已完成,未完成"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：已完成、未完成" sqref="K4:K503">
+      <formula1>"已完成,未完成"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:N503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:N503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="O10:O503">
+      <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="O4:O503">
+      <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="P10:P503">
+      <formula1>"上肢,下肢,核心,全身"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="P4:P503">
+      <formula1>"上肢,下肢,核心,全身"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:R503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:R503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="S10:S503">
+      <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="S4:S503">
+      <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:U503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次序号：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:U503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组序：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组序：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：上午力量" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="课次名称：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：上午力量" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="完成状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：已完成 可选：已完成、未完成" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：已完成、未完成" sqref="K10:K503">
-      <formula1>"已完成,未完成"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="完成状态：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：已完成 可选：已完成、未完成" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：已完成、未完成" sqref="K4:K503">
-      <formula1>"已完成,未完成"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度百分比：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N10:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度百分比：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="N4:N503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="类别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="O10:O503">
-      <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="类别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="O4:O503">
-      <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体部位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="P10:P503">
-      <formula1>"上肢,下肢,核心,全身"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体部位：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="P4:P503">
-      <formula1>"上肢,下肢,核心,全身"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作代码：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：squat" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作代码：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：squat" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="S10:S503">
-      <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="S4:S503">
-      <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T10:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次时长分钟：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="T4:T503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次距离千米：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次距离千米：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="V10:V503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="V10:V503">
       <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="V4:V503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="V4:V503">
       <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -25426,83 +22939,28 @@
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <dataValidations count="24">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+  <dataValidations count="6">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:J503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:J503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：正常、休息、关注、警报、缺失" sqref="K10:K503">
+      <formula1>"正常,休息,关注,警报,缺失"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：正常、休息、关注、警报、缺失" sqref="K4:K503">
+      <formula1>"正常,休息,关注,警报,缺失"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠小时：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：8" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠小时：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：8" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠质量：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="睡眠质量：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疲劳：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疲劳：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉酸痛：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="肌肉酸痛：怎么填" prompt="0—10分，越高越严重；仅填本人实际报告。 例：2" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="情绪：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="情绪：怎么填" prompt="0—10分，越高越好；仅填本人实际报告。 例：4" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="晨脉：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：55" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="晨脉：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：55" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="体重kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：75" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="从下拉选择正常、休息、关注、警报或缺失；至少一项恢复数值或状态，不能仅备注。 例：正常 可选：正常、休息、关注、警报、缺失" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：正常、休息、关注、警报、缺失" sqref="K10:K503">
-      <formula1>"正常,休息,关注,警报,缺失"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="从下拉选择正常、休息、关注、警报或缺失；至少一项恢复数值或状态，不能仅备注。 例：正常 可选：正常、休息、关注、警报、缺失" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：正常、休息、关注、警报、缺失" sqref="K4:K503">
-      <formula1>"正常,休息,关注,警报,缺失"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -28096,82 +25554,33 @@
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <dataValidations count="24">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+  <dataValidations count="8">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:E503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:E503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：左、右、双侧、未指定" sqref="F10:F503">
+      <formula1>"左,右,双侧,未指定"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：左、右、双侧、未指定" sqref="F4:F503">
+      <formula1>"左,右,双侧,未指定"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：健康、观察、限训、康复、停训" sqref="G10:G503">
+      <formula1>"健康,观察,限训,康复,停训"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：健康、观察、限训、康复、停训" sqref="G4:G503">
+      <formula1>"健康,观察,限训,康复,停训"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:L503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="姓名：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="发生日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="发生日期：怎么填" prompt="本行日期或上传页明确选择的统一日期必须提供一个；不自动使用今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="伤病名称：怎么填" prompt="填写实际记录。 例：踝关节扭伤" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="伤病名称：怎么填" prompt="填写实际记录。 例：踝关节扭伤" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="部位：怎么填" prompt="填写实际记录。 例：踝关节" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="部位：怎么填" prompt="填写实际记录。 例：踝关节" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：左 可选：左、右、双侧、未指定" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：左、右、双侧、未指定" sqref="F10:F503">
-      <formula1>"左,右,双侧,未指定"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="侧别：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：左 可选：左、右、双侧、未指定" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：左、右、双侧、未指定" sqref="F4:F503">
-      <formula1>"左,右,双侧,未指定"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="空白新增时沿用观察状态，不自动推断诊断。 例：观察 可选：健康、观察、限训、康复、停训" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：健康、观察、限训、康复、停训" sqref="G10:G503">
-      <formula1>"健康,观察,限训,康复,停训"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="状态：怎么填" prompt="空白新增时沿用观察状态，不自动推断诊断。 例：观察 可选：健康、观察、限训、康复、停训" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：健康、观察、限训、康复、停训" sqref="G4:G503">
-      <formula1>"健康,观察,限训,康复,停训"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疼痛评分：怎么填" prompt="0—10分；0表示无痛，未采集必须留空。 例：2" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="疼痛评分：怎么填" prompt="0—10分；0表示无痛，未采集必须留空。 例：2" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练限制：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：避免跑跳" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练限制：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：避免跑跳" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="康复计划：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按专业人员制定的方案填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K10:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="康复计划：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：按专业人员制定的方案填写" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="K4:K503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="复查日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="复查日期：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:L503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>